--- a/data/BioTecnos.xlsx
+++ b/data/BioTecnos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="660">
   <si>
     <t>ID</t>
   </si>
@@ -58,6 +58,9 @@
     <t>897</t>
   </si>
   <si>
+    <t>893</t>
+  </si>
+  <si>
     <t>892</t>
   </si>
   <si>
@@ -580,6 +583,9 @@
     <t>M02T118LA5601</t>
   </si>
   <si>
+    <t>M02Q047L24606</t>
+  </si>
+  <si>
     <t>M02Q047LA5602</t>
   </si>
   <si>
@@ -1369,6 +1375,9 @@
     <t>02T118LA5</t>
   </si>
   <si>
+    <t>02Q047L24</t>
+  </si>
+  <si>
     <t>02Q047LA5</t>
   </si>
   <si>
@@ -1435,9 +1444,6 @@
     <t>02Q047L14</t>
   </si>
   <si>
-    <t>02Q047L24</t>
-  </si>
-  <si>
     <t>04L005</t>
   </si>
   <si>
@@ -1567,6 +1573,9 @@
     <t>56</t>
   </si>
   <si>
+    <t>7.656</t>
+  </si>
+  <si>
     <t>960</t>
   </si>
   <si>
@@ -1732,117 +1741,111 @@
     <t>16.192</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1.152</t>
+  </si>
+  <si>
+    <t>100.232</t>
+  </si>
+  <si>
+    <t>2.211</t>
+  </si>
+  <si>
+    <t>13.605</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>2.358</t>
+  </si>
+  <si>
+    <t>64.800</t>
+  </si>
+  <si>
+    <t>53.624</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>15.591</t>
+  </si>
+  <si>
+    <t>10.238</t>
+  </si>
+  <si>
+    <t>3.635</t>
+  </si>
+  <si>
+    <t>580</t>
+  </si>
+  <si>
+    <t>3.505</t>
+  </si>
+  <si>
+    <t>2.777</t>
+  </si>
+  <si>
+    <t>12.408</t>
+  </si>
+  <si>
+    <t>5.856</t>
+  </si>
+  <si>
+    <t>21.024</t>
+  </si>
+  <si>
+    <t>14.356</t>
+  </si>
+  <si>
+    <t>1.248</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>5.731</t>
+  </si>
+  <si>
+    <t>67.416</t>
+  </si>
+  <si>
+    <t>4.680</t>
+  </si>
+  <si>
+    <t>6.480</t>
+  </si>
+  <si>
+    <t>1.056</t>
+  </si>
+  <si>
+    <t>648</t>
+  </si>
+  <si>
+    <t>9.642</t>
+  </si>
+  <si>
+    <t>6.264</t>
+  </si>
+  <si>
+    <t>16.032</t>
+  </si>
+  <si>
+    <t>528</t>
+  </si>
+  <si>
+    <t>126.669</t>
+  </si>
+  <si>
+    <t>2.083</t>
+  </si>
+  <si>
     <t>1.392</t>
   </si>
   <si>
-    <t>7.292</t>
-  </si>
-  <si>
-    <t>127.516</t>
-  </si>
-  <si>
-    <t>2.211</t>
-  </si>
-  <si>
-    <t>13.605</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>3.600</t>
-  </si>
-  <si>
-    <t>64.800</t>
-  </si>
-  <si>
-    <t>53.624</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>15.591</t>
-  </si>
-  <si>
-    <t>10.238</t>
-  </si>
-  <si>
-    <t>3.635</t>
-  </si>
-  <si>
-    <t>6.888</t>
-  </si>
-  <si>
-    <t>44.808</t>
-  </si>
-  <si>
-    <t>12.696</t>
-  </si>
-  <si>
-    <t>3.505</t>
-  </si>
-  <si>
-    <t>2.777</t>
-  </si>
-  <si>
-    <t>12.408</t>
-  </si>
-  <si>
-    <t>5.856</t>
-  </si>
-  <si>
-    <t>21.024</t>
-  </si>
-  <si>
-    <t>16.106</t>
-  </si>
-  <si>
-    <t>1.248</t>
-  </si>
-  <si>
-    <t>258</t>
-  </si>
-  <si>
-    <t>5.731</t>
-  </si>
-  <si>
-    <t>67.416</t>
-  </si>
-  <si>
-    <t>4.680</t>
-  </si>
-  <si>
-    <t>6.480</t>
-  </si>
-  <si>
-    <t>1.056</t>
-  </si>
-  <si>
-    <t>648</t>
-  </si>
-  <si>
-    <t>9.642</t>
-  </si>
-  <si>
-    <t>6.264</t>
-  </si>
-  <si>
-    <t>16.032</t>
-  </si>
-  <si>
-    <t>528</t>
-  </si>
-  <si>
-    <t>189.888</t>
-  </si>
-  <si>
-    <t>2.083</t>
-  </si>
-  <si>
     <t>4.256</t>
   </si>
   <si>
@@ -1879,7 +1882,7 @@
     <t>13.809</t>
   </si>
   <si>
-    <t>3.408</t>
+    <t>2.726</t>
   </si>
   <si>
     <t>9.446</t>
@@ -1945,7 +1948,7 @@
     <t>3.590</t>
   </si>
   <si>
-    <t>3.666</t>
+    <t>1.916</t>
   </si>
   <si>
     <t>384</t>
@@ -1982,9 +1985,6 @@
   </si>
   <si>
     <t>5.100</t>
-  </si>
-  <si>
-    <t>1.619</t>
   </si>
   <si>
     <t>1.239</t>
@@ -2325,7 +2325,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I175"/>
+  <dimension ref="A1:I176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2362,22 +2362,22 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="H2" t="s">
         <v>658</v>
@@ -2391,22 +2391,22 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H3" t="s">
         <v>658</v>
@@ -2420,22 +2420,22 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F4" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G4" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="H4" t="s">
         <v>658</v>
@@ -2449,22 +2449,22 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E5" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F5" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G5" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H5" t="s">
         <v>658</v>
@@ -2478,22 +2478,22 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C6" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F6" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G6" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H6" t="s">
         <v>658</v>
@@ -2507,22 +2507,22 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D7" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E7" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F7" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G7" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="H7" t="s">
         <v>658</v>
@@ -2536,22 +2536,22 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E8" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F8" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="H8" t="s">
         <v>658</v>
@@ -2565,22 +2565,22 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D9" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E9" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F9" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G9" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H9" t="s">
         <v>658</v>
@@ -2594,22 +2594,22 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D10" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F10" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G10" t="s">
-        <v>146</v>
+        <v>522</v>
       </c>
       <c r="H10" t="s">
         <v>658</v>
@@ -2623,22 +2623,22 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C11" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D11" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E11" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F11" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G11" t="s">
-        <v>520</v>
+        <v>147</v>
       </c>
       <c r="H11" t="s">
         <v>658</v>
@@ -2652,22 +2652,22 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C12" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D12" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E12" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F12" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="H12" t="s">
         <v>658</v>
@@ -2681,22 +2681,22 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C13" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D13" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E13" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F13" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G13" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H13" t="s">
         <v>658</v>
@@ -2710,22 +2710,22 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D14" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E14" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F14" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G14" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="H14" t="s">
         <v>658</v>
@@ -2739,22 +2739,22 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D15" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E15" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F15" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G15" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="H15" t="s">
         <v>658</v>
@@ -2768,22 +2768,22 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C16" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D16" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E16" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F16" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G16" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="H16" t="s">
         <v>658</v>
@@ -2797,22 +2797,22 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C17" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D17" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E17" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F17" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G17" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="H17" t="s">
         <v>658</v>
@@ -2826,22 +2826,22 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C18" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D18" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E18" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F18" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G18" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H18" t="s">
         <v>658</v>
@@ -2855,22 +2855,22 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C19" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D19" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E19" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="F19" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G19" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="H19" t="s">
         <v>658</v>
@@ -2884,22 +2884,22 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C20" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D20" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E20" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F20" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G20" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="H20" t="s">
         <v>658</v>
@@ -2913,22 +2913,22 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C21" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D21" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E21" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F21" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G21" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H21" t="s">
         <v>658</v>
@@ -2942,22 +2942,22 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C22" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D22" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E22" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F22" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G22" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="H22" t="s">
         <v>658</v>
@@ -2971,22 +2971,22 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C23" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D23" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E23" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F23" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G23" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H23" t="s">
         <v>658</v>
@@ -3000,22 +3000,22 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C24" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D24" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E24" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F24" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G24" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="H24" t="s">
         <v>658</v>
@@ -3029,22 +3029,22 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C25" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D25" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E25" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F25" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G25" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="H25" t="s">
         <v>658</v>
@@ -3058,22 +3058,22 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C26" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D26" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E26" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F26" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G26" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="H26" t="s">
         <v>658</v>
@@ -3087,22 +3087,22 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C27" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D27" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E27" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F27" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G27" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="H27" t="s">
         <v>658</v>
@@ -3116,22 +3116,22 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C28" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D28" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E28" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F28" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G28" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="H28" t="s">
         <v>658</v>
@@ -3145,22 +3145,22 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C29" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D29" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E29" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F29" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G29" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H29" t="s">
         <v>658</v>
@@ -3174,22 +3174,22 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C30" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D30" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E30" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F30" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G30" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H30" t="s">
         <v>658</v>
@@ -3203,22 +3203,22 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C31" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D31" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E31" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G31" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H31" t="s">
         <v>658</v>
@@ -3232,22 +3232,22 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C32" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D32" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E32" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F32" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G32" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H32" t="s">
         <v>658</v>
@@ -3261,22 +3261,22 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C33" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D33" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E33" t="s">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="F33" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G33" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H33" t="s">
         <v>658</v>
@@ -3290,22 +3290,22 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C34" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D34" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E34" t="s">
-        <v>474</v>
+        <v>453</v>
       </c>
       <c r="F34" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G34" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H34" t="s">
         <v>658</v>
@@ -3319,22 +3319,22 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C35" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D35" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E35" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F35" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G35" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H35" t="s">
         <v>658</v>
@@ -3348,22 +3348,22 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C36" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D36" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E36" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F36" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G36" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H36" t="s">
         <v>658</v>
@@ -3377,22 +3377,22 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C37" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D37" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E37" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F37" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G37" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H37" t="s">
         <v>658</v>
@@ -3406,22 +3406,22 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C38" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D38" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E38" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F38" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G38" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H38" t="s">
         <v>658</v>
@@ -3435,22 +3435,22 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C39" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D39" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E39" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F39" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G39" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="H39" t="s">
         <v>658</v>
@@ -3464,22 +3464,22 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C40" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D40" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E40" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F40" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G40" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="H40" t="s">
         <v>658</v>
@@ -3493,22 +3493,22 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C41" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D41" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E41" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F41" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G41" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H41" t="s">
         <v>658</v>
@@ -3522,22 +3522,22 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C42" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D42" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E42" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F42" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G42" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="H42" t="s">
         <v>658</v>
@@ -3551,22 +3551,22 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C43" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D43" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E43" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F43" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G43" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="H43" t="s">
         <v>658</v>
@@ -3580,22 +3580,22 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C44" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D44" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E44" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F44" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G44" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H44" t="s">
         <v>658</v>
@@ -3609,22 +3609,22 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C45" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D45" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E45" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="F45" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G45" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H45" t="s">
         <v>658</v>
@@ -3638,22 +3638,22 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C46" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D46" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E46" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="F46" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G46" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H46" t="s">
         <v>658</v>
@@ -3667,22 +3667,22 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C47" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D47" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E47" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F47" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G47" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H47" t="s">
         <v>658</v>
@@ -3696,22 +3696,22 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C48" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D48" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E48" t="s">
-        <v>452</v>
+        <v>488</v>
       </c>
       <c r="F48" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G48" t="s">
-        <v>141</v>
+        <v>559</v>
       </c>
       <c r="H48" t="s">
         <v>658</v>
@@ -3725,22 +3725,22 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C49" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D49" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E49" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F49" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G49" t="s">
-        <v>557</v>
+        <v>142</v>
       </c>
       <c r="H49" t="s">
         <v>658</v>
@@ -3754,22 +3754,22 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C50" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D50" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E50" t="s">
-        <v>485</v>
+        <v>457</v>
       </c>
       <c r="F50" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G50" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H50" t="s">
         <v>658</v>
@@ -3783,22 +3783,22 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C51" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D51" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E51" t="s">
-        <v>454</v>
+        <v>487</v>
       </c>
       <c r="F51" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G51" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H51" t="s">
         <v>658</v>
@@ -3812,22 +3812,22 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C52" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D52" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E52" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="F52" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G52" t="s">
-        <v>175</v>
+        <v>562</v>
       </c>
       <c r="H52" t="s">
         <v>658</v>
@@ -3841,22 +3841,22 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C53" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D53" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E53" t="s">
-        <v>487</v>
+        <v>456</v>
       </c>
       <c r="F53" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G53" t="s">
-        <v>560</v>
+        <v>176</v>
       </c>
       <c r="H53" t="s">
         <v>658</v>
@@ -3870,22 +3870,22 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C54" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D54" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E54" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="F54" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G54" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="H54" t="s">
         <v>658</v>
@@ -3899,22 +3899,22 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C55" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D55" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E55" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F55" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G55" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H55" t="s">
         <v>658</v>
@@ -3928,22 +3928,22 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C56" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D56" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E56" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="F56" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G56" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H56" t="s">
         <v>658</v>
@@ -3957,22 +3957,22 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C57" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D57" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E57" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="F57" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G57" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H57" t="s">
         <v>658</v>
@@ -3986,22 +3986,22 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C58" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D58" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E58" t="s">
-        <v>489</v>
+        <v>455</v>
       </c>
       <c r="F58" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G58" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="H58" t="s">
         <v>658</v>
@@ -4015,22 +4015,22 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C59" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D59" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E59" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="F59" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G59" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="H59" t="s">
         <v>658</v>
@@ -4044,22 +4044,22 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C60" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D60" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E60" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="F60" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G60" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="H60" t="s">
         <v>658</v>
@@ -4073,22 +4073,22 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C61" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D61" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E61" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F61" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G61" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="H61" t="s">
         <v>658</v>
@@ -4102,22 +4102,22 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C62" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D62" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E62" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F62" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G62" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H62" t="s">
         <v>658</v>
@@ -4131,22 +4131,22 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C63" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D63" t="s">
         <v>445</v>
       </c>
       <c r="E63" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F63" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G63" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H63" t="s">
         <v>658</v>
@@ -4160,22 +4160,22 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C64" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D64" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E64" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F64" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G64" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H64" t="s">
         <v>658</v>
@@ -4189,22 +4189,22 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C65" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D65" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E65" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="F65" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G65" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="H65" t="s">
         <v>658</v>
@@ -4218,22 +4218,22 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C66" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D66" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E66" t="s">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="F66" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G66" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="H66" t="s">
         <v>658</v>
@@ -4247,22 +4247,22 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C67" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D67" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E67" t="s">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="F67" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G67" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="H67" t="s">
         <v>658</v>
@@ -4276,22 +4276,22 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C68" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D68" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E68" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="F68" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G68" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H68" t="s">
         <v>658</v>
@@ -4305,22 +4305,22 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C69" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D69" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E69" t="s">
-        <v>493</v>
+        <v>469</v>
       </c>
       <c r="F69" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G69" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H69" t="s">
         <v>658</v>
@@ -4334,22 +4334,22 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C70" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D70" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E70" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F70" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G70" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="H70" t="s">
         <v>658</v>
@@ -4363,22 +4363,22 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C71" t="s">
         <v>383</v>
       </c>
       <c r="D71" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E71" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F71" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G71" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="H71" t="s">
         <v>658</v>
@@ -4392,22 +4392,22 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C72" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D72" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E72" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="F72" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G72" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="H72" t="s">
         <v>658</v>
@@ -4421,22 +4421,22 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C73" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D73" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E73" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="F73" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G73" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="H73" t="s">
         <v>658</v>
@@ -4450,22 +4450,22 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C74" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D74" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E74" t="s">
-        <v>492</v>
+        <v>462</v>
       </c>
       <c r="F74" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G74" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="H74" t="s">
         <v>658</v>
@@ -4479,22 +4479,22 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C75" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D75" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E75" t="s">
         <v>494</v>
       </c>
       <c r="F75" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G75" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H75" t="s">
         <v>658</v>
@@ -4508,22 +4508,22 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C76" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D76" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E76" t="s">
-        <v>466</v>
+        <v>496</v>
       </c>
       <c r="F76" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G76" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="H76" t="s">
         <v>658</v>
@@ -4537,22 +4537,22 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C77" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D77" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E77" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="F77" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G77" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H77" t="s">
         <v>658</v>
@@ -4566,22 +4566,22 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D78" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E78" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F78" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G78" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="H78" t="s">
         <v>658</v>
@@ -4595,22 +4595,22 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C79" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D79" t="s">
         <v>445</v>
       </c>
       <c r="E79" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="F79" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G79" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="H79" t="s">
         <v>658</v>
@@ -4624,22 +4624,22 @@
         <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C80" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D80" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E80" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="F80" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G80" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="H80" t="s">
         <v>658</v>
@@ -4653,22 +4653,22 @@
         <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C81" t="s">
         <v>391</v>
       </c>
       <c r="D81" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E81" t="s">
-        <v>451</v>
+        <v>492</v>
       </c>
       <c r="F81" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G81" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="H81" t="s">
         <v>658</v>
@@ -4682,22 +4682,22 @@
         <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C82" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D82" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E82" t="s">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="F82" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G82" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="H82" t="s">
         <v>658</v>
@@ -4711,22 +4711,22 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C83" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D83" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E83" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="F83" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G83" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="H83" t="s">
         <v>658</v>
@@ -4740,22 +4740,22 @@
         <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C84" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D84" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E84" t="s">
-        <v>495</v>
+        <v>474</v>
       </c>
       <c r="F84" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G84" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="H84" t="s">
         <v>658</v>
@@ -4769,22 +4769,22 @@
         <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C85" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D85" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E85" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F85" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G85" t="s">
-        <v>589</v>
+        <v>571</v>
       </c>
       <c r="H85" t="s">
         <v>658</v>
@@ -4798,22 +4798,22 @@
         <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C86" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D86" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E86" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="F86" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G86" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H86" t="s">
         <v>658</v>
@@ -4827,22 +4827,22 @@
         <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C87" t="s">
         <v>393</v>
       </c>
       <c r="D87" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E87" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F87" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G87" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H87" t="s">
         <v>658</v>
@@ -4856,22 +4856,22 @@
         <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C88" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D88" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E88" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="F88" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G88" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H88" t="s">
         <v>658</v>
@@ -4885,22 +4885,22 @@
         <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C89" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D89" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E89" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F89" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G89" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H89" t="s">
         <v>658</v>
@@ -4914,22 +4914,22 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C90" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D90" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E90" t="s">
-        <v>484</v>
+        <v>454</v>
       </c>
       <c r="F90" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G90" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H90" t="s">
         <v>658</v>
@@ -4943,22 +4943,22 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C91" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D91" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E91" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="F91" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G91" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H91" t="s">
         <v>658</v>
@@ -4972,22 +4972,22 @@
         <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C92" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D92" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E92" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F92" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G92" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H92" t="s">
         <v>658</v>
@@ -5001,22 +5001,22 @@
         <v>100</v>
       </c>
       <c r="B93" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C93" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D93" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E93" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="F93" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G93" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H93" t="s">
         <v>658</v>
@@ -5030,22 +5030,22 @@
         <v>101</v>
       </c>
       <c r="B94" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C94" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D94" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E94" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F94" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G94" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H94" t="s">
         <v>658</v>
@@ -5059,22 +5059,22 @@
         <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C95" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D95" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E95" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="F95" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G95" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H95" t="s">
         <v>658</v>
@@ -5088,22 +5088,22 @@
         <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C96" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D96" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E96" t="s">
-        <v>454</v>
+        <v>487</v>
       </c>
       <c r="F96" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G96" t="s">
-        <v>526</v>
+        <v>599</v>
       </c>
       <c r="H96" t="s">
         <v>658</v>
@@ -5117,22 +5117,22 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C97" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D97" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E97" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="F97" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G97" t="s">
-        <v>600</v>
+        <v>529</v>
       </c>
       <c r="H97" t="s">
         <v>658</v>
@@ -5146,22 +5146,22 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C98" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D98" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E98" t="s">
-        <v>497</v>
+        <v>456</v>
       </c>
       <c r="F98" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G98" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H98" t="s">
         <v>658</v>
@@ -5175,22 +5175,22 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C99" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D99" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E99" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="F99" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G99" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H99" t="s">
         <v>658</v>
@@ -5204,22 +5204,22 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C100" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D100" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E100" t="s">
-        <v>456</v>
+        <v>491</v>
       </c>
       <c r="F100" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G100" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H100" t="s">
         <v>658</v>
@@ -5233,22 +5233,22 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C101" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D101" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E101" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F101" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G101" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H101" t="s">
         <v>658</v>
@@ -5262,22 +5262,22 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C102" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D102" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E102" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F102" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G102" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H102" t="s">
         <v>658</v>
@@ -5291,22 +5291,22 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C103" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D103" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E103" t="s">
-        <v>480</v>
+        <v>454</v>
       </c>
       <c r="F103" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G103" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H103" t="s">
         <v>658</v>
@@ -5320,22 +5320,22 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C104" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D104" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E104" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="F104" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G104" t="s">
-        <v>87</v>
+        <v>606</v>
       </c>
       <c r="H104" t="s">
         <v>658</v>
@@ -5349,22 +5349,22 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C105" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D105" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E105" t="s">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="F105" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G105" t="s">
-        <v>607</v>
+        <v>88</v>
       </c>
       <c r="H105" t="s">
         <v>658</v>
@@ -5378,22 +5378,22 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C106" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D106" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E106" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="F106" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G106" t="s">
-        <v>547</v>
+        <v>607</v>
       </c>
       <c r="H106" t="s">
         <v>658</v>
@@ -5407,22 +5407,22 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C107" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D107" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E107" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F107" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G107" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="H107" t="s">
         <v>658</v>
@@ -5436,22 +5436,22 @@
         <v>115</v>
       </c>
       <c r="B108" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C108" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D108" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E108" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="F108" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G108" t="s">
-        <v>608</v>
+        <v>543</v>
       </c>
       <c r="H108" t="s">
         <v>658</v>
@@ -5465,22 +5465,22 @@
         <v>116</v>
       </c>
       <c r="B109" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C109" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D109" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E109" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F109" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G109" t="s">
-        <v>572</v>
+        <v>608</v>
       </c>
       <c r="H109" t="s">
         <v>658</v>
@@ -5494,19 +5494,19 @@
         <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C110" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D110" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E110" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F110" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G110" t="s">
         <v>609</v>
@@ -5523,19 +5523,19 @@
         <v>118</v>
       </c>
       <c r="B111" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C111" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D111" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E111" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="F111" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G111" t="s">
         <v>610</v>
@@ -5552,19 +5552,19 @@
         <v>119</v>
       </c>
       <c r="B112" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C112" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D112" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E112" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F112" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G112" t="s">
         <v>611</v>
@@ -5581,19 +5581,19 @@
         <v>120</v>
       </c>
       <c r="B113" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C113" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D113" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E113" t="s">
-        <v>498</v>
+        <v>454</v>
       </c>
       <c r="F113" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G113" t="s">
         <v>612</v>
@@ -5610,19 +5610,19 @@
         <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C114" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D114" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E114" t="s">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="F114" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G114" t="s">
         <v>613</v>
@@ -5639,19 +5639,19 @@
         <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C115" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D115" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E115" t="s">
-        <v>499</v>
+        <v>453</v>
       </c>
       <c r="F115" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G115" t="s">
         <v>614</v>
@@ -5668,19 +5668,19 @@
         <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C116" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D116" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E116" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F116" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G116" t="s">
         <v>615</v>
@@ -5697,19 +5697,19 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C117" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D117" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E117" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F117" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G117" t="s">
         <v>616</v>
@@ -5726,19 +5726,19 @@
         <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C118" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D118" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E118" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F118" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G118" t="s">
         <v>617</v>
@@ -5755,19 +5755,19 @@
         <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C119" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D119" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E119" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F119" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G119" t="s">
         <v>618</v>
@@ -5784,19 +5784,19 @@
         <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C120" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D120" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E120" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F120" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G120" t="s">
         <v>619</v>
@@ -5813,19 +5813,19 @@
         <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C121" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D121" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E121" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="F121" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G121" t="s">
         <v>620</v>
@@ -5842,19 +5842,19 @@
         <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C122" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D122" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E122" t="s">
-        <v>505</v>
+        <v>483</v>
       </c>
       <c r="F122" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G122" t="s">
         <v>621</v>
@@ -5871,19 +5871,19 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C123" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D123" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E123" t="s">
-        <v>471</v>
+        <v>507</v>
       </c>
       <c r="F123" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G123" t="s">
         <v>622</v>
@@ -5900,19 +5900,19 @@
         <v>131</v>
       </c>
       <c r="B124" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C124" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D124" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E124" t="s">
-        <v>506</v>
+        <v>474</v>
       </c>
       <c r="F124" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G124" t="s">
         <v>623</v>
@@ -5929,19 +5929,19 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C125" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D125" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E125" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F125" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G125" t="s">
         <v>624</v>
@@ -5958,22 +5958,22 @@
         <v>133</v>
       </c>
       <c r="B126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C126" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D126" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E126" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="F126" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G126" t="s">
-        <v>513</v>
+        <v>625</v>
       </c>
       <c r="H126" t="s">
         <v>658</v>
@@ -5987,22 +5987,22 @@
         <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C127" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D127" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E127" t="s">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="F127" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G127" t="s">
-        <v>582</v>
+        <v>515</v>
       </c>
       <c r="H127" t="s">
         <v>658</v>
@@ -6016,22 +6016,22 @@
         <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C128" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D128" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E128" t="s">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="F128" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G128" t="s">
-        <v>625</v>
+        <v>575</v>
       </c>
       <c r="H128" t="s">
         <v>658</v>
@@ -6045,22 +6045,22 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C129" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D129" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E129" t="s">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="F129" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G129" t="s">
-        <v>582</v>
+        <v>626</v>
       </c>
       <c r="H129" t="s">
         <v>658</v>
@@ -6074,22 +6074,22 @@
         <v>137</v>
       </c>
       <c r="B130" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C130" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D130" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E130" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F130" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G130" t="s">
-        <v>626</v>
+        <v>575</v>
       </c>
       <c r="H130" t="s">
         <v>658</v>
@@ -6103,19 +6103,19 @@
         <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C131" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D131" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E131" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="F131" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G131" t="s">
         <v>627</v>
@@ -6132,22 +6132,22 @@
         <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C132" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D132" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E132" t="s">
-        <v>452</v>
+        <v>492</v>
       </c>
       <c r="F132" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G132" t="s">
-        <v>126</v>
+        <v>628</v>
       </c>
       <c r="H132" t="s">
         <v>658</v>
@@ -6161,22 +6161,22 @@
         <v>140</v>
       </c>
       <c r="B133" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C133" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D133" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E133" t="s">
-        <v>499</v>
+        <v>455</v>
       </c>
       <c r="F133" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G133" t="s">
-        <v>628</v>
+        <v>127</v>
       </c>
       <c r="H133" t="s">
         <v>658</v>
@@ -6190,19 +6190,19 @@
         <v>141</v>
       </c>
       <c r="B134" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C134" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D134" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E134" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="F134" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G134" t="s">
         <v>629</v>
@@ -6219,19 +6219,19 @@
         <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C135" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D135" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E135" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="F135" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G135" t="s">
         <v>630</v>
@@ -6248,19 +6248,19 @@
         <v>143</v>
       </c>
       <c r="B136" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C136" t="s">
         <v>418</v>
       </c>
       <c r="D136" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E136" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F136" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G136" t="s">
         <v>631</v>
@@ -6277,22 +6277,22 @@
         <v>144</v>
       </c>
       <c r="B137" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C137" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D137" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E137" t="s">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="F137" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G137" t="s">
-        <v>116</v>
+        <v>632</v>
       </c>
       <c r="H137" t="s">
         <v>658</v>
@@ -6306,22 +6306,22 @@
         <v>145</v>
       </c>
       <c r="B138" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C138" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D138" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E138" t="s">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="F138" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G138" t="s">
-        <v>632</v>
+        <v>117</v>
       </c>
       <c r="H138" t="s">
         <v>658</v>
@@ -6335,19 +6335,19 @@
         <v>146</v>
       </c>
       <c r="B139" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C139" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D139" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E139" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F139" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G139" t="s">
         <v>633</v>
@@ -6364,19 +6364,19 @@
         <v>147</v>
       </c>
       <c r="B140" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C140" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D140" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E140" t="s">
-        <v>491</v>
+        <v>455</v>
       </c>
       <c r="F140" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G140" t="s">
         <v>634</v>
@@ -6393,19 +6393,19 @@
         <v>148</v>
       </c>
       <c r="B141" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C141" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D141" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E141" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F141" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G141" t="s">
         <v>635</v>
@@ -6422,22 +6422,22 @@
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C142" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D142" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E142" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="F142" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G142" t="s">
-        <v>530</v>
+        <v>636</v>
       </c>
       <c r="H142" t="s">
         <v>658</v>
@@ -6451,22 +6451,22 @@
         <v>150</v>
       </c>
       <c r="B143" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C143" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D143" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E143" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="F143" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G143" t="s">
-        <v>636</v>
+        <v>533</v>
       </c>
       <c r="H143" t="s">
         <v>658</v>
@@ -6480,19 +6480,19 @@
         <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C144" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D144" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E144" t="s">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="F144" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G144" t="s">
         <v>637</v>
@@ -6509,19 +6509,19 @@
         <v>152</v>
       </c>
       <c r="B145" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C145" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D145" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E145" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="F145" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G145" t="s">
         <v>638</v>
@@ -6538,19 +6538,19 @@
         <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C146" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D146" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E146" t="s">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="F146" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G146" t="s">
         <v>639</v>
@@ -6567,19 +6567,19 @@
         <v>154</v>
       </c>
       <c r="B147" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C147" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D147" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E147" t="s">
-        <v>495</v>
+        <v>453</v>
       </c>
       <c r="F147" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G147" t="s">
         <v>640</v>
@@ -6596,22 +6596,22 @@
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C148" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D148" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E148" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="F148" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G148" t="s">
-        <v>582</v>
+        <v>641</v>
       </c>
       <c r="H148" t="s">
         <v>658</v>
@@ -6625,22 +6625,22 @@
         <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C149" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D149" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E149" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F149" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G149" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="H149" t="s">
         <v>658</v>
@@ -6654,22 +6654,22 @@
         <v>157</v>
       </c>
       <c r="B150" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C150" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D150" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E150" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F150" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G150" t="s">
-        <v>641</v>
+        <v>575</v>
       </c>
       <c r="H150" t="s">
         <v>658</v>
@@ -6683,22 +6683,22 @@
         <v>158</v>
       </c>
       <c r="B151" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C151" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D151" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E151" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="F151" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G151" t="s">
-        <v>110</v>
+        <v>642</v>
       </c>
       <c r="H151" t="s">
         <v>658</v>
@@ -6712,22 +6712,22 @@
         <v>159</v>
       </c>
       <c r="B152" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C152" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D152" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E152" t="s">
-        <v>489</v>
+        <v>461</v>
       </c>
       <c r="F152" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G152" t="s">
-        <v>642</v>
+        <v>111</v>
       </c>
       <c r="H152" t="s">
         <v>658</v>
@@ -6741,19 +6741,19 @@
         <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C153" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D153" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E153" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="F153" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G153" t="s">
         <v>643</v>
@@ -6770,22 +6770,22 @@
         <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C154" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D154" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E154" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="F154" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G154" t="s">
-        <v>582</v>
+        <v>644</v>
       </c>
       <c r="H154" t="s">
         <v>658</v>
@@ -6799,22 +6799,22 @@
         <v>162</v>
       </c>
       <c r="B155" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C155" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D155" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E155" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="F155" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G155" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="H155" t="s">
         <v>658</v>
@@ -6828,22 +6828,22 @@
         <v>163</v>
       </c>
       <c r="B156" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C156" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D156" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E156" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="F156" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G156" t="s">
-        <v>644</v>
+        <v>575</v>
       </c>
       <c r="H156" t="s">
         <v>658</v>
@@ -6857,22 +6857,22 @@
         <v>164</v>
       </c>
       <c r="B157" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C157" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D157" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E157" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="F157" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G157" t="s">
-        <v>582</v>
+        <v>645</v>
       </c>
       <c r="H157" t="s">
         <v>658</v>
@@ -6886,22 +6886,22 @@
         <v>165</v>
       </c>
       <c r="B158" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C158" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D158" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E158" t="s">
-        <v>495</v>
+        <v>474</v>
       </c>
       <c r="F158" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G158" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="H158" t="s">
         <v>658</v>
@@ -6915,22 +6915,22 @@
         <v>166</v>
       </c>
       <c r="B159" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C159" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D159" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E159" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="F159" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G159" t="s">
-        <v>645</v>
+        <v>575</v>
       </c>
       <c r="H159" t="s">
         <v>658</v>
@@ -6944,22 +6944,22 @@
         <v>167</v>
       </c>
       <c r="B160" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C160" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D160" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E160" t="s">
-        <v>473</v>
+        <v>510</v>
       </c>
       <c r="F160" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G160" t="s">
-        <v>582</v>
+        <v>646</v>
       </c>
       <c r="H160" t="s">
         <v>658</v>
@@ -6973,22 +6973,22 @@
         <v>168</v>
       </c>
       <c r="B161" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C161" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D161" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E161" t="s">
-        <v>498</v>
+        <v>453</v>
       </c>
       <c r="F161" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G161" t="s">
-        <v>646</v>
+        <v>575</v>
       </c>
       <c r="H161" t="s">
         <v>658</v>
@@ -7002,19 +7002,19 @@
         <v>169</v>
       </c>
       <c r="B162" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C162" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D162" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E162" t="s">
-        <v>471</v>
+        <v>500</v>
       </c>
       <c r="F162" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G162" t="s">
         <v>647</v>
@@ -7031,22 +7031,22 @@
         <v>170</v>
       </c>
       <c r="B163" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C163" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D163" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E163" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F163" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G163" t="s">
-        <v>582</v>
+        <v>648</v>
       </c>
       <c r="H163" t="s">
         <v>658</v>
@@ -7060,22 +7060,22 @@
         <v>171</v>
       </c>
       <c r="B164" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C164" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D164" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E164" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="F164" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G164" t="s">
-        <v>648</v>
+        <v>575</v>
       </c>
       <c r="H164" t="s">
         <v>658</v>
@@ -7089,22 +7089,22 @@
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C165" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D165" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E165" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="F165" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G165" t="s">
-        <v>563</v>
+        <v>649</v>
       </c>
       <c r="H165" t="s">
         <v>658</v>
@@ -7118,22 +7118,22 @@
         <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C166" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D166" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E166" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="F166" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G166" t="s">
-        <v>649</v>
+        <v>566</v>
       </c>
       <c r="H166" t="s">
         <v>658</v>
@@ -7147,19 +7147,19 @@
         <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C167" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D167" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E167" t="s">
         <v>455</v>
       </c>
       <c r="F167" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G167" t="s">
         <v>650</v>
@@ -7176,19 +7176,19 @@
         <v>175</v>
       </c>
       <c r="B168" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C168" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D168" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E168" t="s">
-        <v>484</v>
+        <v>458</v>
       </c>
       <c r="F168" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G168" t="s">
         <v>651</v>
@@ -7205,19 +7205,19 @@
         <v>176</v>
       </c>
       <c r="B169" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C169" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D169" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E169" t="s">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="F169" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G169" t="s">
         <v>652</v>
@@ -7234,19 +7234,19 @@
         <v>177</v>
       </c>
       <c r="B170" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C170" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D170" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E170" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F170" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G170" t="s">
         <v>653</v>
@@ -7263,19 +7263,19 @@
         <v>178</v>
       </c>
       <c r="B171" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C171" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D171" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E171" t="s">
-        <v>485</v>
+        <v>512</v>
       </c>
       <c r="F171" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G171" t="s">
         <v>654</v>
@@ -7292,19 +7292,19 @@
         <v>179</v>
       </c>
       <c r="B172" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C172" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D172" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E172" t="s">
-        <v>454</v>
+        <v>487</v>
       </c>
       <c r="F172" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G172" t="s">
         <v>655</v>
@@ -7321,19 +7321,19 @@
         <v>180</v>
       </c>
       <c r="B173" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C173" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D173" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E173" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="F173" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G173" t="s">
         <v>656</v>
@@ -7350,22 +7350,22 @@
         <v>181</v>
       </c>
       <c r="B174" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C174" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D174" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E174" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F174" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G174" t="s">
-        <v>657</v>
+        <v>130</v>
       </c>
       <c r="H174" t="s">
         <v>658</v>
@@ -7379,27 +7379,56 @@
         <v>182</v>
       </c>
       <c r="B175" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C175" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D175" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E175" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="F175" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G175" t="s">
-        <v>115</v>
+        <v>657</v>
       </c>
       <c r="H175" t="s">
         <v>658</v>
       </c>
       <c r="I175" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
+      <c r="A176" t="s">
+        <v>183</v>
+      </c>
+      <c r="B176" t="s">
+        <v>358</v>
+      </c>
+      <c r="C176" t="s">
+        <v>444</v>
+      </c>
+      <c r="D176" t="s">
+        <v>445</v>
+      </c>
+      <c r="E176" t="s">
+        <v>474</v>
+      </c>
+      <c r="F176" t="s">
+        <v>513</v>
+      </c>
+      <c r="G176" t="s">
+        <v>116</v>
+      </c>
+      <c r="H176" t="s">
+        <v>658</v>
+      </c>
+      <c r="I176" t="s">
         <v>659</v>
       </c>
     </row>

--- a/data/BioTecnos.xlsx
+++ b/data/BioTecnos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="678">
   <si>
     <t>ID</t>
   </si>
@@ -43,6 +43,15 @@
     <t>Estado</t>
   </si>
   <si>
+    <t>904</t>
+  </si>
+  <si>
+    <t>903</t>
+  </si>
+  <si>
+    <t>902</t>
+  </si>
+  <si>
     <t>901</t>
   </si>
   <si>
@@ -58,12 +67,18 @@
     <t>897</t>
   </si>
   <si>
+    <t>895</t>
+  </si>
+  <si>
     <t>893</t>
   </si>
   <si>
     <t>892</t>
   </si>
   <si>
+    <t>891</t>
+  </si>
+  <si>
     <t>890</t>
   </si>
   <si>
@@ -568,6 +583,15 @@
     <t>711</t>
   </si>
   <si>
+    <t>M02N042LB5601</t>
+  </si>
+  <si>
+    <t>M02N042LA5601</t>
+  </si>
+  <si>
+    <t>M02N042LC5601</t>
+  </si>
+  <si>
     <t>M02T118LB5601</t>
   </si>
   <si>
@@ -583,12 +607,18 @@
     <t>M02T118LA5601</t>
   </si>
   <si>
+    <t>M02Q048L33604</t>
+  </si>
+  <si>
     <t>M02Q047L24606</t>
   </si>
   <si>
     <t>M02Q047LA5602</t>
   </si>
   <si>
+    <t>M02Q047L24605</t>
+  </si>
+  <si>
     <t>M02M039L20603</t>
   </si>
   <si>
@@ -1093,12 +1123,24 @@
     <t>M02Q048L33504</t>
   </si>
   <si>
+    <t>10-04-2026</t>
+  </si>
+  <si>
+    <t>09-04-2026</t>
+  </si>
+  <si>
     <t>06-04-2026</t>
   </si>
   <si>
+    <t>07-04-2026</t>
+  </si>
+  <si>
     <t>02-04-2026</t>
   </si>
   <si>
+    <t>31-03-2026</t>
+  </si>
+  <si>
     <t>24-03-2026</t>
   </si>
   <si>
@@ -1360,6 +1402,15 @@
     <t>Cerezo</t>
   </si>
   <si>
+    <t>02N042LB5</t>
+  </si>
+  <si>
+    <t>02N042LA5</t>
+  </si>
+  <si>
+    <t>02N042LC5</t>
+  </si>
+  <si>
     <t>02T118LB5</t>
   </si>
   <si>
@@ -1375,6 +1426,9 @@
     <t>02T118LA5</t>
   </si>
   <si>
+    <t>02Q048L33</t>
+  </si>
+  <si>
     <t>02Q047L24</t>
   </si>
   <si>
@@ -1438,9 +1492,6 @@
     <t>02U043L42</t>
   </si>
   <si>
-    <t>02Q048L33</t>
-  </si>
-  <si>
     <t>02Q047L14</t>
   </si>
   <si>
@@ -1558,6 +1609,12 @@
     <t>NO LMC ( 100% )</t>
   </si>
   <si>
+    <t>656</t>
+  </si>
+  <si>
+    <t>2.168</t>
+  </si>
+  <si>
     <t>92</t>
   </si>
   <si>
@@ -1573,12 +1630,18 @@
     <t>56</t>
   </si>
   <si>
+    <t>18.408</t>
+  </si>
+  <si>
     <t>7.656</t>
   </si>
   <si>
     <t>960</t>
   </si>
   <si>
+    <t>30.840</t>
+  </si>
+  <si>
     <t>12.000</t>
   </si>
   <si>
@@ -1633,13 +1696,10 @@
     <t>500</t>
   </si>
   <si>
-    <t>1.536</t>
-  </si>
-  <si>
-    <t>792</t>
-  </si>
-  <si>
-    <t>1.432</t>
+    <t>1.523</t>
+  </si>
+  <si>
+    <t>1.424</t>
   </si>
   <si>
     <t>24.120</t>
@@ -1765,7 +1825,7 @@
     <t>64.800</t>
   </si>
   <si>
-    <t>53.624</t>
+    <t>54.862</t>
   </si>
   <si>
     <t>207</t>
@@ -1900,16 +1960,10 @@
     <t>5.194</t>
   </si>
   <si>
-    <t>12.226</t>
-  </si>
-  <si>
     <t>39.996</t>
   </si>
   <si>
     <t>11.368</t>
-  </si>
-  <si>
-    <t>3.875</t>
   </si>
   <si>
     <t>394</t>
@@ -2325,7 +2379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I176"/>
+  <dimension ref="A1:I181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2362,28 +2416,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C2" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="D2" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E2" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="F2" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G2" t="s">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="H2" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I2" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2391,28 +2445,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C3" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="D3" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E3" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="F3" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G3" t="s">
-        <v>515</v>
+        <v>63</v>
       </c>
       <c r="H3" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I3" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2420,28 +2474,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C4" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="D4" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E4" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="F4" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G4" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="H4" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I4" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2449,28 +2503,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D5" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E5" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="F5" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G5" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="H5" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I5" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2478,28 +2532,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C6" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D6" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E6" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="F6" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G6" t="s">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="H6" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I6" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2507,28 +2561,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C7" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D7" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E7" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="F7" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G7" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="H7" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I7" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2536,28 +2590,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C8" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="D8" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E8" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="F8" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G8" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="H8" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I8" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2565,28 +2619,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C9" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="D9" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E9" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="F9" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G9" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="H9" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I9" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2594,28 +2648,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C10" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="D10" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E10" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="F10" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G10" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="H10" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I10" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2623,28 +2677,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C11" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="D11" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E11" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="F11" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G11" t="s">
-        <v>147</v>
+        <v>539</v>
       </c>
       <c r="H11" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I11" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2652,28 +2706,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C12" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="D12" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E12" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="F12" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G12" t="s">
-        <v>523</v>
+        <v>540</v>
       </c>
       <c r="H12" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I12" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2681,28 +2735,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C13" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="D13" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E13" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="F13" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G13" t="s">
-        <v>524</v>
+        <v>541</v>
       </c>
       <c r="H13" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I13" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2710,28 +2764,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C14" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="D14" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E14" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="F14" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G14" t="s">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="H14" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I14" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2739,28 +2793,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C15" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="D15" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E15" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="F15" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G15" t="s">
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="H15" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I15" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2768,28 +2822,28 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C16" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="D16" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E16" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="F16" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G16" t="s">
-        <v>527</v>
+        <v>152</v>
       </c>
       <c r="H16" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I16" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -2797,28 +2851,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C17" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="D17" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E17" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="F17" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G17" t="s">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="H17" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I17" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2826,28 +2880,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C18" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="D18" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E18" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="F18" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G18" t="s">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="H18" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I18" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -2855,28 +2909,28 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C19" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="D19" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="E19" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="F19" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G19" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="H19" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I19" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2884,28 +2938,28 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C20" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="D20" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="E20" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="F20" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G20" t="s">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="H20" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I20" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -2913,28 +2967,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C21" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="D21" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="E21" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="F21" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G21" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H21" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I21" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -2942,28 +2996,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C22" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="D22" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="E22" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="F22" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G22" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
       <c r="H22" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I22" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -2971,28 +3025,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C23" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="D23" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="E23" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="F23" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G23" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="H23" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I23" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -3000,28 +3054,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C24" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="D24" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="E24" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="F24" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G24" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
       <c r="H24" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I24" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -3029,28 +3083,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C25" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="D25" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="E25" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="F25" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G25" t="s">
-        <v>536</v>
+        <v>552</v>
       </c>
       <c r="H25" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I25" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -3058,28 +3112,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C26" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="D26" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="E26" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="F26" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G26" t="s">
-        <v>537</v>
+        <v>553</v>
       </c>
       <c r="H26" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I26" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -3087,28 +3141,28 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C27" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="D27" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="E27" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="F27" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G27" t="s">
-        <v>538</v>
+        <v>554</v>
       </c>
       <c r="H27" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I27" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -3116,28 +3170,28 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C28" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="D28" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="E28" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="F28" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G28" t="s">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="H28" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I28" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -3145,28 +3199,28 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C29" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D29" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="E29" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="F29" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G29" t="s">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="H29" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I29" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -3174,28 +3228,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C30" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D30" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="E30" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="F30" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G30" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="H30" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I30" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -3203,28 +3257,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C31" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="D31" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="E31" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="F31" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G31" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
       <c r="H31" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I31" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -3232,28 +3286,28 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C32" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="D32" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="E32" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="F32" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G32" t="s">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="H32" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I32" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -3261,28 +3315,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C33" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="D33" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E33" t="s">
-        <v>453</v>
+        <v>489</v>
       </c>
       <c r="F33" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G33" t="s">
-        <v>544</v>
+        <v>560</v>
       </c>
       <c r="H33" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I33" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -3290,28 +3344,28 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C34" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="D34" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E34" t="s">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="F34" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G34" t="s">
-        <v>545</v>
+        <v>116</v>
       </c>
       <c r="H34" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I34" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -3319,28 +3373,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C35" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="D35" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E35" t="s">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="F35" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G35" t="s">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="H35" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I35" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -3348,28 +3402,28 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C36" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D36" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E36" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="F36" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G36" t="s">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="H36" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I36" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -3377,28 +3431,28 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C37" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="D37" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E37" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="F37" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G37" t="s">
-        <v>548</v>
+        <v>563</v>
       </c>
       <c r="H37" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I37" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -3406,28 +3460,28 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C38" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="D38" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E38" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="F38" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G38" t="s">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="H38" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I38" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -3435,28 +3489,28 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C39" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D39" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E39" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="F39" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G39" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="H39" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I39" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -3464,28 +3518,28 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C40" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D40" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="E40" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="F40" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G40" t="s">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="H40" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I40" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -3493,28 +3547,28 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C41" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="D41" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="E41" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="F41" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G41" t="s">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="H41" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I41" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -3522,28 +3576,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C42" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="D42" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="E42" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="F42" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G42" t="s">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="H42" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I42" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -3551,28 +3605,28 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C43" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="D43" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="E43" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="F43" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G43" t="s">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="H43" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I43" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -3580,28 +3634,28 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C44" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="D44" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E44" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="F44" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G44" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="H44" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I44" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -3609,28 +3663,28 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C45" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="D45" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E45" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="F45" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G45" t="s">
-        <v>556</v>
+        <v>571</v>
       </c>
       <c r="H45" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I45" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -3638,28 +3692,28 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C46" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="D46" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E46" t="s">
-        <v>474</v>
+        <v>499</v>
       </c>
       <c r="F46" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G46" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="H46" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I46" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -3667,28 +3721,28 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C47" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="D47" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E47" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="F47" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G47" t="s">
-        <v>558</v>
+        <v>573</v>
       </c>
       <c r="H47" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I47" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -3696,28 +3750,28 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C48" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="D48" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E48" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="F48" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G48" t="s">
-        <v>559</v>
+        <v>574</v>
       </c>
       <c r="H48" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I48" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -3725,28 +3779,28 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C49" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="D49" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E49" t="s">
-        <v>455</v>
+        <v>502</v>
       </c>
       <c r="F49" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G49" t="s">
-        <v>142</v>
+        <v>575</v>
       </c>
       <c r="H49" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I49" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -3754,28 +3808,28 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C50" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="D50" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E50" t="s">
-        <v>457</v>
+        <v>503</v>
       </c>
       <c r="F50" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G50" t="s">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="H50" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I50" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -3783,28 +3837,28 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C51" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="D51" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E51" t="s">
-        <v>487</v>
+        <v>470</v>
       </c>
       <c r="F51" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G51" t="s">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="H51" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I51" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -3812,28 +3866,28 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C52" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="D52" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E52" t="s">
-        <v>457</v>
+        <v>504</v>
       </c>
       <c r="F52" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G52" t="s">
-        <v>562</v>
+        <v>578</v>
       </c>
       <c r="H52" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I52" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -3841,28 +3895,28 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C53" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="D53" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E53" t="s">
-        <v>456</v>
+        <v>505</v>
       </c>
       <c r="F53" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G53" t="s">
-        <v>176</v>
+        <v>579</v>
       </c>
       <c r="H53" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I53" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -3870,28 +3924,28 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C54" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="D54" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E54" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="F54" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G54" t="s">
-        <v>563</v>
+        <v>147</v>
       </c>
       <c r="H54" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I54" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -3899,28 +3953,28 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C55" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="D55" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E55" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="F55" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G55" t="s">
-        <v>564</v>
+        <v>580</v>
       </c>
       <c r="H55" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I55" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -3928,28 +3982,28 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C56" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="D56" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E56" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="F56" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G56" t="s">
-        <v>565</v>
+        <v>581</v>
       </c>
       <c r="H56" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I56" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -3957,28 +4011,28 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C57" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="D57" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E57" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="F57" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G57" t="s">
-        <v>566</v>
+        <v>582</v>
       </c>
       <c r="H57" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I57" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -3986,28 +4040,28 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C58" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="D58" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E58" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="F58" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G58" t="s">
-        <v>567</v>
+        <v>181</v>
       </c>
       <c r="H58" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I58" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -4015,28 +4069,28 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C59" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D59" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E59" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="F59" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G59" t="s">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="H59" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I59" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -4044,28 +4098,28 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C60" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="D60" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E60" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="F60" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G60" t="s">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="H60" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I60" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -4073,28 +4127,28 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C61" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="D61" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E61" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="F61" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G61" t="s">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="H61" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I61" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -4102,28 +4156,28 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C62" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="D62" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E62" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="F62" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G62" t="s">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="H62" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I62" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -4131,28 +4185,28 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C63" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="D63" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E63" t="s">
-        <v>493</v>
+        <v>473</v>
       </c>
       <c r="F63" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G63" t="s">
-        <v>572</v>
+        <v>587</v>
       </c>
       <c r="H63" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I63" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -4160,28 +4214,28 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C64" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="D64" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="E64" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="F64" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G64" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="H64" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I64" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -4189,28 +4243,28 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C65" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="D65" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E65" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F65" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G65" t="s">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="H65" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I65" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -4218,28 +4272,28 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C66" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="D66" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E66" t="s">
-        <v>475</v>
+        <v>509</v>
       </c>
       <c r="F66" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G66" t="s">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="H66" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I66" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -4247,28 +4301,28 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C67" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="D67" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E67" t="s">
-        <v>454</v>
+        <v>509</v>
       </c>
       <c r="F67" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G67" t="s">
-        <v>576</v>
+        <v>591</v>
       </c>
       <c r="H67" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I67" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -4276,28 +4330,28 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C68" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="D68" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E68" t="s">
-        <v>453</v>
+        <v>510</v>
       </c>
       <c r="F68" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G68" t="s">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="H68" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I68" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -4305,28 +4359,28 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C69" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D69" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="E69" t="s">
-        <v>469</v>
+        <v>511</v>
       </c>
       <c r="F69" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G69" t="s">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="H69" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I69" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -4334,28 +4388,28 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C70" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="D70" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="E70" t="s">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="F70" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G70" t="s">
-        <v>579</v>
+        <v>594</v>
       </c>
       <c r="H70" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I70" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -4363,28 +4417,28 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C71" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="D71" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E71" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="F71" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G71" t="s">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="H71" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I71" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -4392,28 +4446,28 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C72" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="D72" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E72" t="s">
-        <v>497</v>
+        <v>472</v>
       </c>
       <c r="F72" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G72" t="s">
-        <v>581</v>
+        <v>596</v>
       </c>
       <c r="H72" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I72" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -4421,28 +4475,28 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C73" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="D73" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E73" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F73" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G73" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="H73" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I73" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -4450,28 +4504,28 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C74" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="D74" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="E74" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="F74" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G74" t="s">
-        <v>583</v>
+        <v>598</v>
       </c>
       <c r="H74" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I74" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -4479,28 +4533,28 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="D75" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="E75" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="F75" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G75" t="s">
-        <v>584</v>
+        <v>599</v>
       </c>
       <c r="H75" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I75" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -4508,28 +4562,28 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C76" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="D76" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="E76" t="s">
-        <v>496</v>
+        <v>513</v>
       </c>
       <c r="F76" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G76" t="s">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="H76" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I76" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -4537,28 +4591,28 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C77" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="D77" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E77" t="s">
-        <v>469</v>
+        <v>514</v>
       </c>
       <c r="F77" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G77" t="s">
-        <v>585</v>
+        <v>601</v>
       </c>
       <c r="H77" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I77" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -4566,28 +4620,28 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C78" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="D78" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E78" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="F78" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G78" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="H78" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I78" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -4595,28 +4649,28 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C79" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="D79" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="E79" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F79" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G79" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="H79" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I79" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -4624,28 +4678,28 @@
         <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C80" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="D80" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="E80" t="s">
-        <v>494</v>
+        <v>511</v>
       </c>
       <c r="F80" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G80" t="s">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="H80" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I80" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -4653,28 +4707,28 @@
         <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C81" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="D81" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="E81" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="F81" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G81" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="H81" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I81" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -4682,28 +4736,28 @@
         <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C82" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D82" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="E82" t="s">
-        <v>454</v>
+        <v>487</v>
       </c>
       <c r="F82" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G82" t="s">
-        <v>575</v>
+        <v>605</v>
       </c>
       <c r="H82" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I82" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -4711,28 +4765,28 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C83" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="D83" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E83" t="s">
-        <v>453</v>
+        <v>499</v>
       </c>
       <c r="F83" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G83" t="s">
-        <v>575</v>
+        <v>606</v>
       </c>
       <c r="H83" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I83" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -4740,28 +4794,28 @@
         <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C84" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="D84" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E84" t="s">
-        <v>474</v>
+        <v>499</v>
       </c>
       <c r="F84" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G84" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="H84" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I84" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -4769,28 +4823,28 @@
         <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C85" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D85" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="E85" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="F85" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G85" t="s">
-        <v>571</v>
+        <v>607</v>
       </c>
       <c r="H85" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I85" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -4798,28 +4852,28 @@
         <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C86" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="D86" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E86" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="F86" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G86" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="H86" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I86" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -4827,28 +4881,28 @@
         <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C87" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="D87" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E87" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="F87" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G87" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="H87" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I87" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -4856,28 +4910,28 @@
         <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C88" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="D88" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E88" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="F88" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G88" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="H88" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I88" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -4885,28 +4939,28 @@
         <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C89" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="D89" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E89" t="s">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="F89" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G89" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="H89" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I89" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -4914,28 +4968,28 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C90" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="D90" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E90" t="s">
-        <v>454</v>
+        <v>514</v>
       </c>
       <c r="F90" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G90" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="H90" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I90" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -4943,28 +4997,28 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C91" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="D91" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E91" t="s">
-        <v>486</v>
+        <v>515</v>
       </c>
       <c r="F91" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G91" t="s">
-        <v>594</v>
+        <v>609</v>
       </c>
       <c r="H91" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I91" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -4972,28 +5026,28 @@
         <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C92" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="D92" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E92" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="F92" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G92" t="s">
-        <v>595</v>
+        <v>610</v>
       </c>
       <c r="H92" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I92" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -5001,28 +5055,28 @@
         <v>100</v>
       </c>
       <c r="B93" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C93" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="D93" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E93" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="F93" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G93" t="s">
-        <v>596</v>
+        <v>611</v>
       </c>
       <c r="H93" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I93" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -5030,28 +5084,28 @@
         <v>101</v>
       </c>
       <c r="B94" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C94" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="D94" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E94" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F94" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G94" t="s">
-        <v>597</v>
+        <v>612</v>
       </c>
       <c r="H94" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I94" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -5059,28 +5113,28 @@
         <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C95" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="D95" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E95" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F95" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G95" t="s">
-        <v>598</v>
+        <v>613</v>
       </c>
       <c r="H95" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I95" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -5088,28 +5142,28 @@
         <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C96" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D96" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E96" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="F96" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G96" t="s">
-        <v>599</v>
+        <v>614</v>
       </c>
       <c r="H96" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I96" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -5117,28 +5171,28 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C97" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="D97" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E97" t="s">
-        <v>457</v>
+        <v>499</v>
       </c>
       <c r="F97" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G97" t="s">
-        <v>529</v>
+        <v>615</v>
       </c>
       <c r="H97" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I97" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -5146,28 +5200,28 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C98" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="D98" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E98" t="s">
-        <v>456</v>
+        <v>500</v>
       </c>
       <c r="F98" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G98" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
       <c r="H98" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I98" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -5175,28 +5229,28 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C99" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="D99" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E99" t="s">
-        <v>499</v>
+        <v>470</v>
       </c>
       <c r="F99" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G99" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
       <c r="H99" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I99" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -5204,28 +5258,28 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C100" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="D100" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E100" t="s">
-        <v>491</v>
+        <v>470</v>
       </c>
       <c r="F100" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G100" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="H100" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I100" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -5233,28 +5287,28 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C101" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="D101" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E101" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="F101" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G101" t="s">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="H101" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I101" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -5262,28 +5316,28 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C102" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="D102" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E102" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="F102" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G102" t="s">
-        <v>604</v>
+        <v>550</v>
       </c>
       <c r="H102" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I102" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -5291,28 +5345,28 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C103" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="D103" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E103" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="F103" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G103" t="s">
-        <v>605</v>
+        <v>620</v>
       </c>
       <c r="H103" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I103" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -5320,28 +5374,28 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C104" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="D104" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E104" t="s">
-        <v>482</v>
+        <v>516</v>
       </c>
       <c r="F104" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G104" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
       <c r="H104" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I104" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -5349,28 +5403,28 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C105" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="D105" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E105" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="F105" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G105" t="s">
-        <v>88</v>
+        <v>622</v>
       </c>
       <c r="H105" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I105" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -5378,28 +5432,28 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C106" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="D106" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E106" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F106" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G106" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="H106" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I106" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -5407,28 +5461,28 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C107" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="D107" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E107" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="F107" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G107" t="s">
-        <v>550</v>
+        <v>624</v>
       </c>
       <c r="H107" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I107" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -5436,28 +5490,28 @@
         <v>115</v>
       </c>
       <c r="B108" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C108" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="D108" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E108" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="F108" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G108" t="s">
-        <v>543</v>
+        <v>625</v>
       </c>
       <c r="H108" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I108" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -5465,28 +5519,28 @@
         <v>116</v>
       </c>
       <c r="B109" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C109" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="D109" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E109" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="F109" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G109" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="H109" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I109" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -5494,28 +5548,28 @@
         <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C110" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="D110" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E110" t="s">
-        <v>483</v>
+        <v>509</v>
       </c>
       <c r="F110" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G110" t="s">
-        <v>609</v>
+        <v>93</v>
       </c>
       <c r="H110" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I110" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -5523,28 +5577,28 @@
         <v>118</v>
       </c>
       <c r="B111" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C111" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="D111" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E111" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="F111" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G111" t="s">
-        <v>610</v>
+        <v>627</v>
       </c>
       <c r="H111" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I111" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -5552,28 +5606,28 @@
         <v>119</v>
       </c>
       <c r="B112" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C112" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="D112" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E112" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="F112" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G112" t="s">
-        <v>611</v>
+        <v>570</v>
       </c>
       <c r="H112" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I112" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -5581,28 +5635,28 @@
         <v>120</v>
       </c>
       <c r="B113" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C113" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="D113" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E113" t="s">
-        <v>454</v>
+        <v>502</v>
       </c>
       <c r="F113" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G113" t="s">
-        <v>612</v>
+        <v>563</v>
       </c>
       <c r="H113" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I113" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -5610,28 +5664,28 @@
         <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C114" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="D114" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E114" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F114" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G114" t="s">
-        <v>613</v>
+        <v>628</v>
       </c>
       <c r="H114" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I114" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -5639,28 +5693,28 @@
         <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C115" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="D115" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E115" t="s">
-        <v>453</v>
+        <v>500</v>
       </c>
       <c r="F115" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G115" t="s">
-        <v>614</v>
+        <v>629</v>
       </c>
       <c r="H115" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I115" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -5668,28 +5722,28 @@
         <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C116" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="D116" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E116" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F116" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G116" t="s">
-        <v>615</v>
+        <v>630</v>
       </c>
       <c r="H116" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I116" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -5697,28 +5751,28 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C117" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="D117" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E117" t="s">
-        <v>502</v>
+        <v>471</v>
       </c>
       <c r="F117" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G117" t="s">
-        <v>616</v>
+        <v>631</v>
       </c>
       <c r="H117" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I117" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -5726,28 +5780,28 @@
         <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C118" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="D118" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E118" t="s">
-        <v>503</v>
+        <v>472</v>
       </c>
       <c r="F118" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G118" t="s">
-        <v>617</v>
+        <v>632</v>
       </c>
       <c r="H118" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I118" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -5755,28 +5809,28 @@
         <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C119" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="D119" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E119" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="F119" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G119" t="s">
-        <v>618</v>
+        <v>633</v>
       </c>
       <c r="H119" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I119" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -5784,28 +5838,28 @@
         <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C120" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="D120" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E120" t="s">
-        <v>505</v>
+        <v>471</v>
       </c>
       <c r="F120" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G120" t="s">
-        <v>619</v>
+        <v>634</v>
       </c>
       <c r="H120" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I120" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -5813,28 +5867,28 @@
         <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C121" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="D121" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E121" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="F121" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G121" t="s">
-        <v>620</v>
+        <v>635</v>
       </c>
       <c r="H121" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I121" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -5842,28 +5896,28 @@
         <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C122" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="D122" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E122" t="s">
-        <v>483</v>
+        <v>519</v>
       </c>
       <c r="F122" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G122" t="s">
-        <v>621</v>
+        <v>636</v>
       </c>
       <c r="H122" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I122" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -5871,28 +5925,28 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C123" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="D123" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E123" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="F123" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G123" t="s">
-        <v>622</v>
+        <v>637</v>
       </c>
       <c r="H123" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I123" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -5900,28 +5954,28 @@
         <v>131</v>
       </c>
       <c r="B124" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C124" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="D124" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E124" t="s">
-        <v>474</v>
+        <v>521</v>
       </c>
       <c r="F124" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G124" t="s">
-        <v>623</v>
+        <v>638</v>
       </c>
       <c r="H124" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I124" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -5929,28 +5983,28 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C125" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="D125" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E125" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="F125" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G125" t="s">
-        <v>624</v>
+        <v>639</v>
       </c>
       <c r="H125" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I125" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -5958,28 +6012,28 @@
         <v>133</v>
       </c>
       <c r="B126" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C126" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="D126" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E126" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="F126" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G126" t="s">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="H126" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I126" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -5987,28 +6041,28 @@
         <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C127" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="D127" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E127" t="s">
         <v>500</v>
       </c>
       <c r="F127" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G127" t="s">
-        <v>515</v>
+        <v>641</v>
       </c>
       <c r="H127" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I127" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -6016,28 +6070,28 @@
         <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C128" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="D128" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E128" t="s">
-        <v>453</v>
+        <v>524</v>
       </c>
       <c r="F128" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G128" t="s">
-        <v>575</v>
+        <v>642</v>
       </c>
       <c r="H128" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I128" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -6045,28 +6099,28 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C129" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="D129" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E129" t="s">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="F129" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G129" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
       <c r="H129" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I129" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -6074,28 +6128,28 @@
         <v>137</v>
       </c>
       <c r="B130" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C130" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="D130" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E130" t="s">
-        <v>475</v>
+        <v>525</v>
       </c>
       <c r="F130" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G130" t="s">
-        <v>575</v>
+        <v>644</v>
       </c>
       <c r="H130" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I130" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -6103,28 +6157,28 @@
         <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C131" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="D131" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E131" t="s">
-        <v>474</v>
+        <v>526</v>
       </c>
       <c r="F131" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G131" t="s">
-        <v>627</v>
+        <v>645</v>
       </c>
       <c r="H131" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I131" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -6132,28 +6186,28 @@
         <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C132" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="D132" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E132" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="F132" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G132" t="s">
-        <v>628</v>
+        <v>534</v>
       </c>
       <c r="H132" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I132" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -6161,28 +6215,28 @@
         <v>140</v>
       </c>
       <c r="B133" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C133" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="D133" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E133" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="F133" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G133" t="s">
-        <v>127</v>
+        <v>595</v>
       </c>
       <c r="H133" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I133" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -6190,28 +6244,28 @@
         <v>141</v>
       </c>
       <c r="B134" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C134" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="D134" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E134" t="s">
-        <v>501</v>
+        <v>471</v>
       </c>
       <c r="F134" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G134" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="H134" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I134" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -6219,28 +6273,28 @@
         <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C135" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="D135" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E135" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="F135" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G135" t="s">
-        <v>630</v>
+        <v>595</v>
       </c>
       <c r="H135" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I135" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -6248,28 +6302,28 @@
         <v>143</v>
       </c>
       <c r="B136" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C136" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="D136" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E136" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="F136" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G136" t="s">
-        <v>631</v>
+        <v>647</v>
       </c>
       <c r="H136" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I136" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -6277,28 +6331,28 @@
         <v>144</v>
       </c>
       <c r="B137" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C137" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="D137" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E137" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="F137" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G137" t="s">
-        <v>632</v>
+        <v>595</v>
       </c>
       <c r="H137" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I137" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -6306,28 +6360,28 @@
         <v>145</v>
       </c>
       <c r="B138" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C138" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="D138" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E138" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="F138" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G138" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="H138" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I138" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -6335,28 +6389,28 @@
         <v>146</v>
       </c>
       <c r="B139" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C139" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="D139" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E139" t="s">
-        <v>453</v>
+        <v>518</v>
       </c>
       <c r="F139" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G139" t="s">
-        <v>633</v>
+        <v>648</v>
       </c>
       <c r="H139" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I139" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -6364,28 +6418,28 @@
         <v>147</v>
       </c>
       <c r="B140" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C140" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="D140" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E140" t="s">
-        <v>455</v>
+        <v>499</v>
       </c>
       <c r="F140" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G140" t="s">
-        <v>634</v>
+        <v>649</v>
       </c>
       <c r="H140" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I140" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -6393,28 +6447,28 @@
         <v>148</v>
       </c>
       <c r="B141" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C141" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="D141" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E141" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="F141" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G141" t="s">
-        <v>635</v>
+        <v>595</v>
       </c>
       <c r="H141" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I141" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -6422,28 +6476,28 @@
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C142" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="D142" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E142" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="F142" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G142" t="s">
-        <v>636</v>
+        <v>650</v>
       </c>
       <c r="H142" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I142" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -6451,28 +6505,28 @@
         <v>150</v>
       </c>
       <c r="B143" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C143" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="D143" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E143" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="F143" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G143" t="s">
-        <v>533</v>
+        <v>122</v>
       </c>
       <c r="H143" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I143" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -6480,28 +6534,28 @@
         <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C144" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="D144" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E144" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="F144" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G144" t="s">
-        <v>637</v>
+        <v>651</v>
       </c>
       <c r="H144" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I144" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -6509,28 +6563,28 @@
         <v>152</v>
       </c>
       <c r="B145" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C145" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="D145" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E145" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F145" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G145" t="s">
-        <v>638</v>
+        <v>652</v>
       </c>
       <c r="H145" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I145" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -6538,28 +6592,28 @@
         <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C146" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="D146" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E146" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="F146" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G146" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="H146" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I146" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -6567,28 +6621,28 @@
         <v>154</v>
       </c>
       <c r="B147" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C147" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="D147" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E147" t="s">
-        <v>453</v>
+        <v>509</v>
       </c>
       <c r="F147" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G147" t="s">
-        <v>640</v>
+        <v>654</v>
       </c>
       <c r="H147" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I147" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -6596,28 +6650,28 @@
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C148" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="D148" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E148" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F148" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G148" t="s">
-        <v>641</v>
+        <v>554</v>
       </c>
       <c r="H148" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I148" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -6625,28 +6679,28 @@
         <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C149" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="D149" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E149" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F149" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G149" t="s">
-        <v>575</v>
+        <v>655</v>
       </c>
       <c r="H149" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I149" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -6654,28 +6708,28 @@
         <v>157</v>
       </c>
       <c r="B150" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C150" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="D150" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E150" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="F150" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G150" t="s">
-        <v>575</v>
+        <v>656</v>
       </c>
       <c r="H150" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I150" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -6683,28 +6737,28 @@
         <v>158</v>
       </c>
       <c r="B151" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C151" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="D151" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E151" t="s">
-        <v>475</v>
+        <v>517</v>
       </c>
       <c r="F151" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G151" t="s">
-        <v>642</v>
+        <v>657</v>
       </c>
       <c r="H151" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I151" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -6712,28 +6766,28 @@
         <v>159</v>
       </c>
       <c r="B152" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C152" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="D152" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="E152" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="F152" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G152" t="s">
-        <v>111</v>
+        <v>658</v>
       </c>
       <c r="H152" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I152" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -6741,28 +6795,28 @@
         <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C153" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="D153" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E153" t="s">
-        <v>491</v>
+        <v>514</v>
       </c>
       <c r="F153" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G153" t="s">
-        <v>643</v>
+        <v>659</v>
       </c>
       <c r="H153" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I153" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -6770,28 +6824,28 @@
         <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C154" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="D154" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E154" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="F154" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G154" t="s">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="H154" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I154" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -6799,28 +6853,28 @@
         <v>162</v>
       </c>
       <c r="B155" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C155" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="D155" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E155" t="s">
-        <v>497</v>
+        <v>470</v>
       </c>
       <c r="F155" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G155" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="H155" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I155" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -6828,28 +6882,28 @@
         <v>163</v>
       </c>
       <c r="B156" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C156" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="D156" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E156" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="F156" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G156" t="s">
-        <v>575</v>
+        <v>660</v>
       </c>
       <c r="H156" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I156" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -6857,28 +6911,28 @@
         <v>164</v>
       </c>
       <c r="B157" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C157" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="D157" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="E157" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="F157" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G157" t="s">
-        <v>645</v>
+        <v>116</v>
       </c>
       <c r="H157" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I157" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -6886,28 +6940,28 @@
         <v>165</v>
       </c>
       <c r="B158" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C158" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="D158" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E158" t="s">
-        <v>474</v>
+        <v>508</v>
       </c>
       <c r="F158" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G158" t="s">
-        <v>575</v>
+        <v>661</v>
       </c>
       <c r="H158" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I158" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -6915,28 +6969,28 @@
         <v>166</v>
       </c>
       <c r="B159" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C159" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="D159" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E159" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F159" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G159" t="s">
-        <v>575</v>
+        <v>662</v>
       </c>
       <c r="H159" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I159" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -6944,28 +6998,28 @@
         <v>167</v>
       </c>
       <c r="B160" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C160" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="D160" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E160" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F160" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G160" t="s">
-        <v>646</v>
+        <v>595</v>
       </c>
       <c r="H160" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I160" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -6973,28 +7027,28 @@
         <v>168</v>
       </c>
       <c r="B161" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C161" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="D161" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E161" t="s">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="F161" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G161" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="H161" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I161" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -7002,28 +7056,28 @@
         <v>169</v>
       </c>
       <c r="B162" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C162" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="D162" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E162" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="F162" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G162" t="s">
-        <v>647</v>
+        <v>663</v>
       </c>
       <c r="H162" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I162" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -7031,28 +7085,28 @@
         <v>170</v>
       </c>
       <c r="B163" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C163" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="D163" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E163" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="F163" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G163" t="s">
-        <v>648</v>
+        <v>595</v>
       </c>
       <c r="H163" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I163" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -7060,28 +7114,28 @@
         <v>171</v>
       </c>
       <c r="B164" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C164" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="D164" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E164" t="s">
-        <v>475</v>
+        <v>514</v>
       </c>
       <c r="F164" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G164" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="H164" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I164" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -7089,28 +7143,28 @@
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C165" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="D165" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E165" t="s">
-        <v>486</v>
+        <v>527</v>
       </c>
       <c r="F165" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G165" t="s">
-        <v>649</v>
+        <v>664</v>
       </c>
       <c r="H165" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I165" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -7118,28 +7172,28 @@
         <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C166" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="D166" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E166" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="F166" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G166" t="s">
-        <v>566</v>
+        <v>595</v>
       </c>
       <c r="H166" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I166" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -7147,28 +7201,28 @@
         <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C167" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="D167" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E167" t="s">
-        <v>455</v>
+        <v>517</v>
       </c>
       <c r="F167" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G167" t="s">
-        <v>650</v>
+        <v>665</v>
       </c>
       <c r="H167" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I167" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -7176,28 +7230,28 @@
         <v>175</v>
       </c>
       <c r="B168" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C168" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="D168" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E168" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="F168" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G168" t="s">
-        <v>651</v>
+        <v>666</v>
       </c>
       <c r="H168" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I168" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -7205,28 +7259,28 @@
         <v>176</v>
       </c>
       <c r="B169" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C169" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="D169" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E169" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="F169" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G169" t="s">
-        <v>652</v>
+        <v>595</v>
       </c>
       <c r="H169" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I169" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -7234,28 +7288,28 @@
         <v>177</v>
       </c>
       <c r="B170" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C170" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="D170" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E170" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="F170" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G170" t="s">
-        <v>653</v>
+        <v>667</v>
       </c>
       <c r="H170" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I170" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -7263,28 +7317,28 @@
         <v>178</v>
       </c>
       <c r="B171" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C171" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="D171" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E171" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="F171" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G171" t="s">
-        <v>654</v>
+        <v>595</v>
       </c>
       <c r="H171" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I171" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -7292,28 +7346,28 @@
         <v>179</v>
       </c>
       <c r="B172" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C172" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="D172" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E172" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="F172" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G172" t="s">
-        <v>655</v>
+        <v>668</v>
       </c>
       <c r="H172" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I172" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -7321,28 +7375,28 @@
         <v>180</v>
       </c>
       <c r="B173" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C173" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D173" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E173" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="F173" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G173" t="s">
-        <v>656</v>
+        <v>669</v>
       </c>
       <c r="H173" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I173" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -7350,28 +7404,28 @@
         <v>181</v>
       </c>
       <c r="B174" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C174" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="D174" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E174" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="F174" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G174" t="s">
-        <v>130</v>
+        <v>670</v>
       </c>
       <c r="H174" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I174" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -7379,28 +7433,28 @@
         <v>182</v>
       </c>
       <c r="B175" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C175" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="D175" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E175" t="s">
-        <v>482</v>
+        <v>528</v>
       </c>
       <c r="F175" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G175" t="s">
-        <v>657</v>
+        <v>671</v>
       </c>
       <c r="H175" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I175" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -7408,28 +7462,173 @@
         <v>183</v>
       </c>
       <c r="B176" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C176" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="D176" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E176" t="s">
-        <v>474</v>
+        <v>529</v>
       </c>
       <c r="F176" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="G176" t="s">
-        <v>116</v>
+        <v>672</v>
       </c>
       <c r="H176" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="I176" t="s">
-        <v>659</v>
+        <v>677</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
+      <c r="A177" t="s">
+        <v>184</v>
+      </c>
+      <c r="B177" t="s">
+        <v>364</v>
+      </c>
+      <c r="C177" t="s">
+        <v>455</v>
+      </c>
+      <c r="D177" t="s">
+        <v>459</v>
+      </c>
+      <c r="E177" t="s">
+        <v>504</v>
+      </c>
+      <c r="F177" t="s">
+        <v>530</v>
+      </c>
+      <c r="G177" t="s">
+        <v>673</v>
+      </c>
+      <c r="H177" t="s">
+        <v>676</v>
+      </c>
+      <c r="I177" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
+      <c r="A178" t="s">
+        <v>185</v>
+      </c>
+      <c r="B178" t="s">
+        <v>365</v>
+      </c>
+      <c r="C178" t="s">
+        <v>456</v>
+      </c>
+      <c r="D178" t="s">
+        <v>459</v>
+      </c>
+      <c r="E178" t="s">
+        <v>475</v>
+      </c>
+      <c r="F178" t="s">
+        <v>530</v>
+      </c>
+      <c r="G178" t="s">
+        <v>674</v>
+      </c>
+      <c r="H178" t="s">
+        <v>676</v>
+      </c>
+      <c r="I178" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
+      <c r="A179" t="s">
+        <v>186</v>
+      </c>
+      <c r="B179" t="s">
+        <v>366</v>
+      </c>
+      <c r="C179" t="s">
+        <v>457</v>
+      </c>
+      <c r="D179" t="s">
+        <v>459</v>
+      </c>
+      <c r="E179" t="s">
+        <v>499</v>
+      </c>
+      <c r="F179" t="s">
+        <v>530</v>
+      </c>
+      <c r="G179" t="s">
+        <v>135</v>
+      </c>
+      <c r="H179" t="s">
+        <v>676</v>
+      </c>
+      <c r="I179" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
+      <c r="A180" t="s">
+        <v>187</v>
+      </c>
+      <c r="B180" t="s">
+        <v>367</v>
+      </c>
+      <c r="C180" t="s">
+        <v>457</v>
+      </c>
+      <c r="D180" t="s">
+        <v>459</v>
+      </c>
+      <c r="E180" t="s">
+        <v>499</v>
+      </c>
+      <c r="F180" t="s">
+        <v>530</v>
+      </c>
+      <c r="G180" t="s">
+        <v>675</v>
+      </c>
+      <c r="H180" t="s">
+        <v>676</v>
+      </c>
+      <c r="I180" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
+      <c r="A181" t="s">
+        <v>188</v>
+      </c>
+      <c r="B181" t="s">
+        <v>368</v>
+      </c>
+      <c r="C181" t="s">
+        <v>458</v>
+      </c>
+      <c r="D181" t="s">
+        <v>459</v>
+      </c>
+      <c r="E181" t="s">
+        <v>470</v>
+      </c>
+      <c r="F181" t="s">
+        <v>530</v>
+      </c>
+      <c r="G181" t="s">
+        <v>121</v>
+      </c>
+      <c r="H181" t="s">
+        <v>676</v>
+      </c>
+      <c r="I181" t="s">
+        <v>677</v>
       </c>
     </row>
   </sheetData>

--- a/data/BioTecnos.xlsx
+++ b/data/BioTecnos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="670">
   <si>
     <t>ID</t>
   </si>
@@ -43,6 +43,12 @@
     <t>Estado</t>
   </si>
   <si>
+    <t>907</t>
+  </si>
+  <si>
+    <t>906</t>
+  </si>
+  <si>
     <t>904</t>
   </si>
   <si>
@@ -571,16 +577,10 @@
     <t>717</t>
   </si>
   <si>
-    <t>716</t>
-  </si>
-  <si>
-    <t>714</t>
-  </si>
-  <si>
-    <t>713</t>
-  </si>
-  <si>
-    <t>711</t>
+    <t>M02T106L03603</t>
+  </si>
+  <si>
+    <t>M02L008L11603</t>
   </si>
   <si>
     <t>M02N042LB5601</t>
@@ -1111,16 +1111,7 @@
     <t>M02T106L03504</t>
   </si>
   <si>
-    <t>M02T105L03505</t>
-  </si>
-  <si>
-    <t>M02Q050L01517</t>
-  </si>
-  <si>
-    <t>M02Q050L01516</t>
-  </si>
-  <si>
-    <t>M02Q048L33504</t>
+    <t>16-04-2026</t>
   </si>
   <si>
     <t>10-04-2026</t>
@@ -1384,15 +1375,6 @@
     <t>21-08-2025</t>
   </si>
   <si>
-    <t>20-08-2025</t>
-  </si>
-  <si>
-    <t>19-08-2025</t>
-  </si>
-  <si>
-    <t>18-08-2025</t>
-  </si>
-  <si>
     <t>Arándano</t>
   </si>
   <si>
@@ -1402,6 +1384,12 @@
     <t>Cerezo</t>
   </si>
   <si>
+    <t>02T106L03</t>
+  </si>
+  <si>
+    <t>02L008L11</t>
+  </si>
+  <si>
     <t>02N042LB5</t>
   </si>
   <si>
@@ -1438,9 +1426,6 @@
     <t>02M039L20</t>
   </si>
   <si>
-    <t>02L008L11</t>
-  </si>
-  <si>
     <t>02T105L03</t>
   </si>
   <si>
@@ -1528,9 +1513,6 @@
     <t>02Q068L01</t>
   </si>
   <si>
-    <t>02T106L03</t>
-  </si>
-  <si>
     <t>02M039L23</t>
   </si>
   <si>
@@ -1609,6 +1591,12 @@
     <t>NO LMC ( 100% )</t>
   </si>
   <si>
+    <t>920</t>
+  </si>
+  <si>
+    <t>3.000</t>
+  </si>
+  <si>
     <t>656</t>
   </si>
   <si>
@@ -1765,9 +1753,6 @@
     <t>27.100</t>
   </si>
   <si>
-    <t>3.000</t>
-  </si>
-  <si>
     <t>3.569</t>
   </si>
   <si>
@@ -1783,18 +1768,15 @@
     <t>18.360</t>
   </si>
   <si>
-    <t>11.112</t>
-  </si>
-  <si>
-    <t>7.628</t>
+    <t>11.011</t>
+  </si>
+  <si>
+    <t>7.518</t>
   </si>
   <si>
     <t>552</t>
   </si>
   <si>
-    <t>905</t>
-  </si>
-  <si>
     <t>4.867</t>
   </si>
   <si>
@@ -1999,7 +1981,7 @@
     <t>6.345</t>
   </si>
   <si>
-    <t>3.590</t>
+    <t>3.573</t>
   </si>
   <si>
     <t>1.916</t>
@@ -2036,12 +2018,6 @@
   </si>
   <si>
     <t>3.004</t>
-  </si>
-  <si>
-    <t>5.100</t>
-  </si>
-  <si>
-    <t>1.239</t>
   </si>
   <si>
     <t>NO</t>
@@ -2379,7 +2355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I181"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2416,28 +2392,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D2" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E2" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="F2" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G2" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="H2" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I2" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2445,28 +2421,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C3" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D3" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E3" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="F3" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G3" t="s">
-        <v>63</v>
+        <v>526</v>
       </c>
       <c r="H3" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I3" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2474,28 +2450,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D4" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E4" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="F4" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G4" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="H4" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I4" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2503,28 +2479,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C5" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D5" t="s">
+        <v>453</v>
+      </c>
+      <c r="E5" t="s">
         <v>459</v>
       </c>
-      <c r="E5" t="s">
-        <v>465</v>
-      </c>
       <c r="F5" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G5" t="s">
-        <v>533</v>
+        <v>65</v>
       </c>
       <c r="H5" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I5" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2532,28 +2508,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C6" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D6" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E6" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="F6" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G6" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="H6" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I6" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2561,28 +2537,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D7" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E7" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="F7" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G7" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="H7" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I7" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2590,28 +2566,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C8" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D8" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E8" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="F8" t="s">
+        <v>524</v>
+      </c>
+      <c r="G8" t="s">
         <v>530</v>
       </c>
-      <c r="G8" t="s">
-        <v>536</v>
-      </c>
       <c r="H8" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I8" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2619,28 +2595,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C9" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D9" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E9" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="F9" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G9" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="H9" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I9" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2648,28 +2624,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D10" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E10" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="F10" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G10" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="H10" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I10" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2677,28 +2653,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C11" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D11" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E11" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="F11" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G11" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="H11" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I11" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2706,28 +2682,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C12" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D12" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E12" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="F12" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G12" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="H12" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I12" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2735,28 +2711,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C13" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="D13" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E13" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="F13" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G13" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="H13" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I13" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2764,28 +2740,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C14" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D14" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E14" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="F14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G14" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="H14" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I14" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2793,28 +2769,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C15" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D15" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E15" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="F15" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G15" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H15" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I15" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2822,28 +2798,28 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C16" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D16" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E16" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="F16" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G16" t="s">
-        <v>152</v>
+        <v>538</v>
       </c>
       <c r="H16" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I16" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -2851,28 +2827,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C17" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D17" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E17" t="s">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="F17" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G17" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="H17" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I17" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2880,28 +2856,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C18" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D18" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E18" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="F18" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G18" t="s">
-        <v>545</v>
+        <v>154</v>
       </c>
       <c r="H18" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I18" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -2909,28 +2885,28 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C19" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D19" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E19" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="F19" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G19" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="H19" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I19" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2938,28 +2914,28 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C20" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D20" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E20" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="F20" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G20" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H20" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I20" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -2967,28 +2943,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C21" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D21" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E21" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="F21" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G21" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="H21" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I21" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -2996,28 +2972,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C22" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D22" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E22" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="F22" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G22" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H22" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I22" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -3025,28 +3001,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C23" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D23" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E23" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="F23" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G23" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="H23" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I23" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -3054,28 +3030,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C24" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D24" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="E24" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="F24" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G24" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H24" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I24" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -3083,28 +3059,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C25" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D25" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E25" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F25" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G25" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H25" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I25" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -3112,28 +3088,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C26" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D26" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="E26" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="F26" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G26" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="H26" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I26" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -3141,28 +3117,28 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C27" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D27" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E27" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="F27" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G27" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="H27" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I27" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -3170,28 +3146,28 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C28" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D28" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E28" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="F28" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G28" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="H28" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I28" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -3199,28 +3175,28 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C29" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D29" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E29" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="F29" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G29" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H29" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I29" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -3228,28 +3204,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C30" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D30" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E30" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="F30" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G30" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H30" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I30" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -3257,28 +3233,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C31" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D31" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E31" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="F31" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G31" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="H31" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I31" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -3286,28 +3262,28 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C32" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D32" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E32" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="F32" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G32" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="H32" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I32" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -3315,28 +3291,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C33" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D33" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E33" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="F33" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G33" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="H33" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I33" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -3344,28 +3320,28 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C34" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D34" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E34" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="F34" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G34" t="s">
-        <v>116</v>
+        <v>555</v>
       </c>
       <c r="H34" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I34" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -3373,28 +3349,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C35" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D35" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E35" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="F35" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G35" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="H35" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I35" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -3402,28 +3378,28 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C36" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D36" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E36" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="F36" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G36" t="s">
-        <v>562</v>
+        <v>118</v>
       </c>
       <c r="H36" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I36" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -3431,28 +3407,28 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C37" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D37" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E37" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="F37" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G37" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="H37" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I37" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -3460,28 +3436,28 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C38" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D38" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E38" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="F38" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G38" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="H38" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I38" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -3489,28 +3465,28 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C39" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="D39" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E39" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="F39" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G39" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="H39" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I39" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -3518,28 +3494,28 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C40" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D40" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E40" t="s">
-        <v>493</v>
+        <v>467</v>
       </c>
       <c r="F40" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G40" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="H40" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I40" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -3547,28 +3523,28 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C41" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D41" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E41" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="F41" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G41" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="H41" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I41" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -3576,28 +3552,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C42" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D42" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E42" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F42" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G42" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="H42" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I42" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -3605,28 +3581,28 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C43" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D43" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E43" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="F43" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G43" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="H43" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I43" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -3634,28 +3610,28 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C44" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D44" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E44" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="F44" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G44" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="H44" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I44" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -3663,28 +3639,28 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C45" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D45" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E45" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="F45" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G45" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="H45" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I45" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -3692,28 +3668,28 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C46" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D46" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E46" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="F46" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G46" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="H46" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I46" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -3721,28 +3697,28 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C47" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D47" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E47" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="F47" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G47" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="H47" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I47" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -3750,28 +3726,28 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C48" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D48" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E48" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="F48" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G48" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="H48" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I48" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -3779,28 +3755,28 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C49" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D49" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E49" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="F49" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G49" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="H49" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I49" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -3808,28 +3784,28 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C50" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D50" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E50" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="F50" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G50" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="H50" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I50" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -3837,28 +3813,28 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C51" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D51" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E51" t="s">
-        <v>470</v>
+        <v>497</v>
       </c>
       <c r="F51" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G51" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="H51" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I51" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -3866,28 +3842,28 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C52" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D52" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E52" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="F52" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G52" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="H52" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I52" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -3895,28 +3871,28 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C53" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D53" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E53" t="s">
-        <v>505</v>
+        <v>466</v>
       </c>
       <c r="F53" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G53" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="H53" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I53" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -3924,28 +3900,28 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C54" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D54" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E54" t="s">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="F54" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G54" t="s">
-        <v>147</v>
+        <v>574</v>
       </c>
       <c r="H54" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I54" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -3953,28 +3929,28 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C55" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D55" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E55" t="s">
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="F55" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G55" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="H55" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I55" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -3982,28 +3958,28 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C56" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D56" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E56" t="s">
-        <v>504</v>
+        <v>469</v>
       </c>
       <c r="F56" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G56" t="s">
-        <v>581</v>
+        <v>149</v>
       </c>
       <c r="H56" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I56" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -4011,28 +3987,28 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C57" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D57" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E57" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="F57" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G57" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="H57" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I57" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -4040,28 +4016,28 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C58" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D58" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E58" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="F58" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G58" t="s">
-        <v>181</v>
+        <v>577</v>
       </c>
       <c r="H58" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I58" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -4069,28 +4045,28 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C59" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D59" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E59" t="s">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="F59" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G59" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="H59" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I59" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -4098,28 +4074,28 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C60" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D60" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E60" t="s">
-        <v>503</v>
+        <v>457</v>
       </c>
       <c r="F60" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G60" t="s">
-        <v>584</v>
+        <v>183</v>
       </c>
       <c r="H60" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I60" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -4127,28 +4103,28 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C61" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D61" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E61" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="F61" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G61" t="s">
-        <v>585</v>
+        <v>526</v>
       </c>
       <c r="H61" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I61" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -4156,28 +4132,28 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C62" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D62" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E62" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="F62" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G62" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="H62" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I62" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -4185,28 +4161,28 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C63" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D63" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E63" t="s">
-        <v>473</v>
+        <v>501</v>
       </c>
       <c r="F63" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G63" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="H63" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I63" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -4214,28 +4190,28 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C64" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D64" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E64" t="s">
-        <v>508</v>
+        <v>472</v>
       </c>
       <c r="F64" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G64" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="H64" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I64" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -4243,28 +4219,28 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C65" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D65" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E65" t="s">
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="F65" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G65" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="H65" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I65" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -4272,28 +4248,28 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C66" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D66" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E66" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="F66" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G66" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="H66" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I66" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -4301,28 +4277,28 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C67" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D67" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E67" t="s">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="F67" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G67" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="H67" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I67" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -4330,28 +4306,28 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C68" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D68" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E68" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="F68" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G68" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="H68" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I68" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -4359,28 +4335,28 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C69" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D69" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="E69" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="F69" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G69" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="H69" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I69" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -4388,28 +4364,28 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C70" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D70" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E70" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="F70" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G70" t="s">
-        <v>594</v>
+        <v>26</v>
       </c>
       <c r="H70" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I70" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -4417,28 +4393,28 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C71" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D71" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E71" t="s">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="F71" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G71" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="H71" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I71" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -4446,28 +4422,28 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C72" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D72" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E72" t="s">
-        <v>472</v>
+        <v>506</v>
       </c>
       <c r="F72" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G72" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="H72" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I72" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -4475,28 +4451,28 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C73" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D73" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E73" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="F73" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G73" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="H73" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I73" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -4504,28 +4480,28 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C74" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D74" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E74" t="s">
-        <v>487</v>
+        <v>468</v>
       </c>
       <c r="F74" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G74" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="H74" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I74" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -4533,28 +4509,28 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C75" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D75" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E75" t="s">
-        <v>512</v>
+        <v>467</v>
       </c>
       <c r="F75" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G75" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="H75" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I75" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -4562,28 +4538,28 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C76" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D76" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E76" t="s">
-        <v>513</v>
+        <v>482</v>
       </c>
       <c r="F76" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G76" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="H76" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I76" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -4591,28 +4567,28 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C77" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D77" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E77" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="F77" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G77" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="H77" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I77" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -4620,28 +4596,28 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C78" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D78" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E78" t="s">
-        <v>470</v>
+        <v>507</v>
       </c>
       <c r="F78" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G78" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="H78" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I78" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -4649,28 +4625,28 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C79" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D79" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E79" t="s">
-        <v>480</v>
+        <v>508</v>
       </c>
       <c r="F79" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G79" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="H79" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I79" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -4678,28 +4654,28 @@
         <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C80" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D80" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="E80" t="s">
-        <v>511</v>
+        <v>466</v>
       </c>
       <c r="F80" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G80" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="H80" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I80" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -4707,28 +4683,28 @@
         <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C81" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D81" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E81" t="s">
-        <v>513</v>
+        <v>475</v>
       </c>
       <c r="F81" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G81" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="H81" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I81" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -4736,28 +4712,28 @@
         <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C82" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D82" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="E82" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="F82" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G82" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="H82" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I82" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -4765,28 +4741,28 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C83" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D83" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E83" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="F83" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G83" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="H83" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I83" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -4794,28 +4770,28 @@
         <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C84" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D84" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E84" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="F84" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G84" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="H84" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I84" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -4823,28 +4799,28 @@
         <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C85" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D85" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="E85" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="F85" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G85" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="H85" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I85" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -4852,28 +4828,28 @@
         <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C86" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D86" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E86" t="s">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="F86" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G86" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="H86" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I86" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -4881,28 +4857,28 @@
         <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C87" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D87" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E87" t="s">
-        <v>472</v>
+        <v>505</v>
       </c>
       <c r="F87" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G87" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="H87" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I87" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -4910,28 +4886,28 @@
         <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C88" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D88" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E88" t="s">
-        <v>471</v>
+        <v>503</v>
       </c>
       <c r="F88" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G88" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="H88" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I88" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -4939,28 +4915,28 @@
         <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C89" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D89" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E89" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F89" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G89" t="s">
-        <v>608</v>
+        <v>589</v>
       </c>
       <c r="H89" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I89" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -4968,28 +4944,28 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C90" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D90" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E90" t="s">
-        <v>514</v>
+        <v>467</v>
       </c>
       <c r="F90" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G90" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="H90" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I90" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -4997,28 +4973,28 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C91" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D91" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E91" t="s">
-        <v>515</v>
+        <v>466</v>
       </c>
       <c r="F91" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G91" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="H91" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I91" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -5026,28 +5002,28 @@
         <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C92" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D92" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E92" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="F92" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G92" t="s">
-        <v>610</v>
+        <v>586</v>
       </c>
       <c r="H92" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I92" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -5055,28 +5031,28 @@
         <v>100</v>
       </c>
       <c r="B93" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C93" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D93" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E93" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="F93" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G93" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="H93" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I93" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -5084,28 +5060,28 @@
         <v>101</v>
       </c>
       <c r="B94" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C94" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D94" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E94" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="F94" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G94" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="H94" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I94" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -5113,28 +5089,28 @@
         <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C95" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D95" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E95" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="F95" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G95" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="H95" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I95" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -5142,28 +5118,28 @@
         <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C96" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D96" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E96" t="s">
-        <v>503</v>
+        <v>467</v>
       </c>
       <c r="F96" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G96" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="H96" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I96" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -5171,28 +5147,28 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C97" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D97" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E97" t="s">
-        <v>499</v>
+        <v>468</v>
       </c>
       <c r="F97" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G97" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="H97" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I97" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -5200,28 +5176,28 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C98" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="D98" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E98" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F98" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G98" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="H98" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I98" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -5229,28 +5205,28 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C99" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D99" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E99" t="s">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="F99" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G99" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="H99" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I99" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -5258,28 +5234,28 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C100" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D100" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E100" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="F100" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G100" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="H100" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I100" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -5287,28 +5263,28 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C101" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D101" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E101" t="s">
-        <v>504</v>
+        <v>466</v>
       </c>
       <c r="F101" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G101" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="H101" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I101" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -5316,28 +5292,28 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C102" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D102" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E102" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="F102" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G102" t="s">
-        <v>550</v>
+        <v>612</v>
       </c>
       <c r="H102" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I102" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -5345,28 +5321,28 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C103" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="D103" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E103" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="F103" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G103" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="H103" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I103" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -5374,28 +5350,28 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C104" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="D104" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E104" t="s">
-        <v>516</v>
+        <v>470</v>
       </c>
       <c r="F104" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G104" t="s">
-        <v>621</v>
+        <v>546</v>
       </c>
       <c r="H104" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I104" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -5403,28 +5379,28 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C105" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="D105" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E105" t="s">
-        <v>508</v>
+        <v>457</v>
       </c>
       <c r="F105" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G105" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="H105" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I105" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -5432,28 +5408,28 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C106" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D106" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E106" t="s">
-        <v>477</v>
+        <v>510</v>
       </c>
       <c r="F106" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G106" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="H106" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I106" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -5461,28 +5437,28 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C107" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D107" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E107" t="s">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="F107" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G107" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="H107" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I107" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -5490,28 +5466,28 @@
         <v>115</v>
       </c>
       <c r="B108" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C108" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D108" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E108" t="s">
         <v>472</v>
       </c>
       <c r="F108" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G108" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="H108" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I108" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -5519,28 +5495,28 @@
         <v>116</v>
       </c>
       <c r="B109" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C109" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="D109" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E109" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="F109" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G109" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="H109" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I109" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -5548,28 +5524,28 @@
         <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C110" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="D110" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E110" t="s">
-        <v>509</v>
+        <v>468</v>
       </c>
       <c r="F110" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G110" t="s">
-        <v>93</v>
+        <v>619</v>
       </c>
       <c r="H110" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I110" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -5577,28 +5553,28 @@
         <v>118</v>
       </c>
       <c r="B111" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C111" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="D111" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E111" t="s">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="F111" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G111" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="H111" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I111" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -5606,28 +5582,28 @@
         <v>119</v>
       </c>
       <c r="B112" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C112" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D112" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E112" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F112" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G112" t="s">
-        <v>570</v>
+        <v>95</v>
       </c>
       <c r="H112" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I112" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -5635,28 +5611,28 @@
         <v>120</v>
       </c>
       <c r="B113" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C113" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D113" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E113" t="s">
-        <v>502</v>
+        <v>466</v>
       </c>
       <c r="F113" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G113" t="s">
-        <v>563</v>
+        <v>621</v>
       </c>
       <c r="H113" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I113" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -5664,28 +5640,28 @@
         <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C114" t="s">
         <v>417</v>
       </c>
       <c r="D114" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E114" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="F114" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G114" t="s">
-        <v>628</v>
+        <v>566</v>
       </c>
       <c r="H114" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I114" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -5693,28 +5669,28 @@
         <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C115" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D115" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E115" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F115" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G115" t="s">
-        <v>629</v>
+        <v>559</v>
       </c>
       <c r="H115" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I115" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -5722,28 +5698,28 @@
         <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C116" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D116" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E116" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="F116" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G116" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="H116" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I116" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -5751,28 +5727,28 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C117" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D117" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E117" t="s">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="F117" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G117" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="H117" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I117" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -5780,28 +5756,28 @@
         <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C118" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="D118" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E118" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
       <c r="F118" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G118" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="H118" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I118" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -5809,28 +5785,28 @@
         <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C119" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D119" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E119" t="s">
-        <v>517</v>
+        <v>467</v>
       </c>
       <c r="F119" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G119" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="H119" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I119" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -5838,28 +5814,28 @@
         <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C120" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D120" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E120" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="F120" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G120" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="H120" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I120" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -5867,28 +5843,28 @@
         <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C121" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="D121" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E121" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="F121" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G121" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="H121" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I121" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -5896,28 +5872,28 @@
         <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C122" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D122" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E122" t="s">
-        <v>519</v>
+        <v>467</v>
       </c>
       <c r="F122" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G122" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="H122" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I122" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -5925,28 +5901,28 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C123" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D123" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E123" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="F123" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G123" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="H123" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I123" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -5954,28 +5930,28 @@
         <v>131</v>
       </c>
       <c r="B124" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C124" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="D124" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E124" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F124" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G124" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="H124" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I124" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -5983,28 +5959,28 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C125" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="D125" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E125" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="F125" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G125" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="H125" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I125" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -6012,28 +5988,28 @@
         <v>133</v>
       </c>
       <c r="B126" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C126" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D126" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E126" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="F126" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G126" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="H126" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I126" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -6041,28 +6017,28 @@
         <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C127" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D127" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E127" t="s">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="F127" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G127" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="H127" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I127" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -6070,28 +6046,28 @@
         <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C128" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="D128" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E128" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F128" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G128" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="H128" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I128" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -6099,28 +6075,28 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C129" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D129" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E129" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="F129" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G129" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="H129" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I129" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -6128,28 +6104,28 @@
         <v>137</v>
       </c>
       <c r="B130" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C130" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D130" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E130" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="F130" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G130" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="H130" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I130" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -6157,28 +6133,28 @@
         <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C131" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="D131" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E131" t="s">
-        <v>526</v>
+        <v>466</v>
       </c>
       <c r="F131" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G131" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="H131" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I131" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -6186,28 +6162,28 @@
         <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C132" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="D132" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E132" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F132" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G132" t="s">
-        <v>534</v>
+        <v>638</v>
       </c>
       <c r="H132" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I132" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -6215,28 +6191,28 @@
         <v>140</v>
       </c>
       <c r="B133" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C133" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D133" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E133" t="s">
-        <v>471</v>
+        <v>520</v>
       </c>
       <c r="F133" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G133" t="s">
-        <v>595</v>
+        <v>639</v>
       </c>
       <c r="H133" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I133" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -6244,28 +6220,28 @@
         <v>141</v>
       </c>
       <c r="B134" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C134" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D134" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E134" t="s">
-        <v>471</v>
+        <v>511</v>
       </c>
       <c r="F134" t="s">
+        <v>524</v>
+      </c>
+      <c r="G134" t="s">
         <v>530</v>
       </c>
-      <c r="G134" t="s">
-        <v>646</v>
-      </c>
       <c r="H134" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I134" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -6273,28 +6249,28 @@
         <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C135" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D135" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E135" t="s">
-        <v>492</v>
+        <v>467</v>
       </c>
       <c r="F135" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G135" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="H135" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I135" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -6302,28 +6278,28 @@
         <v>143</v>
       </c>
       <c r="B136" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C136" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D136" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E136" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F136" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G136" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="H136" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I136" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -6331,28 +6307,28 @@
         <v>144</v>
       </c>
       <c r="B137" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C137" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D137" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E137" t="s">
-        <v>509</v>
+        <v>487</v>
       </c>
       <c r="F137" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G137" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="H137" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I137" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -6360,28 +6336,28 @@
         <v>145</v>
       </c>
       <c r="B138" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C138" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D138" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E138" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="F138" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G138" t="s">
-        <v>132</v>
+        <v>641</v>
       </c>
       <c r="H138" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I138" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -6389,28 +6365,28 @@
         <v>146</v>
       </c>
       <c r="B139" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C139" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D139" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E139" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="F139" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G139" t="s">
-        <v>648</v>
+        <v>589</v>
       </c>
       <c r="H139" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I139" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -6418,28 +6394,28 @@
         <v>147</v>
       </c>
       <c r="B140" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C140" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D140" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E140" t="s">
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="F140" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G140" t="s">
-        <v>649</v>
+        <v>134</v>
       </c>
       <c r="H140" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I140" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -6447,28 +6423,28 @@
         <v>148</v>
       </c>
       <c r="B141" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C141" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D141" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E141" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F141" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G141" t="s">
-        <v>595</v>
+        <v>642</v>
       </c>
       <c r="H141" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I141" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -6476,28 +6452,28 @@
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C142" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="D142" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E142" t="s">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="F142" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G142" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="H142" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I142" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -6505,28 +6481,28 @@
         <v>150</v>
       </c>
       <c r="B143" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C143" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="D143" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E143" t="s">
-        <v>471</v>
+        <v>504</v>
       </c>
       <c r="F143" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G143" t="s">
-        <v>122</v>
+        <v>589</v>
       </c>
       <c r="H143" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I143" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -6534,28 +6510,28 @@
         <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C144" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D144" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E144" t="s">
-        <v>471</v>
+        <v>511</v>
       </c>
       <c r="F144" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G144" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="H144" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I144" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -6563,28 +6539,28 @@
         <v>152</v>
       </c>
       <c r="B145" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C145" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D145" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E145" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="F145" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G145" t="s">
-        <v>652</v>
+        <v>124</v>
       </c>
       <c r="H145" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I145" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -6592,28 +6568,28 @@
         <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C146" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D146" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E146" t="s">
-        <v>510</v>
+        <v>467</v>
       </c>
       <c r="F146" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G146" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="H146" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I146" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -6621,28 +6597,28 @@
         <v>154</v>
       </c>
       <c r="B147" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C147" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D147" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E147" t="s">
-        <v>509</v>
+        <v>469</v>
       </c>
       <c r="F147" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G147" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="H147" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I147" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -6650,28 +6626,28 @@
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C148" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D148" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E148" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="F148" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G148" t="s">
-        <v>554</v>
+        <v>647</v>
       </c>
       <c r="H148" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I148" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -6679,28 +6655,28 @@
         <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C149" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D149" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E149" t="s">
-        <v>471</v>
+        <v>503</v>
       </c>
       <c r="F149" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G149" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="H149" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I149" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -6708,28 +6684,28 @@
         <v>157</v>
       </c>
       <c r="B150" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C150" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D150" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E150" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F150" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G150" t="s">
-        <v>656</v>
+        <v>550</v>
       </c>
       <c r="H150" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I150" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -6737,28 +6713,28 @@
         <v>158</v>
       </c>
       <c r="B151" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C151" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D151" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E151" t="s">
-        <v>517</v>
+        <v>467</v>
       </c>
       <c r="F151" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G151" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="H151" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I151" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -6766,28 +6742,28 @@
         <v>159</v>
       </c>
       <c r="B152" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C152" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="D152" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E152" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="F152" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G152" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="H152" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I152" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -6795,28 +6771,28 @@
         <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C153" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="D153" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E153" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="F153" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G153" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="H153" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I153" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -6824,28 +6800,28 @@
         <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C154" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D154" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E154" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F154" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G154" t="s">
-        <v>595</v>
+        <v>652</v>
       </c>
       <c r="H154" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I154" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -6853,28 +6829,28 @@
         <v>162</v>
       </c>
       <c r="B155" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C155" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D155" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E155" t="s">
-        <v>470</v>
+        <v>508</v>
       </c>
       <c r="F155" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G155" t="s">
-        <v>595</v>
+        <v>653</v>
       </c>
       <c r="H155" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I155" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -6882,28 +6858,28 @@
         <v>163</v>
       </c>
       <c r="B156" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C156" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D156" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E156" t="s">
-        <v>492</v>
+        <v>466</v>
       </c>
       <c r="F156" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G156" t="s">
-        <v>660</v>
+        <v>589</v>
       </c>
       <c r="H156" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I156" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -6911,28 +6887,28 @@
         <v>164</v>
       </c>
       <c r="B157" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C157" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D157" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E157" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="F157" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G157" t="s">
-        <v>116</v>
+        <v>589</v>
       </c>
       <c r="H157" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I157" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -6940,28 +6916,28 @@
         <v>165</v>
       </c>
       <c r="B158" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C158" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D158" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E158" t="s">
-        <v>508</v>
+        <v>487</v>
       </c>
       <c r="F158" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G158" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="H158" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I158" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -6969,28 +6945,28 @@
         <v>166</v>
       </c>
       <c r="B159" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C159" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="D159" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E159" t="s">
-        <v>500</v>
+        <v>474</v>
       </c>
       <c r="F159" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G159" t="s">
-        <v>662</v>
+        <v>118</v>
       </c>
       <c r="H159" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I159" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -6998,28 +6974,28 @@
         <v>167</v>
       </c>
       <c r="B160" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C160" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D160" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E160" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="F160" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G160" t="s">
-        <v>595</v>
+        <v>655</v>
       </c>
       <c r="H160" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I160" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -7027,28 +7003,28 @@
         <v>168</v>
       </c>
       <c r="B161" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C161" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D161" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E161" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="F161" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G161" t="s">
-        <v>595</v>
+        <v>656</v>
       </c>
       <c r="H161" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I161" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -7056,28 +7032,28 @@
         <v>169</v>
       </c>
       <c r="B162" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C162" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D162" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E162" t="s">
-        <v>477</v>
+        <v>508</v>
       </c>
       <c r="F162" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G162" t="s">
-        <v>663</v>
+        <v>589</v>
       </c>
       <c r="H162" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I162" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -7085,28 +7061,28 @@
         <v>170</v>
       </c>
       <c r="B163" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C163" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D163" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E163" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F163" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G163" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="H163" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I163" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -7114,28 +7090,28 @@
         <v>171</v>
       </c>
       <c r="B164" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C164" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="D164" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E164" t="s">
-        <v>514</v>
+        <v>472</v>
       </c>
       <c r="F164" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G164" t="s">
-        <v>595</v>
+        <v>657</v>
       </c>
       <c r="H164" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I164" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -7143,28 +7119,28 @@
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C165" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D165" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E165" t="s">
-        <v>527</v>
+        <v>466</v>
       </c>
       <c r="F165" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G165" t="s">
-        <v>664</v>
+        <v>589</v>
       </c>
       <c r="H165" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I165" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -7172,28 +7148,28 @@
         <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C166" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D166" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E166" t="s">
-        <v>471</v>
+        <v>508</v>
       </c>
       <c r="F166" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G166" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="H166" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I166" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -7201,28 +7177,28 @@
         <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C167" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D167" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E167" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="F167" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G167" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="H167" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I167" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -7230,28 +7206,28 @@
         <v>175</v>
       </c>
       <c r="B168" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C168" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D168" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E168" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F168" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G168" t="s">
-        <v>666</v>
+        <v>589</v>
       </c>
       <c r="H168" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I168" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -7259,28 +7235,28 @@
         <v>176</v>
       </c>
       <c r="B169" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C169" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D169" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E169" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="F169" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G169" t="s">
-        <v>595</v>
+        <v>659</v>
       </c>
       <c r="H169" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I169" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -7288,28 +7264,28 @@
         <v>177</v>
       </c>
       <c r="B170" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C170" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D170" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E170" t="s">
-        <v>503</v>
+        <v>466</v>
       </c>
       <c r="F170" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G170" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="H170" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I170" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -7317,28 +7293,28 @@
         <v>178</v>
       </c>
       <c r="B171" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C171" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D171" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E171" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="F171" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G171" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="H171" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I171" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -7346,28 +7322,28 @@
         <v>179</v>
       </c>
       <c r="B172" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C172" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D172" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E172" t="s">
-        <v>473</v>
+        <v>498</v>
       </c>
       <c r="F172" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G172" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="H172" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I172" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -7375,28 +7351,28 @@
         <v>180</v>
       </c>
       <c r="B173" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C173" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D173" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E173" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="F173" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G173" t="s">
-        <v>669</v>
+        <v>589</v>
       </c>
       <c r="H173" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I173" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -7404,28 +7380,28 @@
         <v>181</v>
       </c>
       <c r="B174" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C174" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="D174" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E174" t="s">
-        <v>503</v>
+        <v>469</v>
       </c>
       <c r="F174" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G174" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="H174" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I174" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -7433,28 +7409,28 @@
         <v>182</v>
       </c>
       <c r="B175" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C175" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="D175" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E175" t="s">
-        <v>528</v>
+        <v>471</v>
       </c>
       <c r="F175" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G175" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="H175" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I175" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -7462,28 +7438,28 @@
         <v>183</v>
       </c>
       <c r="B176" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C176" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D176" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E176" t="s">
-        <v>529</v>
+        <v>498</v>
       </c>
       <c r="F176" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G176" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="H176" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I176" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -7491,28 +7467,28 @@
         <v>184</v>
       </c>
       <c r="B177" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C177" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D177" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E177" t="s">
-        <v>504</v>
+        <v>522</v>
       </c>
       <c r="F177" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G177" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="H177" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I177" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -7520,28 +7496,28 @@
         <v>185</v>
       </c>
       <c r="B178" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C178" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="D178" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E178" t="s">
-        <v>475</v>
+        <v>523</v>
       </c>
       <c r="F178" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G178" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="H178" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I178" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -7549,86 +7525,28 @@
         <v>186</v>
       </c>
       <c r="B179" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C179" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="D179" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E179" t="s">
-        <v>499</v>
+        <v>456</v>
       </c>
       <c r="F179" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G179" t="s">
-        <v>135</v>
+        <v>667</v>
       </c>
       <c r="H179" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="I179" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9">
-      <c r="A180" t="s">
-        <v>187</v>
-      </c>
-      <c r="B180" t="s">
-        <v>367</v>
-      </c>
-      <c r="C180" t="s">
-        <v>457</v>
-      </c>
-      <c r="D180" t="s">
-        <v>459</v>
-      </c>
-      <c r="E180" t="s">
-        <v>499</v>
-      </c>
-      <c r="F180" t="s">
-        <v>530</v>
-      </c>
-      <c r="G180" t="s">
-        <v>675</v>
-      </c>
-      <c r="H180" t="s">
-        <v>676</v>
-      </c>
-      <c r="I180" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9">
-      <c r="A181" t="s">
-        <v>188</v>
-      </c>
-      <c r="B181" t="s">
-        <v>368</v>
-      </c>
-      <c r="C181" t="s">
-        <v>458</v>
-      </c>
-      <c r="D181" t="s">
-        <v>459</v>
-      </c>
-      <c r="E181" t="s">
-        <v>470</v>
-      </c>
-      <c r="F181" t="s">
-        <v>530</v>
-      </c>
-      <c r="G181" t="s">
-        <v>121</v>
-      </c>
-      <c r="H181" t="s">
-        <v>676</v>
-      </c>
-      <c r="I181" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
   </sheetData>

--- a/data/BioTecnos.xlsx
+++ b/data/BioTecnos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="669">
   <si>
     <t>ID</t>
   </si>
@@ -43,12 +43,21 @@
     <t>Estado</t>
   </si>
   <si>
+    <t>909</t>
+  </si>
+  <si>
+    <t>908</t>
+  </si>
+  <si>
     <t>907</t>
   </si>
   <si>
     <t>906</t>
   </si>
   <si>
+    <t>905</t>
+  </si>
+  <si>
     <t>904</t>
   </si>
   <si>
@@ -565,1324 +574,1324 @@
     <t>721</t>
   </si>
   <si>
+    <t>M04D002LI2603</t>
+  </si>
+  <si>
+    <t>M02T105L03604</t>
+  </si>
+  <si>
+    <t>M02T106L03603</t>
+  </si>
+  <si>
+    <t>M02L008L11603</t>
+  </si>
+  <si>
+    <t>M02M039L20604</t>
+  </si>
+  <si>
+    <t>M02N042LB5601</t>
+  </si>
+  <si>
+    <t>M02N042LA5601</t>
+  </si>
+  <si>
+    <t>M02N042LC5601</t>
+  </si>
+  <si>
+    <t>M02T118LB5601</t>
+  </si>
+  <si>
+    <t>M02T114LA5602</t>
+  </si>
+  <si>
+    <t>M02T113LA5601</t>
+  </si>
+  <si>
+    <t>M02T119LA5601</t>
+  </si>
+  <si>
+    <t>M02T118LA5601</t>
+  </si>
+  <si>
+    <t>M02Q048L33604</t>
+  </si>
+  <si>
+    <t>M02Q047L24606</t>
+  </si>
+  <si>
+    <t>M02Q047LA5602</t>
+  </si>
+  <si>
+    <t>M02Q047L24605</t>
+  </si>
+  <si>
+    <t>M02M039L20603</t>
+  </si>
+  <si>
+    <t>M02L008L11602</t>
+  </si>
+  <si>
+    <t>M02T105L03603</t>
+  </si>
+  <si>
+    <t>M02T083LA3601</t>
+  </si>
+  <si>
+    <t>M02T083LB4602</t>
+  </si>
+  <si>
+    <t>M04D002LF4602</t>
+  </si>
+  <si>
+    <t>M04B009LA5602</t>
+  </si>
+  <si>
+    <t>M04B009LA5601</t>
+  </si>
+  <si>
+    <t>M04D002LH2602</t>
+  </si>
+  <si>
+    <t>M04D002LG2601</t>
+  </si>
+  <si>
+    <t>M06L004L13601</t>
+  </si>
+  <si>
+    <t>M04D002LF4601</t>
+  </si>
+  <si>
+    <t>M04D002LB4601</t>
+  </si>
+  <si>
+    <t>M04A002LB2601</t>
+  </si>
+  <si>
+    <t>M04L002L14601</t>
+  </si>
+  <si>
+    <t>M04D002LD4601</t>
+  </si>
+  <si>
+    <t>M04D002LM2604</t>
+  </si>
+  <si>
+    <t>M04D002LI2602</t>
+  </si>
+  <si>
+    <t>M04D002LI2601</t>
+  </si>
+  <si>
+    <t>M02U043L62601</t>
+  </si>
+  <si>
+    <t>M02U043L92601</t>
+  </si>
+  <si>
+    <t>M02U043L42601</t>
+  </si>
+  <si>
+    <t>M02Q048L33603</t>
+  </si>
+  <si>
+    <t>M02Q047L14602</t>
+  </si>
+  <si>
+    <t>M02Q047L24604</t>
+  </si>
+  <si>
+    <t>M02Q047L24603</t>
+  </si>
+  <si>
+    <t>M04L005601</t>
+  </si>
+  <si>
+    <t>M04D001LA2601</t>
+  </si>
+  <si>
+    <t>M04L003L33601</t>
+  </si>
+  <si>
+    <t>M04L004601</t>
+  </si>
+  <si>
+    <t>M02P089L03501</t>
+  </si>
+  <si>
+    <t>M02P088L03501</t>
+  </si>
+  <si>
+    <t>M02Q050L01604</t>
+  </si>
+  <si>
+    <t>M02Q053L01601</t>
+  </si>
+  <si>
+    <t>M02Q068L24601</t>
+  </si>
+  <si>
+    <t>M02Q068L14601</t>
+  </si>
+  <si>
+    <t>M02Q068L01602</t>
+  </si>
+  <si>
+    <t>M02Q048L33602</t>
+  </si>
+  <si>
+    <t>M02T106L03602</t>
+  </si>
+  <si>
+    <t>M02M039L23601</t>
+  </si>
+  <si>
+    <t>M02M039L20602</t>
+  </si>
+  <si>
+    <t>M02T105L03602</t>
+  </si>
+  <si>
+    <t>M02T106L03601</t>
+  </si>
+  <si>
+    <t>M02T105L03601</t>
+  </si>
+  <si>
+    <t>M02L008L11601</t>
+  </si>
+  <si>
+    <t>M02M040L53601</t>
+  </si>
+  <si>
+    <t>M02Q068L01601</t>
+  </si>
+  <si>
+    <t>M02Q068L34601</t>
+  </si>
+  <si>
+    <t>M02T083LB4601</t>
+  </si>
+  <si>
+    <t>M02M039L20601</t>
+  </si>
+  <si>
+    <t>M02M021L23601</t>
+  </si>
+  <si>
+    <t>M02Q050L01603</t>
+  </si>
+  <si>
+    <t>M02Q050L24603</t>
+  </si>
+  <si>
+    <t>M02Q050L24602</t>
+  </si>
+  <si>
+    <t>M02Q050L34601</t>
+  </si>
+  <si>
+    <t>M0601602</t>
+  </si>
+  <si>
+    <t>M04L002L23602</t>
+  </si>
+  <si>
+    <t>M02Q047L14601</t>
+  </si>
+  <si>
+    <t>M02Q047LA5601</t>
+  </si>
+  <si>
+    <t>M02Q047L24602</t>
+  </si>
+  <si>
+    <t>M04D002LM2602</t>
+  </si>
+  <si>
+    <t>M04L002L23601</t>
+  </si>
+  <si>
+    <t>M04A002LA0602</t>
+  </si>
+  <si>
+    <t>M02Q048L13601</t>
+  </si>
+  <si>
+    <t>M02Q048L33601</t>
+  </si>
+  <si>
+    <t>M04D002LH2601</t>
+  </si>
+  <si>
+    <t>M0601601</t>
+  </si>
+  <si>
+    <t>M04A002LA0601</t>
+  </si>
+  <si>
+    <t>M04D002LM2601</t>
+  </si>
+  <si>
+    <t>M02Q050L01602</t>
+  </si>
+  <si>
+    <t>M02Q050L01601</t>
+  </si>
+  <si>
+    <t>M0601501</t>
+  </si>
+  <si>
+    <t>M02Q050L24601</t>
+  </si>
+  <si>
+    <t>M02Q047LA5504</t>
+  </si>
+  <si>
+    <t>M02Q047L24513</t>
+  </si>
+  <si>
+    <t>M02Q048L33515</t>
+  </si>
+  <si>
+    <t>M02Q048L13504</t>
+  </si>
+  <si>
+    <t>M0240501</t>
+  </si>
+  <si>
+    <t>M02Q050L01526</t>
+  </si>
+  <si>
+    <t>M02Q053L01506</t>
+  </si>
+  <si>
+    <t>M02Q047L24512</t>
+  </si>
+  <si>
+    <t>M02Q047LA5503</t>
+  </si>
+  <si>
+    <t>M02Q068L01507</t>
+  </si>
+  <si>
+    <t>M02Q050L01525</t>
+  </si>
+  <si>
+    <t>M02Q053L01505</t>
+  </si>
+  <si>
+    <t>M02Q048L33514</t>
+  </si>
+  <si>
+    <t>M02Q048L33513</t>
+  </si>
+  <si>
+    <t>M02T106L03505</t>
+  </si>
+  <si>
+    <t>M02T105L03506</t>
+  </si>
+  <si>
+    <t>M02L008L11501</t>
+  </si>
+  <si>
+    <t>M02M075L02502</t>
+  </si>
+  <si>
+    <t>M02M021L23504</t>
+  </si>
+  <si>
+    <t>M02T083LB4503</t>
+  </si>
+  <si>
+    <t>M02T083LA3507</t>
+  </si>
+  <si>
+    <t>M02Q047LA5502</t>
+  </si>
+  <si>
+    <t>M02Q050L01524</t>
+  </si>
+  <si>
+    <t>M02Q050L24504</t>
+  </si>
+  <si>
+    <t>M02Q048L33512</t>
+  </si>
+  <si>
+    <t>M02Q068L24502</t>
+  </si>
+  <si>
+    <t>M02Q068L14501</t>
+  </si>
+  <si>
+    <t>M02Q050L01522</t>
+  </si>
+  <si>
+    <t>M02Q053L01504</t>
+  </si>
+  <si>
+    <t>M02Q068L01506</t>
+  </si>
+  <si>
+    <t>M02Q047L24511</t>
+  </si>
+  <si>
+    <t>M02Q047LA5501</t>
+  </si>
+  <si>
+    <t>M0247518</t>
+  </si>
+  <si>
+    <t>M02Q047L24510</t>
+  </si>
+  <si>
+    <t>M02M022L02503</t>
+  </si>
+  <si>
+    <t>M02M040L33502</t>
+  </si>
+  <si>
+    <t>M02M040L13501</t>
+  </si>
+  <si>
+    <t>M02M040L23501</t>
+  </si>
+  <si>
+    <t>M02M078L02503</t>
+  </si>
+  <si>
+    <t>M02M110L03502</t>
+  </si>
+  <si>
+    <t>M02Q053L01503</t>
+  </si>
+  <si>
+    <t>M02Q048501</t>
+  </si>
+  <si>
+    <t>M02Q048L33511</t>
+  </si>
+  <si>
+    <t>M02M109L03502</t>
+  </si>
+  <si>
+    <t>M02Q049L01504</t>
+  </si>
+  <si>
+    <t>M0247517</t>
+  </si>
+  <si>
+    <t>M02Q047L24509</t>
+  </si>
+  <si>
+    <t>M02Q047L24508</t>
+  </si>
+  <si>
+    <t>M02Q047L14506</t>
+  </si>
+  <si>
+    <t>M02Q048L33510</t>
+  </si>
+  <si>
+    <t>M02Q050L24503</t>
+  </si>
+  <si>
+    <t>M02M039L20505</t>
+  </si>
+  <si>
+    <t>M02M022L02502</t>
+  </si>
+  <si>
+    <t>M02Q050L01521</t>
+  </si>
+  <si>
+    <t>M02Q050L34502</t>
+  </si>
+  <si>
+    <t>M0247516</t>
+  </si>
+  <si>
+    <t>M02Q047L24507</t>
+  </si>
+  <si>
+    <t>M02Q047L24506</t>
+  </si>
+  <si>
+    <t>M02M039L20504</t>
+  </si>
+  <si>
+    <t>M02Q050L34501</t>
+  </si>
+  <si>
+    <t>M02Q050L24501</t>
+  </si>
+  <si>
+    <t>M02Q050L01520</t>
+  </si>
+  <si>
+    <t>M02Q047L24505</t>
+  </si>
+  <si>
+    <t>M02Q047L14505</t>
+  </si>
+  <si>
+    <t>M0247515</t>
+  </si>
+  <si>
+    <t>M02Q047L24504</t>
+  </si>
+  <si>
+    <t>M02Q048L13503</t>
+  </si>
+  <si>
+    <t>M02Q048L33509</t>
+  </si>
+  <si>
+    <t>M02Q048L33508</t>
+  </si>
+  <si>
+    <t>M02Q047L14504</t>
+  </si>
+  <si>
+    <t>M04B009LA5501</t>
+  </si>
+  <si>
+    <t>M02M021L23503</t>
+  </si>
+  <si>
+    <t>M02Q053L01502</t>
+  </si>
+  <si>
+    <t>M02Q048L13502</t>
+  </si>
+  <si>
+    <t>M02Q048L33507</t>
+  </si>
+  <si>
+    <t>M02T083LB4502</t>
+  </si>
+  <si>
+    <t>M02Q048L33506</t>
+  </si>
+  <si>
+    <t>M02Q048L13501</t>
+  </si>
+  <si>
+    <t>M02Q048L23502</t>
+  </si>
+  <si>
+    <t>M02Q047L24503</t>
+  </si>
+  <si>
+    <t>M0247514</t>
+  </si>
+  <si>
+    <t>M02Q048L33505</t>
+  </si>
+  <si>
+    <t>M02Q047L14503</t>
+  </si>
+  <si>
+    <t>M02Q068L01505</t>
+  </si>
+  <si>
+    <t>M02Q050L01519</t>
+  </si>
+  <si>
+    <t>M02M039L20503</t>
+  </si>
+  <si>
+    <t>M02T083LA3506</t>
+  </si>
+  <si>
+    <t>20-04-2026</t>
+  </si>
+  <si>
+    <t>16-04-2026</t>
+  </si>
+  <si>
+    <t>13-04-2026</t>
+  </si>
+  <si>
+    <t>10-04-2026</t>
+  </si>
+  <si>
+    <t>09-04-2026</t>
+  </si>
+  <si>
+    <t>06-04-2026</t>
+  </si>
+  <si>
+    <t>07-04-2026</t>
+  </si>
+  <si>
+    <t>02-04-2026</t>
+  </si>
+  <si>
+    <t>31-03-2026</t>
+  </si>
+  <si>
+    <t>24-03-2026</t>
+  </si>
+  <si>
+    <t>23-03-2026</t>
+  </si>
+  <si>
+    <t>20-03-2026</t>
+  </si>
+  <si>
+    <t>19-03-2026</t>
+  </si>
+  <si>
+    <t>18-03-2026</t>
+  </si>
+  <si>
+    <t>17-03-2026</t>
+  </si>
+  <si>
+    <t>13-03-2026</t>
+  </si>
+  <si>
+    <t>12-03-2026</t>
+  </si>
+  <si>
+    <t>09-03-2026</t>
+  </si>
+  <si>
+    <t>26-02-2026</t>
+  </si>
+  <si>
+    <t>25-02-2026</t>
+  </si>
+  <si>
+    <t>20-12-2025</t>
+  </si>
+  <si>
+    <t>24-02-2026</t>
+  </si>
+  <si>
+    <t>23-02-2026</t>
+  </si>
+  <si>
+    <t>20-02-2026</t>
+  </si>
+  <si>
+    <t>16-02-2026</t>
+  </si>
+  <si>
+    <t>12-02-2026</t>
+  </si>
+  <si>
+    <t>11-02-2026</t>
+  </si>
+  <si>
+    <t>10-02-2026</t>
+  </si>
+  <si>
+    <t>06-02-2026</t>
+  </si>
+  <si>
+    <t>05-02-2026</t>
+  </si>
+  <si>
+    <t>02-02-2026</t>
+  </si>
+  <si>
+    <t>28-01-2026</t>
+  </si>
+  <si>
+    <t>29-01-2026</t>
+  </si>
+  <si>
+    <t>26-01-2026</t>
+  </si>
+  <si>
+    <t>19-01-2026</t>
+  </si>
+  <si>
+    <t>15-01-2026</t>
+  </si>
+  <si>
+    <t>14-01-2026</t>
+  </si>
+  <si>
+    <t>13-01-2026</t>
+  </si>
+  <si>
+    <t>08-01-2026</t>
+  </si>
+  <si>
+    <t>05-01-2026</t>
+  </si>
+  <si>
+    <t>24-12-2025</t>
+  </si>
+  <si>
+    <t>29-12-2025</t>
+  </si>
+  <si>
+    <t>30-12-2025</t>
+  </si>
+  <si>
+    <t>27-12-2025</t>
+  </si>
+  <si>
+    <t>26-12-2025</t>
+  </si>
+  <si>
+    <t>23-12-2025</t>
+  </si>
+  <si>
+    <t>22-12-2025</t>
+  </si>
+  <si>
+    <t>18-12-2025</t>
+  </si>
+  <si>
+    <t>17-12-2025</t>
+  </si>
+  <si>
+    <t>16-12-2025</t>
+  </si>
+  <si>
+    <t>15-12-2025</t>
+  </si>
+  <si>
+    <t>05-12-2025</t>
+  </si>
+  <si>
+    <t>12-12-2025</t>
+  </si>
+  <si>
+    <t>10-12-2025</t>
+  </si>
+  <si>
+    <t>04-12-2025</t>
+  </si>
+  <si>
+    <t>24-11-2025</t>
+  </si>
+  <si>
+    <t>18-11-2025</t>
+  </si>
+  <si>
+    <t>17-11-2025</t>
+  </si>
+  <si>
+    <t>13-11-2025</t>
+  </si>
+  <si>
+    <t>12-11-2025</t>
+  </si>
+  <si>
+    <t>11-11-2025</t>
+  </si>
+  <si>
+    <t>10-11-2025</t>
+  </si>
+  <si>
+    <t>06-11-2025</t>
+  </si>
+  <si>
+    <t>05-11-2025</t>
+  </si>
+  <si>
+    <t>04-11-2025</t>
+  </si>
+  <si>
+    <t>03-11-2025</t>
+  </si>
+  <si>
+    <t>30-10-2025</t>
+  </si>
+  <si>
+    <t>31-10-2025</t>
+  </si>
+  <si>
+    <t>29-10-2025</t>
+  </si>
+  <si>
+    <t>27-10-2025</t>
+  </si>
+  <si>
+    <t>20-10-2025</t>
+  </si>
+  <si>
+    <t>17-10-2025</t>
+  </si>
+  <si>
+    <t>16-10-2025</t>
+  </si>
+  <si>
+    <t>15-10-2025</t>
+  </si>
+  <si>
+    <t>14-10-2025</t>
+  </si>
+  <si>
+    <t>13-10-2025</t>
+  </si>
+  <si>
+    <t>24-09-2025</t>
+  </si>
+  <si>
+    <t>23-09-2025</t>
+  </si>
+  <si>
+    <t>18-09-2025</t>
+  </si>
+  <si>
+    <t>16-09-2025</t>
+  </si>
+  <si>
+    <t>15-09-2025</t>
+  </si>
+  <si>
+    <t>09-09-2025</t>
+  </si>
+  <si>
+    <t>08-09-2025</t>
+  </si>
+  <si>
+    <t>05-09-2025</t>
+  </si>
+  <si>
+    <t>04-09-2025</t>
+  </si>
+  <si>
+    <t>03-09-2025</t>
+  </si>
+  <si>
+    <t>02-09-2025</t>
+  </si>
+  <si>
+    <t>01-09-2025</t>
+  </si>
+  <si>
+    <t>28-08-2025</t>
+  </si>
+  <si>
+    <t>Avellano</t>
+  </si>
+  <si>
+    <t>Arándano</t>
+  </si>
+  <si>
+    <t>Cerezo</t>
+  </si>
+  <si>
+    <t>04D002LI2</t>
+  </si>
+  <si>
+    <t>02T105L03</t>
+  </si>
+  <si>
+    <t>02T106L03</t>
+  </si>
+  <si>
+    <t>02L008L11</t>
+  </si>
+  <si>
+    <t>02M039L20</t>
+  </si>
+  <si>
+    <t>02N042LB5</t>
+  </si>
+  <si>
+    <t>02N042LA5</t>
+  </si>
+  <si>
+    <t>02N042LC5</t>
+  </si>
+  <si>
+    <t>02T118LB5</t>
+  </si>
+  <si>
+    <t>02T114LA5</t>
+  </si>
+  <si>
+    <t>02T113LA5</t>
+  </si>
+  <si>
+    <t>02T119LA5</t>
+  </si>
+  <si>
+    <t>02T118LA5</t>
+  </si>
+  <si>
+    <t>02Q048L33</t>
+  </si>
+  <si>
+    <t>02Q047L24</t>
+  </si>
+  <si>
+    <t>02Q047LA5</t>
+  </si>
+  <si>
+    <t>02T083LA3</t>
+  </si>
+  <si>
+    <t>02T083LB4</t>
+  </si>
+  <si>
+    <t>04D002LF4</t>
+  </si>
+  <si>
+    <t>04B009LA5</t>
+  </si>
+  <si>
+    <t>04D002LH2</t>
+  </si>
+  <si>
+    <t>04D002LG2</t>
+  </si>
+  <si>
+    <t>06L004L13</t>
+  </si>
+  <si>
+    <t>04D002LB4</t>
+  </si>
+  <si>
+    <t>04A002LB2</t>
+  </si>
+  <si>
+    <t>04L002L14</t>
+  </si>
+  <si>
+    <t>04D002LD4</t>
+  </si>
+  <si>
+    <t>04D002LM2</t>
+  </si>
+  <si>
+    <t>02U043L62</t>
+  </si>
+  <si>
+    <t>02U043L92</t>
+  </si>
+  <si>
+    <t>02U043L42</t>
+  </si>
+  <si>
+    <t>02Q047L14</t>
+  </si>
+  <si>
+    <t>04L005</t>
+  </si>
+  <si>
+    <t>04D001LA2</t>
+  </si>
+  <si>
+    <t>04L003L33</t>
+  </si>
+  <si>
+    <t>04L004</t>
+  </si>
+  <si>
+    <t>02P089L03</t>
+  </si>
+  <si>
+    <t>02P088L03</t>
+  </si>
+  <si>
+    <t>02Q050L01</t>
+  </si>
+  <si>
+    <t>02Q053L01</t>
+  </si>
+  <si>
+    <t>02Q068L24</t>
+  </si>
+  <si>
+    <t>02Q068L14</t>
+  </si>
+  <si>
+    <t>02Q068L01</t>
+  </si>
+  <si>
+    <t>02M039L23</t>
+  </si>
+  <si>
+    <t>02M040L53</t>
+  </si>
+  <si>
+    <t>02Q068L34</t>
+  </si>
+  <si>
+    <t>02M021L23</t>
+  </si>
+  <si>
+    <t>02Q050L24</t>
+  </si>
+  <si>
+    <t>02Q050L34</t>
+  </si>
+  <si>
+    <t>0601</t>
+  </si>
+  <si>
+    <t>04L002L23</t>
+  </si>
+  <si>
+    <t>04A002LA0</t>
+  </si>
+  <si>
+    <t>02Q048L13</t>
+  </si>
+  <si>
+    <t>0240</t>
+  </si>
+  <si>
+    <t>02M075L02</t>
+  </si>
+  <si>
+    <t>0247</t>
+  </si>
+  <si>
+    <t>02M022L02</t>
+  </si>
+  <si>
+    <t>02M040L33</t>
+  </si>
+  <si>
+    <t>02M040L13</t>
+  </si>
+  <si>
+    <t>02M040L23</t>
+  </si>
+  <si>
+    <t>02M078L02</t>
+  </si>
+  <si>
+    <t>02M110L03</t>
+  </si>
+  <si>
+    <t>02Q048</t>
+  </si>
+  <si>
+    <t>02M109L03</t>
+  </si>
+  <si>
+    <t>02Q049L01</t>
+  </si>
+  <si>
+    <t>02Q048L23</t>
+  </si>
+  <si>
+    <t>NO LMC ( 100% )</t>
+  </si>
+  <si>
+    <t>950</t>
+  </si>
+  <si>
+    <t>14.835</t>
+  </si>
+  <si>
+    <t>920</t>
+  </si>
+  <si>
+    <t>3.000</t>
+  </si>
+  <si>
+    <t>7.547</t>
+  </si>
+  <si>
+    <t>656</t>
+  </si>
+  <si>
+    <t>2.168</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>18.408</t>
+  </si>
+  <si>
+    <t>7.656</t>
+  </si>
+  <si>
+    <t>960</t>
+  </si>
+  <si>
+    <t>30.840</t>
+  </si>
+  <si>
+    <t>12.000</t>
+  </si>
+  <si>
+    <t>620</t>
+  </si>
+  <si>
+    <t>3.318</t>
+  </si>
+  <si>
+    <t>2.836</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>1.039</t>
+  </si>
+  <si>
+    <t>690</t>
+  </si>
+  <si>
+    <t>1.223</t>
+  </si>
+  <si>
+    <t>700</t>
+  </si>
+  <si>
+    <t>3.916</t>
+  </si>
+  <si>
+    <t>2.788</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>4.395</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>4.287</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>1.523</t>
+  </si>
+  <si>
+    <t>1.424</t>
+  </si>
+  <si>
+    <t>23.870</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>39.927</t>
+  </si>
+  <si>
+    <t>67.488</t>
+  </si>
+  <si>
+    <t>1.068</t>
+  </si>
+  <si>
+    <t>5.443</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>3.108</t>
+  </si>
+  <si>
+    <t>480</t>
+  </si>
+  <si>
+    <t>470</t>
+  </si>
+  <si>
+    <t>1.968</t>
+  </si>
+  <si>
+    <t>2.540</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>1.053</t>
+  </si>
+  <si>
+    <t>589</t>
+  </si>
+  <si>
+    <t>2.784</t>
+  </si>
+  <si>
+    <t>3.308</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>672</t>
+  </si>
+  <si>
+    <t>8.381</t>
+  </si>
+  <si>
+    <t>45.322</t>
+  </si>
+  <si>
+    <t>27.100</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>719</t>
-  </si>
-  <si>
-    <t>718</t>
-  </si>
-  <si>
-    <t>717</t>
-  </si>
-  <si>
-    <t>M02T106L03603</t>
-  </si>
-  <si>
-    <t>M02L008L11603</t>
-  </si>
-  <si>
-    <t>M02N042LB5601</t>
-  </si>
-  <si>
-    <t>M02N042LA5601</t>
-  </si>
-  <si>
-    <t>M02N042LC5601</t>
-  </si>
-  <si>
-    <t>M02T118LB5601</t>
-  </si>
-  <si>
-    <t>M02T114LA5602</t>
-  </si>
-  <si>
-    <t>M02T113LA5601</t>
-  </si>
-  <si>
-    <t>M02T119LA5601</t>
-  </si>
-  <si>
-    <t>M02T118LA5601</t>
-  </si>
-  <si>
-    <t>M02Q048L33604</t>
-  </si>
-  <si>
-    <t>M02Q047L24606</t>
-  </si>
-  <si>
-    <t>M02Q047LA5602</t>
-  </si>
-  <si>
-    <t>M02Q047L24605</t>
-  </si>
-  <si>
-    <t>M02M039L20603</t>
-  </si>
-  <si>
-    <t>M02L008L11602</t>
-  </si>
-  <si>
-    <t>M02T105L03603</t>
-  </si>
-  <si>
-    <t>M02T083LA3601</t>
-  </si>
-  <si>
-    <t>M02T083LB4602</t>
-  </si>
-  <si>
-    <t>M04D002LF4602</t>
-  </si>
-  <si>
-    <t>M04B009LA5602</t>
-  </si>
-  <si>
-    <t>M04B009LA5601</t>
-  </si>
-  <si>
-    <t>M04D002LH2602</t>
-  </si>
-  <si>
-    <t>M04D002LG2601</t>
-  </si>
-  <si>
-    <t>M06L004L13601</t>
-  </si>
-  <si>
-    <t>M04D002LF4601</t>
-  </si>
-  <si>
-    <t>M04D002LB4601</t>
-  </si>
-  <si>
-    <t>M04A002LB2601</t>
-  </si>
-  <si>
-    <t>M04L002L14601</t>
-  </si>
-  <si>
-    <t>M04D002LD4601</t>
-  </si>
-  <si>
-    <t>M04D002LM2604</t>
-  </si>
-  <si>
-    <t>M04D002LI2602</t>
-  </si>
-  <si>
-    <t>M04D002LI2601</t>
-  </si>
-  <si>
-    <t>M02U043L62601</t>
-  </si>
-  <si>
-    <t>M02U043L92601</t>
-  </si>
-  <si>
-    <t>M02U043L42601</t>
-  </si>
-  <si>
-    <t>M02Q048L33603</t>
-  </si>
-  <si>
-    <t>M02Q047L14602</t>
-  </si>
-  <si>
-    <t>M02Q047L24604</t>
-  </si>
-  <si>
-    <t>M02Q047L24603</t>
-  </si>
-  <si>
-    <t>M04L005601</t>
-  </si>
-  <si>
-    <t>M04D001LA2601</t>
-  </si>
-  <si>
-    <t>M04L003L33601</t>
-  </si>
-  <si>
-    <t>M04L004601</t>
-  </si>
-  <si>
-    <t>M02P089L03501</t>
-  </si>
-  <si>
-    <t>M02P088L03501</t>
-  </si>
-  <si>
-    <t>M02Q050L01604</t>
-  </si>
-  <si>
-    <t>M02Q053L01601</t>
-  </si>
-  <si>
-    <t>M02Q068L24601</t>
-  </si>
-  <si>
-    <t>M02Q068L14601</t>
-  </si>
-  <si>
-    <t>M02Q068L01602</t>
-  </si>
-  <si>
-    <t>M02Q048L33602</t>
-  </si>
-  <si>
-    <t>M02T106L03602</t>
-  </si>
-  <si>
-    <t>M02M039L23601</t>
-  </si>
-  <si>
-    <t>M02M039L20602</t>
-  </si>
-  <si>
-    <t>M02T105L03602</t>
-  </si>
-  <si>
-    <t>M02T106L03601</t>
-  </si>
-  <si>
-    <t>M02T105L03601</t>
-  </si>
-  <si>
-    <t>M02L008L11601</t>
-  </si>
-  <si>
-    <t>M02M040L53601</t>
-  </si>
-  <si>
-    <t>M02Q068L01601</t>
-  </si>
-  <si>
-    <t>M02Q068L34601</t>
-  </si>
-  <si>
-    <t>M02T083LB4601</t>
-  </si>
-  <si>
-    <t>M02M039L20601</t>
-  </si>
-  <si>
-    <t>M02M021L23601</t>
-  </si>
-  <si>
-    <t>M02Q050L01603</t>
-  </si>
-  <si>
-    <t>M02Q050L24603</t>
-  </si>
-  <si>
-    <t>M02Q050L24602</t>
-  </si>
-  <si>
-    <t>M02Q050L34601</t>
-  </si>
-  <si>
-    <t>M0601602</t>
-  </si>
-  <si>
-    <t>M04L002L23602</t>
-  </si>
-  <si>
-    <t>M02Q047L14601</t>
-  </si>
-  <si>
-    <t>M02Q047LA5601</t>
-  </si>
-  <si>
-    <t>M02Q047L24602</t>
-  </si>
-  <si>
-    <t>M04D002LM2602</t>
-  </si>
-  <si>
-    <t>M04L002L23601</t>
-  </si>
-  <si>
-    <t>M04A002LA0602</t>
-  </si>
-  <si>
-    <t>M02Q048L13601</t>
-  </si>
-  <si>
-    <t>M02Q048L33601</t>
-  </si>
-  <si>
-    <t>M04D002LH2601</t>
-  </si>
-  <si>
-    <t>M0601601</t>
-  </si>
-  <si>
-    <t>M04A002LA0601</t>
-  </si>
-  <si>
-    <t>M04D002LM2601</t>
-  </si>
-  <si>
-    <t>M02Q050L01602</t>
-  </si>
-  <si>
-    <t>M02Q050L01601</t>
-  </si>
-  <si>
-    <t>M0601501</t>
-  </si>
-  <si>
-    <t>M02Q050L24601</t>
-  </si>
-  <si>
-    <t>M02Q047LA5504</t>
-  </si>
-  <si>
-    <t>M02Q047L24513</t>
-  </si>
-  <si>
-    <t>M02Q048L33515</t>
-  </si>
-  <si>
-    <t>M02Q048L13504</t>
-  </si>
-  <si>
-    <t>M0240501</t>
-  </si>
-  <si>
-    <t>M02Q050L01526</t>
-  </si>
-  <si>
-    <t>M02Q053L01506</t>
-  </si>
-  <si>
-    <t>M02Q047L24512</t>
-  </si>
-  <si>
-    <t>M02Q047LA5503</t>
-  </si>
-  <si>
-    <t>M02Q068L01507</t>
-  </si>
-  <si>
-    <t>M02Q050L01525</t>
-  </si>
-  <si>
-    <t>M02Q053L01505</t>
-  </si>
-  <si>
-    <t>M02Q048L33514</t>
-  </si>
-  <si>
-    <t>M02Q048L33513</t>
-  </si>
-  <si>
-    <t>M02T106L03505</t>
-  </si>
-  <si>
-    <t>M02T105L03506</t>
-  </si>
-  <si>
-    <t>M02L008L11501</t>
-  </si>
-  <si>
-    <t>M02M075L02502</t>
-  </si>
-  <si>
-    <t>M02M021L23504</t>
-  </si>
-  <si>
-    <t>M02T083LB4503</t>
-  </si>
-  <si>
-    <t>M02T083LA3507</t>
-  </si>
-  <si>
-    <t>M02Q047LA5502</t>
-  </si>
-  <si>
-    <t>M02Q050L01524</t>
-  </si>
-  <si>
-    <t>M02Q050L24504</t>
-  </si>
-  <si>
-    <t>M02Q048L33512</t>
-  </si>
-  <si>
-    <t>M02Q068L24502</t>
-  </si>
-  <si>
-    <t>M02Q068L14501</t>
-  </si>
-  <si>
-    <t>M02Q050L01522</t>
-  </si>
-  <si>
-    <t>M02Q053L01504</t>
-  </si>
-  <si>
-    <t>M02Q068L01506</t>
-  </si>
-  <si>
-    <t>M02Q047L24511</t>
-  </si>
-  <si>
-    <t>M02Q047LA5501</t>
-  </si>
-  <si>
-    <t>M0247518</t>
-  </si>
-  <si>
-    <t>M02Q047L24510</t>
-  </si>
-  <si>
-    <t>M02M022L02503</t>
-  </si>
-  <si>
-    <t>M02M040L33502</t>
-  </si>
-  <si>
-    <t>M02M040L13501</t>
-  </si>
-  <si>
-    <t>M02M040L23501</t>
-  </si>
-  <si>
-    <t>M02M078L02503</t>
-  </si>
-  <si>
-    <t>M02M110L03502</t>
-  </si>
-  <si>
-    <t>M02Q053L01503</t>
-  </si>
-  <si>
-    <t>M02Q048501</t>
-  </si>
-  <si>
-    <t>M02Q048L33511</t>
-  </si>
-  <si>
-    <t>M02M109L03502</t>
-  </si>
-  <si>
-    <t>M02Q049L01504</t>
-  </si>
-  <si>
-    <t>M0247517</t>
-  </si>
-  <si>
-    <t>M02Q047L24509</t>
-  </si>
-  <si>
-    <t>M02Q047L24508</t>
-  </si>
-  <si>
-    <t>M02Q047L14506</t>
-  </si>
-  <si>
-    <t>M02Q048L33510</t>
-  </si>
-  <si>
-    <t>M02Q050L24503</t>
-  </si>
-  <si>
-    <t>M02M039L20505</t>
-  </si>
-  <si>
-    <t>M02M022L02502</t>
-  </si>
-  <si>
-    <t>M02Q050L01521</t>
-  </si>
-  <si>
-    <t>M02Q050L34502</t>
-  </si>
-  <si>
-    <t>M0247516</t>
-  </si>
-  <si>
-    <t>M02Q047L24507</t>
-  </si>
-  <si>
-    <t>M02Q047L24506</t>
-  </si>
-  <si>
-    <t>M02M039L20504</t>
-  </si>
-  <si>
-    <t>M02Q050L34501</t>
-  </si>
-  <si>
-    <t>M02Q050L24501</t>
-  </si>
-  <si>
-    <t>M02Q050L01520</t>
-  </si>
-  <si>
-    <t>M02Q047L24505</t>
-  </si>
-  <si>
-    <t>M02Q047L14505</t>
-  </si>
-  <si>
-    <t>M0247515</t>
-  </si>
-  <si>
-    <t>M02Q047L24504</t>
-  </si>
-  <si>
-    <t>M02Q048L13503</t>
-  </si>
-  <si>
-    <t>M02Q048L33509</t>
-  </si>
-  <si>
-    <t>M02Q048L33508</t>
-  </si>
-  <si>
-    <t>M02Q047L14504</t>
-  </si>
-  <si>
-    <t>M04B009LA5501</t>
-  </si>
-  <si>
-    <t>M02M021L23503</t>
-  </si>
-  <si>
-    <t>M02Q053L01502</t>
-  </si>
-  <si>
-    <t>M02Q048L13502</t>
-  </si>
-  <si>
-    <t>M02Q048L33507</t>
-  </si>
-  <si>
-    <t>M02T083LB4502</t>
-  </si>
-  <si>
-    <t>M02Q048L33506</t>
-  </si>
-  <si>
-    <t>M02Q048L13501</t>
-  </si>
-  <si>
-    <t>M02Q048L23502</t>
-  </si>
-  <si>
-    <t>M02Q047L24503</t>
-  </si>
-  <si>
-    <t>M0247514</t>
-  </si>
-  <si>
-    <t>M02Q048L33505</t>
-  </si>
-  <si>
-    <t>M02Q047L14503</t>
-  </si>
-  <si>
-    <t>M02Q068L01505</t>
-  </si>
-  <si>
-    <t>M02Q050L01519</t>
-  </si>
-  <si>
-    <t>M02M039L20503</t>
-  </si>
-  <si>
-    <t>M02T083LA3506</t>
-  </si>
-  <si>
-    <t>M02Q068L01504</t>
-  </si>
-  <si>
-    <t>M02T059LB3503</t>
-  </si>
-  <si>
-    <t>M02T059LA3502</t>
-  </si>
-  <si>
-    <t>M02T106L03504</t>
-  </si>
-  <si>
-    <t>16-04-2026</t>
-  </si>
-  <si>
-    <t>10-04-2026</t>
-  </si>
-  <si>
-    <t>09-04-2026</t>
-  </si>
-  <si>
-    <t>06-04-2026</t>
-  </si>
-  <si>
-    <t>07-04-2026</t>
-  </si>
-  <si>
-    <t>02-04-2026</t>
-  </si>
-  <si>
-    <t>31-03-2026</t>
-  </si>
-  <si>
-    <t>24-03-2026</t>
-  </si>
-  <si>
-    <t>23-03-2026</t>
-  </si>
-  <si>
-    <t>20-03-2026</t>
-  </si>
-  <si>
-    <t>19-03-2026</t>
-  </si>
-  <si>
-    <t>18-03-2026</t>
-  </si>
-  <si>
-    <t>17-03-2026</t>
-  </si>
-  <si>
-    <t>13-03-2026</t>
-  </si>
-  <si>
-    <t>12-03-2026</t>
-  </si>
-  <si>
-    <t>09-03-2026</t>
-  </si>
-  <si>
-    <t>26-02-2026</t>
-  </si>
-  <si>
-    <t>25-02-2026</t>
-  </si>
-  <si>
-    <t>20-12-2025</t>
-  </si>
-  <si>
-    <t>24-02-2026</t>
-  </si>
-  <si>
-    <t>23-02-2026</t>
-  </si>
-  <si>
-    <t>20-02-2026</t>
-  </si>
-  <si>
-    <t>16-02-2026</t>
-  </si>
-  <si>
-    <t>12-02-2026</t>
-  </si>
-  <si>
-    <t>11-02-2026</t>
-  </si>
-  <si>
-    <t>10-02-2026</t>
-  </si>
-  <si>
-    <t>06-02-2026</t>
-  </si>
-  <si>
-    <t>05-02-2026</t>
-  </si>
-  <si>
-    <t>02-02-2026</t>
-  </si>
-  <si>
-    <t>28-01-2026</t>
-  </si>
-  <si>
-    <t>29-01-2026</t>
-  </si>
-  <si>
-    <t>26-01-2026</t>
-  </si>
-  <si>
-    <t>19-01-2026</t>
-  </si>
-  <si>
-    <t>15-01-2026</t>
-  </si>
-  <si>
-    <t>14-01-2026</t>
-  </si>
-  <si>
-    <t>13-01-2026</t>
-  </si>
-  <si>
-    <t>08-01-2026</t>
-  </si>
-  <si>
-    <t>05-01-2026</t>
-  </si>
-  <si>
-    <t>24-12-2025</t>
-  </si>
-  <si>
-    <t>29-12-2025</t>
-  </si>
-  <si>
-    <t>30-12-2025</t>
-  </si>
-  <si>
-    <t>27-12-2025</t>
-  </si>
-  <si>
-    <t>26-12-2025</t>
-  </si>
-  <si>
-    <t>23-12-2025</t>
-  </si>
-  <si>
-    <t>22-12-2025</t>
-  </si>
-  <si>
-    <t>18-12-2025</t>
-  </si>
-  <si>
-    <t>17-12-2025</t>
-  </si>
-  <si>
-    <t>16-12-2025</t>
-  </si>
-  <si>
-    <t>15-12-2025</t>
-  </si>
-  <si>
-    <t>05-12-2025</t>
-  </si>
-  <si>
-    <t>12-12-2025</t>
-  </si>
-  <si>
-    <t>10-12-2025</t>
-  </si>
-  <si>
-    <t>04-12-2025</t>
-  </si>
-  <si>
-    <t>24-11-2025</t>
-  </si>
-  <si>
-    <t>18-11-2025</t>
-  </si>
-  <si>
-    <t>17-11-2025</t>
-  </si>
-  <si>
-    <t>13-11-2025</t>
-  </si>
-  <si>
-    <t>12-11-2025</t>
-  </si>
-  <si>
-    <t>11-11-2025</t>
-  </si>
-  <si>
-    <t>10-11-2025</t>
-  </si>
-  <si>
-    <t>06-11-2025</t>
-  </si>
-  <si>
-    <t>05-11-2025</t>
-  </si>
-  <si>
-    <t>04-11-2025</t>
-  </si>
-  <si>
-    <t>03-11-2025</t>
-  </si>
-  <si>
-    <t>30-10-2025</t>
-  </si>
-  <si>
-    <t>31-10-2025</t>
-  </si>
-  <si>
-    <t>29-10-2025</t>
-  </si>
-  <si>
-    <t>27-10-2025</t>
-  </si>
-  <si>
-    <t>20-10-2025</t>
-  </si>
-  <si>
-    <t>17-10-2025</t>
-  </si>
-  <si>
-    <t>16-10-2025</t>
-  </si>
-  <si>
-    <t>15-10-2025</t>
-  </si>
-  <si>
-    <t>14-10-2025</t>
-  </si>
-  <si>
-    <t>13-10-2025</t>
-  </si>
-  <si>
-    <t>24-09-2025</t>
-  </si>
-  <si>
-    <t>23-09-2025</t>
-  </si>
-  <si>
-    <t>18-09-2025</t>
-  </si>
-  <si>
-    <t>16-09-2025</t>
-  </si>
-  <si>
-    <t>15-09-2025</t>
-  </si>
-  <si>
-    <t>09-09-2025</t>
-  </si>
-  <si>
-    <t>08-09-2025</t>
-  </si>
-  <si>
-    <t>05-09-2025</t>
-  </si>
-  <si>
-    <t>04-09-2025</t>
-  </si>
-  <si>
-    <t>03-09-2025</t>
-  </si>
-  <si>
-    <t>02-09-2025</t>
-  </si>
-  <si>
-    <t>01-09-2025</t>
-  </si>
-  <si>
-    <t>28-08-2025</t>
-  </si>
-  <si>
-    <t>21-08-2025</t>
-  </si>
-  <si>
-    <t>Arándano</t>
-  </si>
-  <si>
-    <t>Avellano</t>
-  </si>
-  <si>
-    <t>Cerezo</t>
-  </si>
-  <si>
-    <t>02T106L03</t>
-  </si>
-  <si>
-    <t>02L008L11</t>
-  </si>
-  <si>
-    <t>02N042LB5</t>
-  </si>
-  <si>
-    <t>02N042LA5</t>
-  </si>
-  <si>
-    <t>02N042LC5</t>
-  </si>
-  <si>
-    <t>02T118LB5</t>
-  </si>
-  <si>
-    <t>02T114LA5</t>
-  </si>
-  <si>
-    <t>02T113LA5</t>
-  </si>
-  <si>
-    <t>02T119LA5</t>
-  </si>
-  <si>
-    <t>02T118LA5</t>
-  </si>
-  <si>
-    <t>02Q048L33</t>
-  </si>
-  <si>
-    <t>02Q047L24</t>
-  </si>
-  <si>
-    <t>02Q047LA5</t>
-  </si>
-  <si>
-    <t>02M039L20</t>
-  </si>
-  <si>
-    <t>02T105L03</t>
-  </si>
-  <si>
-    <t>02T083LA3</t>
-  </si>
-  <si>
-    <t>02T083LB4</t>
-  </si>
-  <si>
-    <t>04D002LF4</t>
-  </si>
-  <si>
-    <t>04B009LA5</t>
-  </si>
-  <si>
-    <t>04D002LH2</t>
-  </si>
-  <si>
-    <t>04D002LG2</t>
-  </si>
-  <si>
-    <t>06L004L13</t>
-  </si>
-  <si>
-    <t>04D002LB4</t>
-  </si>
-  <si>
-    <t>04A002LB2</t>
-  </si>
-  <si>
-    <t>04L002L14</t>
-  </si>
-  <si>
-    <t>04D002LD4</t>
-  </si>
-  <si>
-    <t>04D002LM2</t>
-  </si>
-  <si>
-    <t>04D002LI2</t>
-  </si>
-  <si>
-    <t>02U043L62</t>
-  </si>
-  <si>
-    <t>02U043L92</t>
-  </si>
-  <si>
-    <t>02U043L42</t>
-  </si>
-  <si>
-    <t>02Q047L14</t>
-  </si>
-  <si>
-    <t>04L005</t>
-  </si>
-  <si>
-    <t>04D001LA2</t>
-  </si>
-  <si>
-    <t>04L003L33</t>
-  </si>
-  <si>
-    <t>04L004</t>
-  </si>
-  <si>
-    <t>02P089L03</t>
-  </si>
-  <si>
-    <t>02P088L03</t>
-  </si>
-  <si>
-    <t>02Q050L01</t>
-  </si>
-  <si>
-    <t>02Q053L01</t>
-  </si>
-  <si>
-    <t>02Q068L24</t>
-  </si>
-  <si>
-    <t>02Q068L14</t>
-  </si>
-  <si>
-    <t>02Q068L01</t>
-  </si>
-  <si>
-    <t>02M039L23</t>
-  </si>
-  <si>
-    <t>02M040L53</t>
-  </si>
-  <si>
-    <t>02Q068L34</t>
-  </si>
-  <si>
-    <t>02M021L23</t>
-  </si>
-  <si>
-    <t>02Q050L24</t>
-  </si>
-  <si>
-    <t>02Q050L34</t>
-  </si>
-  <si>
-    <t>0601</t>
-  </si>
-  <si>
-    <t>04L002L23</t>
-  </si>
-  <si>
-    <t>04A002LA0</t>
-  </si>
-  <si>
-    <t>02Q048L13</t>
-  </si>
-  <si>
-    <t>0240</t>
-  </si>
-  <si>
-    <t>02M075L02</t>
-  </si>
-  <si>
-    <t>0247</t>
-  </si>
-  <si>
-    <t>02M022L02</t>
-  </si>
-  <si>
-    <t>02M040L33</t>
-  </si>
-  <si>
-    <t>02M040L13</t>
-  </si>
-  <si>
-    <t>02M040L23</t>
-  </si>
-  <si>
-    <t>02M078L02</t>
-  </si>
-  <si>
-    <t>02M110L03</t>
-  </si>
-  <si>
-    <t>02Q048</t>
-  </si>
-  <si>
-    <t>02M109L03</t>
-  </si>
-  <si>
-    <t>02Q049L01</t>
-  </si>
-  <si>
-    <t>02Q048L23</t>
-  </si>
-  <si>
-    <t>02T059LB3</t>
-  </si>
-  <si>
-    <t>02T059LA3</t>
-  </si>
-  <si>
-    <t>NO LMC ( 100% )</t>
-  </si>
-  <si>
-    <t>920</t>
-  </si>
-  <si>
-    <t>3.000</t>
-  </si>
-  <si>
-    <t>656</t>
-  </si>
-  <si>
-    <t>2.168</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>204</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>18.408</t>
-  </si>
-  <si>
-    <t>7.656</t>
-  </si>
-  <si>
-    <t>960</t>
-  </si>
-  <si>
-    <t>30.840</t>
-  </si>
-  <si>
-    <t>12.000</t>
-  </si>
-  <si>
-    <t>620</t>
-  </si>
-  <si>
-    <t>3.318</t>
-  </si>
-  <si>
-    <t>2.836</t>
-  </si>
-  <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>1.039</t>
-  </si>
-  <si>
-    <t>690</t>
-  </si>
-  <si>
-    <t>1.223</t>
-  </si>
-  <si>
-    <t>700</t>
-  </si>
-  <si>
-    <t>3.916</t>
-  </si>
-  <si>
-    <t>2.788</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>345</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>4.395</t>
-  </si>
-  <si>
-    <t>360</t>
-  </si>
-  <si>
-    <t>4.287</t>
-  </si>
-  <si>
-    <t>500</t>
-  </si>
-  <si>
-    <t>1.523</t>
-  </si>
-  <si>
-    <t>1.424</t>
-  </si>
-  <si>
-    <t>24.120</t>
+    <t>3.540</t>
+  </si>
+  <si>
+    <t>464</t>
+  </si>
+  <si>
+    <t>2.135</t>
+  </si>
+  <si>
+    <t>2.190</t>
+  </si>
+  <si>
+    <t>17.923</t>
+  </si>
+  <si>
+    <t>11.011</t>
+  </si>
+  <si>
+    <t>7.518</t>
+  </si>
+  <si>
+    <t>552</t>
+  </si>
+  <si>
+    <t>4.867</t>
+  </si>
+  <si>
+    <t>16.192</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1.152</t>
+  </si>
+  <si>
+    <t>93.728</t>
+  </si>
+  <si>
+    <t>2.211</t>
+  </si>
+  <si>
+    <t>13.605</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>13.128</t>
+  </si>
+  <si>
+    <t>54.862</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>15.591</t>
+  </si>
+  <si>
+    <t>10.238</t>
+  </si>
+  <si>
+    <t>3.635</t>
+  </si>
+  <si>
+    <t>580</t>
+  </si>
+  <si>
+    <t>3.505</t>
+  </si>
+  <si>
+    <t>2.777</t>
+  </si>
+  <si>
+    <t>12.408</t>
+  </si>
+  <si>
+    <t>5.856</t>
+  </si>
+  <si>
+    <t>21.024</t>
+  </si>
+  <si>
+    <t>14.356</t>
+  </si>
+  <si>
+    <t>1.248</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>8.124</t>
+  </si>
+  <si>
+    <t>4.680</t>
+  </si>
+  <si>
+    <t>6.480</t>
+  </si>
+  <si>
+    <t>1.056</t>
+  </si>
+  <si>
+    <t>648</t>
+  </si>
+  <si>
+    <t>9.642</t>
+  </si>
+  <si>
+    <t>6.264</t>
+  </si>
+  <si>
+    <t>16.032</t>
+  </si>
+  <si>
+    <t>528</t>
+  </si>
+  <si>
+    <t>3.887</t>
   </si>
   <si>
     <t>408</t>
   </si>
   <si>
-    <t>40.200</t>
-  </si>
-  <si>
-    <t>67.488</t>
-  </si>
-  <si>
-    <t>1.068</t>
-  </si>
-  <si>
-    <t>5.443</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>3.108</t>
-  </si>
-  <si>
-    <t>480</t>
-  </si>
-  <si>
-    <t>470</t>
-  </si>
-  <si>
-    <t>2.012</t>
-  </si>
-  <si>
-    <t>2.760</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>1.073</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>2.832</t>
-  </si>
-  <si>
-    <t>3.308</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>8.381</t>
-  </si>
-  <si>
-    <t>45.322</t>
-  </si>
-  <si>
-    <t>27.100</t>
-  </si>
-  <si>
-    <t>3.569</t>
-  </si>
-  <si>
-    <t>477</t>
-  </si>
-  <si>
-    <t>2.160</t>
-  </si>
-  <si>
-    <t>2.316</t>
-  </si>
-  <si>
-    <t>18.360</t>
-  </si>
-  <si>
-    <t>11.011</t>
-  </si>
-  <si>
-    <t>7.518</t>
-  </si>
-  <si>
-    <t>552</t>
-  </si>
-  <si>
-    <t>4.867</t>
-  </si>
-  <si>
-    <t>16.192</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1.152</t>
-  </si>
-  <si>
-    <t>100.232</t>
-  </si>
-  <si>
-    <t>2.211</t>
-  </si>
-  <si>
-    <t>13.605</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>2.358</t>
-  </si>
-  <si>
-    <t>64.800</t>
-  </si>
-  <si>
-    <t>54.862</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>15.591</t>
-  </si>
-  <si>
-    <t>10.238</t>
-  </si>
-  <si>
-    <t>3.635</t>
-  </si>
-  <si>
-    <t>580</t>
-  </si>
-  <si>
-    <t>3.505</t>
-  </si>
-  <si>
-    <t>2.777</t>
-  </si>
-  <si>
-    <t>12.408</t>
-  </si>
-  <si>
-    <t>5.856</t>
-  </si>
-  <si>
-    <t>21.024</t>
-  </si>
-  <si>
-    <t>14.356</t>
-  </si>
-  <si>
-    <t>1.248</t>
-  </si>
-  <si>
-    <t>258</t>
-  </si>
-  <si>
-    <t>5.731</t>
-  </si>
-  <si>
-    <t>67.416</t>
-  </si>
-  <si>
-    <t>4.680</t>
-  </si>
-  <si>
-    <t>6.480</t>
-  </si>
-  <si>
-    <t>1.056</t>
-  </si>
-  <si>
-    <t>648</t>
-  </si>
-  <si>
-    <t>9.642</t>
-  </si>
-  <si>
-    <t>6.264</t>
-  </si>
-  <si>
-    <t>16.032</t>
-  </si>
-  <si>
-    <t>528</t>
-  </si>
-  <si>
-    <t>126.669</t>
-  </si>
-  <si>
-    <t>2.083</t>
+    <t>1.741</t>
   </si>
   <si>
     <t>1.392</t>
@@ -1891,7 +1900,7 @@
     <t>4.256</t>
   </si>
   <si>
-    <t>136.267</t>
+    <t>104.301</t>
   </si>
   <si>
     <t>1.032</t>
@@ -1927,7 +1936,7 @@
     <t>2.726</t>
   </si>
   <si>
-    <t>9.446</t>
+    <t>7.746</t>
   </si>
   <si>
     <t>3.864</t>
@@ -1936,10 +1945,10 @@
     <t>151</t>
   </si>
   <si>
-    <t>4.240</t>
-  </si>
-  <si>
-    <t>5.194</t>
+    <t>3.740</t>
+  </si>
+  <si>
+    <t>5.049</t>
   </si>
   <si>
     <t>39.996</t>
@@ -1999,25 +2008,13 @@
     <t>3.168</t>
   </si>
   <si>
-    <t>2.713</t>
+    <t>713</t>
   </si>
   <si>
     <t>7.850</t>
   </si>
   <si>
     <t>2.649</t>
-  </si>
-  <si>
-    <t>4.010</t>
-  </si>
-  <si>
-    <t>2.200</t>
-  </si>
-  <si>
-    <t>2.229</t>
-  </si>
-  <si>
-    <t>3.004</t>
   </si>
   <si>
     <t>NO</t>
@@ -2355,7 +2352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I179"/>
+  <dimension ref="A1:I178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2392,28 +2389,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="H2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2421,28 +2418,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D3" t="s">
         <v>453</v>
       </c>
       <c r="E3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F3" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G3" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="H3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2450,28 +2447,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D4" t="s">
         <v>453</v>
       </c>
       <c r="E4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F4" t="s">
+        <v>521</v>
+      </c>
+      <c r="G4" t="s">
         <v>524</v>
       </c>
-      <c r="G4" t="s">
-        <v>527</v>
-      </c>
       <c r="H4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2479,28 +2476,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D5" t="s">
         <v>453</v>
       </c>
       <c r="E5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G5" t="s">
-        <v>65</v>
+        <v>525</v>
       </c>
       <c r="H5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2508,28 +2505,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D6" t="s">
         <v>453</v>
       </c>
       <c r="E6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F6" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H6" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I6" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2537,28 +2534,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D7" t="s">
         <v>453</v>
       </c>
       <c r="E7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F7" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G7" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H7" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2566,28 +2563,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D8" t="s">
         <v>453</v>
       </c>
       <c r="E8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F8" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G8" t="s">
-        <v>530</v>
+        <v>68</v>
       </c>
       <c r="H8" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I8" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2595,28 +2592,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D9" t="s">
         <v>453</v>
       </c>
       <c r="E9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F9" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G9" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H9" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I9" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2624,7 +2621,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C10" t="s">
         <v>368</v>
@@ -2633,19 +2630,19 @@
         <v>453</v>
       </c>
       <c r="E10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F10" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G10" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="H10" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I10" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2653,7 +2650,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C11" t="s">
         <v>368</v>
@@ -2662,19 +2659,19 @@
         <v>453</v>
       </c>
       <c r="E11" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F11" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G11" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="H11" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I11" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2682,28 +2679,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D12" t="s">
         <v>453</v>
       </c>
       <c r="E12" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F12" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G12" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="H12" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I12" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2711,7 +2708,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C13" t="s">
         <v>368</v>
@@ -2720,19 +2717,19 @@
         <v>453</v>
       </c>
       <c r="E13" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F13" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G13" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="H13" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I13" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2740,28 +2737,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C14" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D14" t="s">
         <v>453</v>
       </c>
       <c r="E14" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F14" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G14" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="H14" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I14" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2769,28 +2766,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C15" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D15" t="s">
         <v>453</v>
       </c>
       <c r="E15" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F15" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G15" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="H15" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I15" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2798,10 +2795,10 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C16" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D16" t="s">
         <v>453</v>
@@ -2810,16 +2807,16 @@
         <v>469</v>
       </c>
       <c r="F16" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G16" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="H16" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I16" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -2827,28 +2824,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C17" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D17" t="s">
         <v>453</v>
       </c>
       <c r="E17" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="F17" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G17" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="H17" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I17" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2856,28 +2853,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C18" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D18" t="s">
         <v>453</v>
       </c>
       <c r="E18" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F18" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G18" t="s">
-        <v>154</v>
+        <v>537</v>
       </c>
       <c r="H18" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I18" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -2885,7 +2882,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C19" t="s">
         <v>372</v>
@@ -2894,19 +2891,19 @@
         <v>453</v>
       </c>
       <c r="E19" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="F19" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G19" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="H19" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I19" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2914,7 +2911,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C20" t="s">
         <v>372</v>
@@ -2923,19 +2920,19 @@
         <v>453</v>
       </c>
       <c r="E20" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="F20" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G20" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="H20" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I20" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -2943,28 +2940,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C21" t="s">
         <v>372</v>
       </c>
       <c r="D21" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E21" t="s">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="F21" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G21" t="s">
-        <v>542</v>
+        <v>157</v>
       </c>
       <c r="H21" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I21" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -2972,28 +2969,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C22" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D22" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E22" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F22" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G22" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="H22" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I22" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -3001,28 +2998,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C23" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D23" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E23" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F23" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G23" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H23" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -3030,28 +3027,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C24" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D24" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E24" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F24" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G24" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="H24" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I24" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -3059,28 +3056,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C25" t="s">
         <v>373</v>
       </c>
       <c r="D25" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E25" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F25" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G25" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H25" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I25" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -3088,28 +3085,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C26" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D26" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E26" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F26" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G26" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H26" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I26" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -3117,28 +3114,28 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D27" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E27" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F27" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G27" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="H27" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I27" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -3146,28 +3143,28 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C28" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D28" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E28" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F28" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G28" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="H28" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I28" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -3175,7 +3172,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C29" t="s">
         <v>374</v>
@@ -3184,19 +3181,19 @@
         <v>454</v>
       </c>
       <c r="E29" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F29" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G29" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H29" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I29" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -3204,28 +3201,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C30" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D30" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E30" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F30" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G30" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="H30" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I30" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -3233,28 +3230,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C31" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D31" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E31" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F31" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G31" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H31" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I31" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -3262,28 +3259,28 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C32" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D32" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E32" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F32" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G32" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H32" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I32" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -3291,28 +3288,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C33" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D33" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E33" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F33" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G33" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H33" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I33" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -3320,28 +3317,28 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C34" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D34" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E34" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F34" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G34" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="H34" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I34" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -3349,28 +3346,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C35" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D35" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E35" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F35" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G35" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H35" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I35" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -3378,28 +3375,28 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C36" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D36" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E36" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="F36" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G36" t="s">
-        <v>118</v>
+        <v>554</v>
       </c>
       <c r="H36" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I36" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -3407,28 +3404,28 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C37" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D37" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E37" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="F37" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G37" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="H37" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I37" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -3436,28 +3433,28 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C38" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D38" t="s">
         <v>453</v>
       </c>
       <c r="E38" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="F38" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="H38" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I38" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -3465,28 +3462,28 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C39" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D39" t="s">
         <v>453</v>
       </c>
       <c r="E39" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F39" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G39" t="s">
-        <v>559</v>
+        <v>121</v>
       </c>
       <c r="H39" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I39" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -3494,28 +3491,28 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C40" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D40" t="s">
         <v>453</v>
       </c>
       <c r="E40" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="F40" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G40" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="H40" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I40" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -3523,28 +3520,28 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C41" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D41" t="s">
         <v>453</v>
       </c>
       <c r="E41" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F41" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G41" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="H41" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I41" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -3552,28 +3549,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C42" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D42" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E42" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F42" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G42" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="H42" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I42" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -3581,28 +3578,28 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C43" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D43" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E43" t="s">
-        <v>489</v>
+        <v>469</v>
       </c>
       <c r="F43" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G43" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="H43" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I43" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -3610,28 +3607,28 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C44" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D44" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E44" t="s">
-        <v>490</v>
+        <v>469</v>
       </c>
       <c r="F44" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G44" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="H44" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I44" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -3639,28 +3636,28 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C45" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D45" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E45" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="F45" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G45" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="H45" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I45" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -3668,28 +3665,28 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C46" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D46" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E46" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F46" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G46" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="H46" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I46" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -3697,28 +3694,28 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C47" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D47" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E47" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="F47" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G47" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="H47" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I47" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -3726,28 +3723,28 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C48" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D48" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E48" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="F48" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G48" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="H48" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I48" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -3755,28 +3752,28 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C49" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D49" t="s">
         <v>453</v>
       </c>
       <c r="E49" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="F49" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G49" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="H49" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I49" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -3784,28 +3781,28 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C50" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D50" t="s">
         <v>453</v>
       </c>
       <c r="E50" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="F50" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G50" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="H50" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I50" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -3813,7 +3810,7 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C51" t="s">
         <v>384</v>
@@ -3822,19 +3819,19 @@
         <v>453</v>
       </c>
       <c r="E51" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="F51" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G51" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="H51" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I51" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -3842,7 +3839,7 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C52" t="s">
         <v>384</v>
@@ -3851,19 +3848,19 @@
         <v>453</v>
       </c>
       <c r="E52" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="F52" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G52" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="H52" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I52" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -3871,28 +3868,28 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D53" t="s">
         <v>453</v>
       </c>
       <c r="E53" t="s">
-        <v>466</v>
+        <v>495</v>
       </c>
       <c r="F53" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G53" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H53" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I53" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -3900,28 +3897,28 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C54" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D54" t="s">
         <v>453</v>
       </c>
       <c r="E54" t="s">
-        <v>456</v>
+        <v>496</v>
       </c>
       <c r="F54" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G54" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="H54" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I54" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -3929,28 +3926,28 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C55" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D55" t="s">
         <v>453</v>
       </c>
       <c r="E55" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F55" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G55" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="H55" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I55" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -3958,7 +3955,7 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C56" t="s">
         <v>385</v>
@@ -3967,19 +3964,19 @@
         <v>453</v>
       </c>
       <c r="E56" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F56" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G56" t="s">
-        <v>149</v>
+        <v>573</v>
       </c>
       <c r="H56" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I56" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -3987,28 +3984,28 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C57" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D57" t="s">
         <v>453</v>
       </c>
       <c r="E57" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="F57" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G57" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H57" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I57" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -4016,28 +4013,28 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C58" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D58" t="s">
         <v>453</v>
       </c>
       <c r="E58" t="s">
-        <v>456</v>
+        <v>498</v>
       </c>
       <c r="F58" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G58" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H58" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I58" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -4045,28 +4042,28 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C59" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D59" t="s">
         <v>453</v>
       </c>
       <c r="E59" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="F59" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G59" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H59" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I59" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -4074,28 +4071,28 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C60" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D60" t="s">
         <v>453</v>
       </c>
       <c r="E60" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F60" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G60" t="s">
-        <v>183</v>
+        <v>577</v>
       </c>
       <c r="H60" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I60" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -4103,28 +4100,28 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C61" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D61" t="s">
         <v>453</v>
       </c>
       <c r="E61" t="s">
-        <v>500</v>
+        <v>457</v>
       </c>
       <c r="F61" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G61" t="s">
-        <v>526</v>
+        <v>578</v>
       </c>
       <c r="H61" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I61" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -4132,28 +4129,28 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C62" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D62" t="s">
         <v>453</v>
       </c>
       <c r="E62" t="s">
-        <v>498</v>
+        <v>456</v>
       </c>
       <c r="F62" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G62" t="s">
         <v>579</v>
       </c>
       <c r="H62" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I62" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -4161,7 +4158,7 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C63" t="s">
         <v>389</v>
@@ -4170,19 +4167,19 @@
         <v>453</v>
       </c>
       <c r="E63" t="s">
-        <v>501</v>
+        <v>458</v>
       </c>
       <c r="F63" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G63" t="s">
         <v>580</v>
       </c>
       <c r="H63" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I63" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -4190,7 +4187,7 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C64" t="s">
         <v>389</v>
@@ -4199,19 +4196,19 @@
         <v>453</v>
       </c>
       <c r="E64" t="s">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="F64" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G64" t="s">
-        <v>581</v>
+        <v>525</v>
       </c>
       <c r="H64" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I64" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -4219,28 +4216,28 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C65" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D65" t="s">
         <v>453</v>
       </c>
       <c r="E65" t="s">
-        <v>469</v>
+        <v>497</v>
       </c>
       <c r="F65" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G65" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H65" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I65" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -4248,28 +4245,28 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C66" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D66" t="s">
         <v>453</v>
       </c>
       <c r="E66" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F66" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G66" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H66" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I66" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -4277,28 +4274,28 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C67" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D67" t="s">
         <v>453</v>
       </c>
       <c r="E67" t="s">
-        <v>494</v>
+        <v>472</v>
       </c>
       <c r="F67" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G67" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H67" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I67" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -4306,28 +4303,28 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C68" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D68" t="s">
         <v>453</v>
       </c>
       <c r="E68" t="s">
-        <v>503</v>
+        <v>459</v>
       </c>
       <c r="F68" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G68" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H68" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I68" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -4335,28 +4332,28 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C69" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D69" t="s">
         <v>453</v>
       </c>
       <c r="E69" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F69" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G69" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H69" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I69" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -4364,7 +4361,7 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C70" t="s">
         <v>392</v>
@@ -4373,19 +4370,19 @@
         <v>453</v>
       </c>
       <c r="E70" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="F70" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G70" t="s">
-        <v>26</v>
+        <v>586</v>
       </c>
       <c r="H70" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I70" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -4393,28 +4390,28 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C71" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D71" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E71" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="F71" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G71" t="s">
         <v>587</v>
       </c>
       <c r="H71" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I71" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -4422,28 +4419,28 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C72" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D72" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E72" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="F72" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G72" t="s">
         <v>588</v>
       </c>
       <c r="H72" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I72" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -4451,28 +4448,28 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C73" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D73" t="s">
         <v>453</v>
       </c>
       <c r="E73" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="F73" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G73" t="s">
-        <v>589</v>
+        <v>29</v>
       </c>
       <c r="H73" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I73" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -4480,28 +4477,28 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C74" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D74" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E74" t="s">
-        <v>468</v>
+        <v>504</v>
       </c>
       <c r="F74" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G74" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H74" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I74" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -4509,28 +4506,28 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C75" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D75" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E75" t="s">
-        <v>467</v>
+        <v>505</v>
       </c>
       <c r="F75" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G75" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H75" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I75" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -4538,28 +4535,28 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C76" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D76" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E76" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F76" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G76" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H76" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I76" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -4567,28 +4564,28 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C77" t="s">
         <v>394</v>
       </c>
       <c r="D77" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E77" t="s">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="F77" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G77" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H77" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I77" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -4596,28 +4593,28 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C78" t="s">
         <v>394</v>
       </c>
       <c r="D78" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E78" t="s">
-        <v>507</v>
+        <v>469</v>
       </c>
       <c r="F78" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G78" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H78" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I78" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -4625,28 +4622,28 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C79" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D79" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E79" t="s">
-        <v>508</v>
+        <v>482</v>
       </c>
       <c r="F79" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G79" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H79" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I79" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -4654,28 +4651,28 @@
         <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C80" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D80" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E80" t="s">
-        <v>466</v>
+        <v>505</v>
       </c>
       <c r="F80" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G80" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H80" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I80" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -4683,28 +4680,28 @@
         <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C81" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D81" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E81" t="s">
-        <v>475</v>
+        <v>506</v>
       </c>
       <c r="F81" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G81" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H81" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I81" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -4712,28 +4709,28 @@
         <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C82" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D82" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E82" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F82" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G82" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="H82" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I82" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -4741,28 +4738,28 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C83" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D83" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E83" t="s">
-        <v>507</v>
+        <v>468</v>
       </c>
       <c r="F83" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G83" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="H83" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I83" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -4770,28 +4767,28 @@
         <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C84" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D84" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E84" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="F84" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G84" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H84" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I84" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -4799,28 +4796,28 @@
         <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C85" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D85" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E85" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="F85" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G85" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H85" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I85" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -4828,28 +4825,28 @@
         <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C86" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D86" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E86" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="F86" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G86" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="H86" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I86" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -4857,28 +4854,28 @@
         <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C87" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D87" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E87" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="F87" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G87" t="s">
         <v>601</v>
       </c>
       <c r="H87" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I87" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -4886,28 +4883,28 @@
         <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C88" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D88" t="s">
         <v>453</v>
       </c>
       <c r="E88" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="F88" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G88" t="s">
-        <v>589</v>
+        <v>602</v>
       </c>
       <c r="H88" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I88" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -4915,28 +4912,28 @@
         <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C89" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D89" t="s">
         <v>453</v>
       </c>
       <c r="E89" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="F89" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G89" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H89" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I89" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -4944,28 +4941,28 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C90" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D90" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E90" t="s">
-        <v>467</v>
+        <v>504</v>
       </c>
       <c r="F90" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G90" t="s">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="H90" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I90" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -4973,28 +4970,28 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C91" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D91" t="s">
         <v>453</v>
       </c>
       <c r="E91" t="s">
-        <v>466</v>
+        <v>502</v>
       </c>
       <c r="F91" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G91" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="H91" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I91" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -5002,28 +4999,28 @@
         <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C92" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D92" t="s">
         <v>453</v>
       </c>
       <c r="E92" t="s">
-        <v>508</v>
+        <v>470</v>
       </c>
       <c r="F92" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G92" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="H92" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I92" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -5031,7 +5028,7 @@
         <v>100</v>
       </c>
       <c r="B93" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C93" t="s">
         <v>404</v>
@@ -5040,19 +5037,19 @@
         <v>453</v>
       </c>
       <c r="E93" t="s">
-        <v>509</v>
+        <v>469</v>
       </c>
       <c r="F93" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G93" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="H93" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I93" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -5060,7 +5057,7 @@
         <v>101</v>
       </c>
       <c r="B94" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C94" t="s">
         <v>404</v>
@@ -5069,19 +5066,19 @@
         <v>453</v>
       </c>
       <c r="E94" t="s">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="F94" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G94" t="s">
         <v>604</v>
       </c>
       <c r="H94" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I94" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -5089,28 +5086,28 @@
         <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C95" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D95" t="s">
         <v>453</v>
       </c>
       <c r="E95" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="F95" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G95" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="H95" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I95" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -5118,28 +5115,28 @@
         <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C96" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D96" t="s">
         <v>453</v>
       </c>
       <c r="E96" t="s">
-        <v>467</v>
+        <v>508</v>
       </c>
       <c r="F96" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G96" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H96" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I96" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -5147,28 +5144,28 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C97" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D97" t="s">
         <v>453</v>
       </c>
       <c r="E97" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="F97" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G97" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H97" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I97" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -5176,28 +5173,28 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C98" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D98" t="s">
         <v>453</v>
       </c>
       <c r="E98" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="F98" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G98" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H98" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I98" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -5205,28 +5202,28 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C99" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D99" t="s">
         <v>453</v>
       </c>
       <c r="E99" t="s">
-        <v>494</v>
+        <v>469</v>
       </c>
       <c r="F99" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G99" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H99" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I99" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -5234,28 +5231,28 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C100" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D100" t="s">
         <v>453</v>
       </c>
       <c r="E100" t="s">
-        <v>495</v>
+        <v>470</v>
       </c>
       <c r="F100" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G100" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H100" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I100" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -5263,28 +5260,28 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C101" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D101" t="s">
         <v>453</v>
       </c>
       <c r="E101" t="s">
-        <v>466</v>
+        <v>497</v>
       </c>
       <c r="F101" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G101" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H101" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I101" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -5292,28 +5289,28 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C102" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D102" t="s">
         <v>453</v>
       </c>
       <c r="E102" t="s">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="F102" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G102" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H102" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I102" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -5321,28 +5318,28 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C103" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D103" t="s">
         <v>453</v>
       </c>
       <c r="E103" t="s">
-        <v>456</v>
+        <v>494</v>
       </c>
       <c r="F103" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G103" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H103" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I103" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -5350,7 +5347,7 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C104" t="s">
         <v>409</v>
@@ -5359,19 +5356,19 @@
         <v>453</v>
       </c>
       <c r="E104" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F104" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G104" t="s">
-        <v>546</v>
+        <v>613</v>
       </c>
       <c r="H104" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I104" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -5379,28 +5376,28 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C105" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D105" t="s">
         <v>453</v>
       </c>
       <c r="E105" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="F105" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G105" t="s">
         <v>614</v>
       </c>
       <c r="H105" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I105" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -5408,28 +5405,28 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C106" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D106" t="s">
         <v>453</v>
       </c>
       <c r="E106" t="s">
-        <v>510</v>
+        <v>457</v>
       </c>
       <c r="F106" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G106" t="s">
         <v>615</v>
       </c>
       <c r="H106" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I106" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -5437,28 +5434,28 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C107" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D107" t="s">
         <v>453</v>
       </c>
       <c r="E107" t="s">
-        <v>502</v>
+        <v>456</v>
       </c>
       <c r="F107" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G107" t="s">
-        <v>616</v>
+        <v>546</v>
       </c>
       <c r="H107" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I107" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -5466,28 +5463,28 @@
         <v>115</v>
       </c>
       <c r="B108" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C108" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D108" t="s">
         <v>453</v>
       </c>
       <c r="E108" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="F108" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G108" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H108" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I108" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -5495,28 +5492,28 @@
         <v>116</v>
       </c>
       <c r="B109" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C109" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D109" t="s">
         <v>453</v>
       </c>
       <c r="E109" t="s">
-        <v>471</v>
+        <v>509</v>
       </c>
       <c r="F109" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G109" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H109" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I109" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -5524,28 +5521,28 @@
         <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C110" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D110" t="s">
         <v>453</v>
       </c>
       <c r="E110" t="s">
-        <v>468</v>
+        <v>501</v>
       </c>
       <c r="F110" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G110" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H110" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I110" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -5553,28 +5550,28 @@
         <v>118</v>
       </c>
       <c r="B111" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C111" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D111" t="s">
         <v>453</v>
       </c>
       <c r="E111" t="s">
-        <v>494</v>
+        <v>472</v>
       </c>
       <c r="F111" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G111" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H111" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I111" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -5582,28 +5579,28 @@
         <v>119</v>
       </c>
       <c r="B112" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C112" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D112" t="s">
         <v>453</v>
       </c>
       <c r="E112" t="s">
-        <v>503</v>
+        <v>471</v>
       </c>
       <c r="F112" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G112" t="s">
-        <v>95</v>
+        <v>620</v>
       </c>
       <c r="H112" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I112" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -5611,28 +5608,28 @@
         <v>120</v>
       </c>
       <c r="B113" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C113" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D113" t="s">
         <v>453</v>
       </c>
       <c r="E113" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F113" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G113" t="s">
         <v>621</v>
       </c>
       <c r="H113" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I113" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -5640,28 +5637,28 @@
         <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C114" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D114" t="s">
         <v>453</v>
       </c>
       <c r="E114" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F114" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G114" t="s">
-        <v>566</v>
+        <v>622</v>
       </c>
       <c r="H114" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I114" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -5669,28 +5666,28 @@
         <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C115" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D115" t="s">
         <v>453</v>
       </c>
       <c r="E115" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="F115" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G115" t="s">
-        <v>559</v>
+        <v>98</v>
       </c>
       <c r="H115" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I115" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -5698,28 +5695,28 @@
         <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C116" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D116" t="s">
         <v>453</v>
       </c>
       <c r="E116" t="s">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="F116" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G116" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H116" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I116" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -5727,7 +5724,7 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C117" t="s">
         <v>417</v>
@@ -5739,16 +5736,16 @@
         <v>495</v>
       </c>
       <c r="F117" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G117" t="s">
-        <v>623</v>
+        <v>566</v>
       </c>
       <c r="H117" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I117" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -5756,7 +5753,7 @@
         <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C118" t="s">
         <v>417</v>
@@ -5765,19 +5762,19 @@
         <v>453</v>
       </c>
       <c r="E118" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F118" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G118" t="s">
         <v>624</v>
       </c>
       <c r="H118" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I118" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -5785,28 +5782,28 @@
         <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C119" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D119" t="s">
         <v>453</v>
       </c>
       <c r="E119" t="s">
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="F119" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G119" t="s">
         <v>625</v>
       </c>
       <c r="H119" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I119" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -5814,28 +5811,28 @@
         <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C120" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D120" t="s">
         <v>453</v>
       </c>
       <c r="E120" t="s">
-        <v>468</v>
+        <v>494</v>
       </c>
       <c r="F120" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G120" t="s">
         <v>626</v>
       </c>
       <c r="H120" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I120" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -5843,28 +5840,28 @@
         <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C121" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D121" t="s">
         <v>453</v>
       </c>
       <c r="E121" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="F121" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G121" t="s">
         <v>627</v>
       </c>
       <c r="H121" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I121" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -5872,28 +5869,28 @@
         <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C122" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D122" t="s">
         <v>453</v>
       </c>
       <c r="E122" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F122" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G122" t="s">
         <v>628</v>
       </c>
       <c r="H122" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I122" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -5901,28 +5898,28 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C123" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D123" t="s">
         <v>453</v>
       </c>
       <c r="E123" t="s">
-        <v>512</v>
+        <v>470</v>
       </c>
       <c r="F123" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G123" t="s">
         <v>629</v>
       </c>
       <c r="H123" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I123" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -5930,28 +5927,28 @@
         <v>131</v>
       </c>
       <c r="B124" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C124" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D124" t="s">
         <v>453</v>
       </c>
       <c r="E124" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F124" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G124" t="s">
         <v>630</v>
       </c>
       <c r="H124" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I124" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -5959,28 +5956,28 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C125" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D125" t="s">
         <v>453</v>
       </c>
       <c r="E125" t="s">
-        <v>514</v>
+        <v>469</v>
       </c>
       <c r="F125" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G125" t="s">
         <v>631</v>
       </c>
       <c r="H125" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I125" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -5988,28 +5985,28 @@
         <v>133</v>
       </c>
       <c r="B126" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C126" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D126" t="s">
         <v>453</v>
       </c>
       <c r="E126" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="F126" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G126" t="s">
         <v>632</v>
       </c>
       <c r="H126" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I126" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -6017,28 +6014,28 @@
         <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C127" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D127" t="s">
         <v>453</v>
       </c>
       <c r="E127" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="F127" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G127" t="s">
         <v>633</v>
       </c>
       <c r="H127" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I127" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -6046,28 +6043,28 @@
         <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C128" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D128" t="s">
         <v>453</v>
       </c>
       <c r="E128" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F128" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G128" t="s">
         <v>634</v>
       </c>
       <c r="H128" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I128" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -6075,28 +6072,28 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C129" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D129" t="s">
         <v>453</v>
       </c>
       <c r="E129" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="F129" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G129" t="s">
         <v>635</v>
       </c>
       <c r="H129" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I129" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -6104,28 +6101,28 @@
         <v>137</v>
       </c>
       <c r="B130" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C130" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D130" t="s">
         <v>453</v>
       </c>
       <c r="E130" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F130" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G130" t="s">
         <v>636</v>
       </c>
       <c r="H130" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I130" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -6133,28 +6130,28 @@
         <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C131" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D131" t="s">
         <v>453</v>
       </c>
       <c r="E131" t="s">
-        <v>466</v>
+        <v>516</v>
       </c>
       <c r="F131" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G131" t="s">
         <v>637</v>
       </c>
       <c r="H131" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I131" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -6162,28 +6159,28 @@
         <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C132" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D132" t="s">
         <v>453</v>
       </c>
       <c r="E132" t="s">
-        <v>519</v>
+        <v>494</v>
       </c>
       <c r="F132" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G132" t="s">
         <v>638</v>
       </c>
       <c r="H132" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I132" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -6191,28 +6188,28 @@
         <v>140</v>
       </c>
       <c r="B133" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C133" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D133" t="s">
         <v>453</v>
       </c>
       <c r="E133" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="F133" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G133" t="s">
         <v>639</v>
       </c>
       <c r="H133" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I133" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -6220,28 +6217,28 @@
         <v>141</v>
       </c>
       <c r="B134" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C134" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D134" t="s">
         <v>453</v>
       </c>
       <c r="E134" t="s">
-        <v>511</v>
+        <v>468</v>
       </c>
       <c r="F134" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G134" t="s">
-        <v>530</v>
+        <v>640</v>
       </c>
       <c r="H134" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I134" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -6249,28 +6246,28 @@
         <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C135" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D135" t="s">
         <v>453</v>
       </c>
       <c r="E135" t="s">
-        <v>467</v>
+        <v>518</v>
       </c>
       <c r="F135" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G135" t="s">
-        <v>589</v>
+        <v>641</v>
       </c>
       <c r="H135" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I135" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -6278,28 +6275,28 @@
         <v>143</v>
       </c>
       <c r="B136" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C136" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D136" t="s">
         <v>453</v>
       </c>
       <c r="E136" t="s">
-        <v>467</v>
+        <v>519</v>
       </c>
       <c r="F136" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G136" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H136" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I136" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -6307,28 +6304,28 @@
         <v>144</v>
       </c>
       <c r="B137" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C137" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D137" t="s">
         <v>453</v>
       </c>
       <c r="E137" t="s">
-        <v>487</v>
+        <v>510</v>
       </c>
       <c r="F137" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G137" t="s">
-        <v>589</v>
+        <v>530</v>
       </c>
       <c r="H137" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I137" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -6336,28 +6333,28 @@
         <v>145</v>
       </c>
       <c r="B138" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C138" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D138" t="s">
         <v>453</v>
       </c>
       <c r="E138" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F138" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G138" t="s">
-        <v>641</v>
+        <v>591</v>
       </c>
       <c r="H138" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I138" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -6365,28 +6362,28 @@
         <v>146</v>
       </c>
       <c r="B139" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C139" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D139" t="s">
         <v>453</v>
       </c>
       <c r="E139" t="s">
-        <v>503</v>
+        <v>469</v>
       </c>
       <c r="F139" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G139" t="s">
-        <v>589</v>
+        <v>643</v>
       </c>
       <c r="H139" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I139" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -6394,28 +6391,28 @@
         <v>147</v>
       </c>
       <c r="B140" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C140" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D140" t="s">
         <v>453</v>
       </c>
       <c r="E140" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="F140" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G140" t="s">
-        <v>134</v>
+        <v>591</v>
       </c>
       <c r="H140" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I140" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -6423,28 +6420,28 @@
         <v>148</v>
       </c>
       <c r="B141" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C141" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D141" t="s">
         <v>453</v>
       </c>
       <c r="E141" t="s">
-        <v>512</v>
+        <v>468</v>
       </c>
       <c r="F141" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G141" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H141" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I141" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -6452,7 +6449,7 @@
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C142" t="s">
         <v>429</v>
@@ -6461,19 +6458,19 @@
         <v>453</v>
       </c>
       <c r="E142" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="F142" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G142" t="s">
-        <v>643</v>
+        <v>591</v>
       </c>
       <c r="H142" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I142" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -6481,28 +6478,28 @@
         <v>150</v>
       </c>
       <c r="B143" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C143" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D143" t="s">
         <v>453</v>
       </c>
       <c r="E143" t="s">
-        <v>504</v>
+        <v>459</v>
       </c>
       <c r="F143" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G143" t="s">
-        <v>589</v>
+        <v>137</v>
       </c>
       <c r="H143" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I143" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -6510,10 +6507,10 @@
         <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C144" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D144" t="s">
         <v>453</v>
@@ -6522,16 +6519,16 @@
         <v>511</v>
       </c>
       <c r="F144" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G144" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H144" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I144" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -6539,28 +6536,28 @@
         <v>152</v>
       </c>
       <c r="B145" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C145" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D145" t="s">
         <v>453</v>
       </c>
       <c r="E145" t="s">
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="F145" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G145" t="s">
-        <v>124</v>
+        <v>646</v>
       </c>
       <c r="H145" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I145" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -6568,28 +6565,28 @@
         <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C146" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D146" t="s">
         <v>453</v>
       </c>
       <c r="E146" t="s">
-        <v>467</v>
+        <v>503</v>
       </c>
       <c r="F146" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G146" t="s">
-        <v>645</v>
+        <v>591</v>
       </c>
       <c r="H146" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I146" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -6597,28 +6594,28 @@
         <v>154</v>
       </c>
       <c r="B147" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C147" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D147" t="s">
         <v>453</v>
       </c>
       <c r="E147" t="s">
-        <v>469</v>
+        <v>510</v>
       </c>
       <c r="F147" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G147" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H147" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I147" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -6626,28 +6623,28 @@
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C148" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D148" t="s">
         <v>453</v>
       </c>
       <c r="E148" t="s">
-        <v>504</v>
+        <v>469</v>
       </c>
       <c r="F148" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G148" t="s">
-        <v>647</v>
+        <v>127</v>
       </c>
       <c r="H148" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I148" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -6655,28 +6652,28 @@
         <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C149" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D149" t="s">
         <v>453</v>
       </c>
       <c r="E149" t="s">
-        <v>503</v>
+        <v>469</v>
       </c>
       <c r="F149" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G149" t="s">
         <v>648</v>
       </c>
       <c r="H149" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I149" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -6684,28 +6681,28 @@
         <v>157</v>
       </c>
       <c r="B150" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C150" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D150" t="s">
         <v>453</v>
       </c>
       <c r="E150" t="s">
-        <v>494</v>
+        <v>459</v>
       </c>
       <c r="F150" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G150" t="s">
-        <v>550</v>
+        <v>649</v>
       </c>
       <c r="H150" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I150" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -6713,7 +6710,7 @@
         <v>158</v>
       </c>
       <c r="B151" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C151" t="s">
         <v>433</v>
@@ -6722,19 +6719,19 @@
         <v>453</v>
       </c>
       <c r="E151" t="s">
-        <v>467</v>
+        <v>503</v>
       </c>
       <c r="F151" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G151" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H151" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I151" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -6742,7 +6739,7 @@
         <v>159</v>
       </c>
       <c r="B152" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C152" t="s">
         <v>433</v>
@@ -6751,19 +6748,19 @@
         <v>453</v>
       </c>
       <c r="E152" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="F152" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G152" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H152" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I152" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -6771,28 +6768,28 @@
         <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C153" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D153" t="s">
         <v>453</v>
       </c>
       <c r="E153" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="F153" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G153" t="s">
-        <v>651</v>
+        <v>550</v>
       </c>
       <c r="H153" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I153" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -6800,28 +6797,28 @@
         <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C154" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D154" t="s">
         <v>453</v>
       </c>
       <c r="E154" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F154" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G154" t="s">
         <v>652</v>
       </c>
       <c r="H154" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I154" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -6829,28 +6826,28 @@
         <v>162</v>
       </c>
       <c r="B155" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C155" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D155" t="s">
         <v>453</v>
       </c>
       <c r="E155" t="s">
-        <v>508</v>
+        <v>486</v>
       </c>
       <c r="F155" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G155" t="s">
         <v>653</v>
       </c>
       <c r="H155" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I155" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -6858,28 +6855,28 @@
         <v>163</v>
       </c>
       <c r="B156" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C156" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D156" t="s">
         <v>453</v>
       </c>
       <c r="E156" t="s">
-        <v>466</v>
+        <v>510</v>
       </c>
       <c r="F156" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G156" t="s">
-        <v>589</v>
+        <v>654</v>
       </c>
       <c r="H156" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I156" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -6887,28 +6884,28 @@
         <v>164</v>
       </c>
       <c r="B157" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C157" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D157" t="s">
         <v>453</v>
       </c>
       <c r="E157" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F157" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G157" t="s">
-        <v>589</v>
+        <v>655</v>
       </c>
       <c r="H157" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I157" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -6916,28 +6913,28 @@
         <v>165</v>
       </c>
       <c r="B158" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C158" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D158" t="s">
         <v>453</v>
       </c>
       <c r="E158" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="F158" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G158" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="H158" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I158" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -6945,28 +6942,28 @@
         <v>166</v>
       </c>
       <c r="B159" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C159" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D159" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E159" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="F159" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G159" t="s">
-        <v>118</v>
+        <v>591</v>
       </c>
       <c r="H159" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I159" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -6974,28 +6971,28 @@
         <v>167</v>
       </c>
       <c r="B160" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C160" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D160" t="s">
         <v>453</v>
       </c>
       <c r="E160" t="s">
-        <v>502</v>
+        <v>468</v>
       </c>
       <c r="F160" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G160" t="s">
-        <v>655</v>
+        <v>591</v>
       </c>
       <c r="H160" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I160" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -7003,28 +7000,28 @@
         <v>168</v>
       </c>
       <c r="B161" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C161" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D161" t="s">
         <v>453</v>
       </c>
       <c r="E161" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="F161" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G161" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H161" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I161" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -7032,28 +7029,28 @@
         <v>169</v>
       </c>
       <c r="B162" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C162" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D162" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E162" t="s">
-        <v>508</v>
+        <v>474</v>
       </c>
       <c r="F162" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G162" t="s">
-        <v>589</v>
+        <v>121</v>
       </c>
       <c r="H162" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I162" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -7061,28 +7058,28 @@
         <v>170</v>
       </c>
       <c r="B163" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C163" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D163" t="s">
         <v>453</v>
       </c>
       <c r="E163" t="s">
-        <v>466</v>
+        <v>501</v>
       </c>
       <c r="F163" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G163" t="s">
-        <v>589</v>
+        <v>658</v>
       </c>
       <c r="H163" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I163" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -7090,28 +7087,28 @@
         <v>171</v>
       </c>
       <c r="B164" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C164" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D164" t="s">
         <v>453</v>
       </c>
       <c r="E164" t="s">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="F164" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G164" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H164" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I164" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -7119,28 +7116,28 @@
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C165" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D165" t="s">
         <v>453</v>
       </c>
       <c r="E165" t="s">
-        <v>466</v>
+        <v>507</v>
       </c>
       <c r="F165" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G165" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H165" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I165" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -7148,28 +7145,28 @@
         <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C166" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D166" t="s">
         <v>453</v>
       </c>
       <c r="E166" t="s">
-        <v>508</v>
+        <v>468</v>
       </c>
       <c r="F166" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G166" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H166" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I166" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -7177,28 +7174,28 @@
         <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C167" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D167" t="s">
         <v>453</v>
       </c>
       <c r="E167" t="s">
-        <v>521</v>
+        <v>472</v>
       </c>
       <c r="F167" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G167" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="H167" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I167" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -7206,28 +7203,28 @@
         <v>175</v>
       </c>
       <c r="B168" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C168" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D168" t="s">
         <v>453</v>
       </c>
       <c r="E168" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F168" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G168" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H168" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I168" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -7235,28 +7232,28 @@
         <v>176</v>
       </c>
       <c r="B169" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C169" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D169" t="s">
         <v>453</v>
       </c>
       <c r="E169" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="F169" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G169" t="s">
-        <v>659</v>
+        <v>591</v>
       </c>
       <c r="H169" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I169" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -7264,28 +7261,28 @@
         <v>177</v>
       </c>
       <c r="B170" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C170" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D170" t="s">
         <v>453</v>
       </c>
       <c r="E170" t="s">
-        <v>466</v>
+        <v>520</v>
       </c>
       <c r="F170" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G170" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H170" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I170" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -7293,28 +7290,28 @@
         <v>178</v>
       </c>
       <c r="B171" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C171" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D171" t="s">
         <v>453</v>
       </c>
       <c r="E171" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="F171" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G171" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H171" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I171" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -7322,28 +7319,28 @@
         <v>179</v>
       </c>
       <c r="B172" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C172" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D172" t="s">
         <v>453</v>
       </c>
       <c r="E172" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="F172" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G172" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H172" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I172" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -7351,28 +7348,28 @@
         <v>180</v>
       </c>
       <c r="B173" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C173" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D173" t="s">
         <v>453</v>
       </c>
       <c r="E173" t="s">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="F173" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G173" t="s">
-        <v>589</v>
+        <v>663</v>
       </c>
       <c r="H173" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I173" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -7380,28 +7377,28 @@
         <v>181</v>
       </c>
       <c r="B174" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C174" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D174" t="s">
         <v>453</v>
       </c>
       <c r="E174" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="F174" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G174" t="s">
-        <v>662</v>
+        <v>591</v>
       </c>
       <c r="H174" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I174" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -7409,28 +7406,28 @@
         <v>182</v>
       </c>
       <c r="B175" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C175" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D175" t="s">
         <v>453</v>
       </c>
       <c r="E175" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="F175" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G175" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H175" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I175" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -7438,28 +7435,28 @@
         <v>183</v>
       </c>
       <c r="B176" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C176" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D176" t="s">
         <v>453</v>
       </c>
       <c r="E176" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F176" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G176" t="s">
-        <v>664</v>
+        <v>591</v>
       </c>
       <c r="H176" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I176" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -7467,28 +7464,28 @@
         <v>184</v>
       </c>
       <c r="B177" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C177" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D177" t="s">
         <v>453</v>
       </c>
       <c r="E177" t="s">
-        <v>522</v>
+        <v>459</v>
       </c>
       <c r="F177" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G177" t="s">
         <v>665</v>
       </c>
       <c r="H177" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I177" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -7496,57 +7493,28 @@
         <v>185</v>
       </c>
       <c r="B178" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C178" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D178" t="s">
         <v>453</v>
       </c>
       <c r="E178" t="s">
-        <v>523</v>
+        <v>471</v>
       </c>
       <c r="F178" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G178" t="s">
         <v>666</v>
       </c>
       <c r="H178" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I178" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9">
-      <c r="A179" t="s">
-        <v>186</v>
-      </c>
-      <c r="B179" t="s">
-        <v>364</v>
-      </c>
-      <c r="C179" t="s">
-        <v>452</v>
-      </c>
-      <c r="D179" t="s">
-        <v>453</v>
-      </c>
-      <c r="E179" t="s">
-        <v>456</v>
-      </c>
-      <c r="F179" t="s">
-        <v>524</v>
-      </c>
-      <c r="G179" t="s">
-        <v>667</v>
-      </c>
-      <c r="H179" t="s">
-        <v>668</v>
-      </c>
-      <c r="I179" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
   </sheetData>

--- a/data/BioTecnos.xlsx
+++ b/data/BioTecnos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="659">
   <si>
     <t>ID</t>
   </si>
@@ -568,12 +568,6 @@
     <t>723</t>
   </si>
   <si>
-    <t>722</t>
-  </si>
-  <si>
-    <t>721</t>
-  </si>
-  <si>
     <t>M04D002LI2603</t>
   </si>
   <si>
@@ -1099,12 +1093,6 @@
     <t>M02Q050L01519</t>
   </si>
   <si>
-    <t>M02M039L20503</t>
-  </si>
-  <si>
-    <t>M02T083LA3506</t>
-  </si>
-  <si>
     <t>20-04-2026</t>
   </si>
   <si>
@@ -1369,9 +1357,6 @@
     <t>01-09-2025</t>
   </si>
   <si>
-    <t>28-08-2025</t>
-  </si>
-  <si>
     <t>Avellano</t>
   </si>
   <si>
@@ -1792,10 +1777,7 @@
     <t>0</t>
   </si>
   <si>
-    <t>1.152</t>
-  </si>
-  <si>
-    <t>93.728</t>
+    <t>65.506</t>
   </si>
   <si>
     <t>2.211</t>
@@ -1843,7 +1825,7 @@
     <t>5.856</t>
   </si>
   <si>
-    <t>21.024</t>
+    <t>20.715</t>
   </si>
   <si>
     <t>14.356</t>
@@ -1879,7 +1861,7 @@
     <t>6.264</t>
   </si>
   <si>
-    <t>16.032</t>
+    <t>12.264</t>
   </si>
   <si>
     <t>528</t>
@@ -1900,13 +1882,13 @@
     <t>4.256</t>
   </si>
   <si>
-    <t>104.301</t>
+    <t>81.568</t>
   </si>
   <si>
     <t>1.032</t>
   </si>
   <si>
-    <t>35.496</t>
+    <t>32.016</t>
   </si>
   <si>
     <t>1.592</t>
@@ -1930,7 +1912,7 @@
     <t>1.495</t>
   </si>
   <si>
-    <t>13.809</t>
+    <t>4.234</t>
   </si>
   <si>
     <t>2.726</t>
@@ -1945,22 +1927,22 @@
     <t>151</t>
   </si>
   <si>
-    <t>3.740</t>
+    <t>1.403</t>
   </si>
   <si>
     <t>5.049</t>
   </si>
   <si>
-    <t>39.996</t>
-  </si>
-  <si>
-    <t>11.368</t>
+    <t>11.688</t>
+  </si>
+  <si>
+    <t>8.130</t>
   </si>
   <si>
     <t>394</t>
   </si>
   <si>
-    <t>1.904</t>
+    <t>564</t>
   </si>
   <si>
     <t>7.872</t>
@@ -1972,22 +1954,19 @@
     <t>120</t>
   </si>
   <si>
-    <t>5.350</t>
-  </si>
-  <si>
-    <t>707</t>
-  </si>
-  <si>
-    <t>15.412</t>
-  </si>
-  <si>
-    <t>3.552</t>
+    <t>2.854</t>
+  </si>
+  <si>
+    <t>10.444</t>
+  </si>
+  <si>
+    <t>3.045</t>
   </si>
   <si>
     <t>264</t>
   </si>
   <si>
-    <t>6.345</t>
+    <t>2.478</t>
   </si>
   <si>
     <t>3.573</t>
@@ -2002,19 +1981,10 @@
     <t>60</t>
   </si>
   <si>
-    <t>16.895</t>
-  </si>
-  <si>
     <t>3.168</t>
   </si>
   <si>
     <t>713</t>
-  </si>
-  <si>
-    <t>7.850</t>
-  </si>
-  <si>
-    <t>2.649</t>
   </si>
   <si>
     <t>NO</t>
@@ -2352,7 +2322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I178"/>
+  <dimension ref="A1:I176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2389,28 +2359,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D2" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E2" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="F2" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G2" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="H2" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I2" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2418,28 +2388,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D3" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E3" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F3" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G3" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="H3" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I3" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2447,28 +2417,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D4" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E4" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="F4" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G4" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="H4" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I4" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2476,28 +2446,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D5" t="s">
+        <v>448</v>
+      </c>
+      <c r="E5" t="s">
         <v>453</v>
       </c>
-      <c r="E5" t="s">
-        <v>458</v>
-      </c>
       <c r="F5" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G5" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="H5" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I5" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2505,28 +2475,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C6" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D6" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E6" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F6" t="s">
+        <v>516</v>
+      </c>
+      <c r="G6" t="s">
         <v>521</v>
       </c>
-      <c r="G6" t="s">
-        <v>526</v>
-      </c>
       <c r="H6" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I6" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2534,28 +2504,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D7" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E7" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="F7" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G7" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="H7" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I7" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2563,28 +2533,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D8" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E8" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="F8" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G8" t="s">
         <v>68</v>
       </c>
       <c r="H8" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I8" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2592,28 +2562,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C9" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D9" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E9" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="F9" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G9" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="H9" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I9" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2621,28 +2591,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D10" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E10" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="F10" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G10" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="H10" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I10" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2650,28 +2620,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C11" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D11" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E11" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="F11" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G11" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="H11" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I11" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2679,28 +2649,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C12" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D12" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E12" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="F12" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G12" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="H12" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I12" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2708,28 +2678,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C13" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D13" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E13" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="F13" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G13" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="H13" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I13" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2737,28 +2707,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C14" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D14" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E14" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="F14" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G14" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="H14" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I14" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2766,28 +2736,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C15" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D15" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E15" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F15" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G15" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="H15" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I15" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2795,28 +2765,28 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C16" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D16" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E16" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F16" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G16" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="H16" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I16" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -2824,28 +2794,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C17" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D17" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E17" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="F17" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G17" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="H17" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I17" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2853,28 +2823,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C18" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D18" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E18" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F18" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G18" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="H18" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I18" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -2882,28 +2852,28 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C19" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D19" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E19" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F19" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G19" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="H19" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I19" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2911,28 +2881,28 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C20" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D20" t="s">
+        <v>448</v>
+      </c>
+      <c r="E20" t="s">
         <v>453</v>
       </c>
-      <c r="E20" t="s">
-        <v>458</v>
-      </c>
       <c r="F20" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G20" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="H20" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I20" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -2940,28 +2910,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C21" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D21" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E21" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F21" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G21" t="s">
         <v>157</v>
       </c>
       <c r="H21" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I21" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -2969,28 +2939,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C22" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D22" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E22" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="F22" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G22" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="H22" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I22" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -2998,28 +2968,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C23" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D23" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E23" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F23" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G23" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="H23" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I23" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -3027,28 +2997,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C24" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D24" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E24" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="F24" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G24" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="H24" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I24" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -3056,28 +3026,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C25" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D25" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E25" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="F25" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G25" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="H25" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I25" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -3085,28 +3055,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C26" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D26" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E26" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="F26" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G26" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="H26" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I26" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -3114,28 +3084,28 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C27" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D27" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E27" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="F27" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G27" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="H27" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I27" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -3143,28 +3113,28 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C28" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D28" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E28" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="F28" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G28" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="H28" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I28" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -3172,28 +3142,28 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C29" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D29" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E29" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="F29" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G29" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="H29" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I29" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -3201,28 +3171,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C30" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D30" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E30" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="F30" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G30" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="H30" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I30" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -3230,28 +3200,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C31" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D31" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E31" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="F31" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G31" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="H31" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I31" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -3259,28 +3229,28 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C32" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D32" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E32" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="F32" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G32" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="H32" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I32" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -3288,28 +3258,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C33" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D33" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E33" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="F33" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G33" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="H33" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I33" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -3317,28 +3287,28 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C34" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D34" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E34" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="F34" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G34" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="H34" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I34" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -3346,28 +3316,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C35" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D35" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E35" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="F35" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G35" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="H35" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I35" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -3375,28 +3345,28 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C36" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D36" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E36" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="F36" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G36" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="H36" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I36" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -3404,28 +3374,28 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C37" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D37" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E37" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="F37" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G37" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="H37" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I37" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -3433,28 +3403,28 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C38" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D38" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E38" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="F38" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G38" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="H38" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I38" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -3462,28 +3432,28 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C39" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D39" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E39" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="F39" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G39" t="s">
         <v>121</v>
       </c>
       <c r="H39" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I39" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -3491,28 +3461,28 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C40" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D40" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E40" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="F40" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G40" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="H40" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I40" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -3520,28 +3490,28 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C41" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D41" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E41" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F41" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G41" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="H41" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I41" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -3549,28 +3519,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C42" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D42" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E42" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="F42" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G42" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="H42" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I42" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -3578,28 +3548,28 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C43" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D43" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E43" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F43" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G43" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="H43" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I43" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -3607,28 +3577,28 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C44" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D44" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E44" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F44" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G44" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="H44" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I44" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -3636,28 +3606,28 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C45" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D45" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E45" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="F45" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G45" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="H45" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I45" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -3665,28 +3635,28 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C46" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D46" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E46" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="F46" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G46" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="H46" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I46" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -3694,28 +3664,28 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C47" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D47" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E47" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="F47" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G47" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="H47" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I47" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -3723,28 +3693,28 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C48" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D48" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E48" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="F48" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G48" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="H48" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I48" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -3752,28 +3722,28 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C49" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D49" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E49" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="F49" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G49" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="H49" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I49" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -3781,28 +3751,28 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C50" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D50" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E50" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="F50" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G50" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="H50" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I50" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -3810,28 +3780,28 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C51" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D51" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E51" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F51" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G51" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="H51" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I51" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -3839,28 +3809,28 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C52" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D52" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E52" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="F52" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G52" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="H52" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I52" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -3868,28 +3838,28 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C53" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D53" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E53" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="F53" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G53" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="H53" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I53" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -3897,28 +3867,28 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C54" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D54" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E54" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="F54" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G54" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="H54" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I54" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -3926,28 +3896,28 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C55" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D55" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E55" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="F55" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G55" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="H55" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I55" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -3955,28 +3925,28 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C56" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D56" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E56" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F56" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G56" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="H56" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I56" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -3984,28 +3954,28 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C57" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D57" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E57" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="F57" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G57" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="H57" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I57" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -4013,28 +3983,28 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C58" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D58" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E58" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F58" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G58" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="H58" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I58" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -4042,28 +4012,28 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C59" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D59" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E59" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F59" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G59" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="H59" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I59" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -4071,28 +4041,28 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C60" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D60" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E60" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F60" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G60" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="H60" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I60" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -4100,28 +4070,28 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C61" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D61" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E61" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="F61" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G61" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="H61" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I61" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -4129,28 +4099,28 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C62" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D62" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E62" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F62" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G62" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="H62" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I62" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -4158,28 +4128,28 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C63" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D63" t="s">
+        <v>448</v>
+      </c>
+      <c r="E63" t="s">
         <v>453</v>
       </c>
-      <c r="E63" t="s">
-        <v>458</v>
-      </c>
       <c r="F63" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G63" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="H63" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I63" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -4187,28 +4157,28 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C64" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D64" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E64" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="F64" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G64" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="H64" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I64" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -4216,28 +4186,28 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C65" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D65" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E65" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="F65" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G65" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H65" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I65" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -4245,28 +4215,28 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C66" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D66" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E66" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F66" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G66" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="H66" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I66" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -4274,28 +4244,28 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C67" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D67" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E67" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F67" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G67" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="H67" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I67" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -4303,28 +4273,28 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C68" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D68" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E68" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F68" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G68" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="H68" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I68" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -4332,28 +4302,28 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C69" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D69" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E69" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="F69" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G69" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="H69" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I69" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -4361,28 +4331,28 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C70" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D70" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E70" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F70" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G70" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="H70" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I70" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -4390,28 +4360,28 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C71" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D71" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E71" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="F71" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G71" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="H71" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I71" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -4419,28 +4389,28 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C72" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D72" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E72" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="F72" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G72" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="H72" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I72" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -4448,28 +4418,28 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C73" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D73" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E73" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="F73" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G73" t="s">
         <v>29</v>
       </c>
       <c r="H73" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I73" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -4477,28 +4447,28 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C74" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D74" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E74" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="F74" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G74" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="H74" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I74" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -4506,28 +4476,28 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C75" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D75" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E75" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="F75" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G75" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="H75" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I75" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -4535,28 +4505,28 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C76" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D76" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E76" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="F76" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G76" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H76" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I76" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -4564,28 +4534,28 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C77" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D77" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E77" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="F77" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G77" t="s">
-        <v>592</v>
+        <v>38</v>
       </c>
       <c r="H77" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I77" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -4593,28 +4563,28 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D78" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E78" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F78" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G78" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="H78" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I78" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -4622,28 +4592,28 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C79" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D79" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E79" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="F79" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G79" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="H79" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I79" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -4651,28 +4621,28 @@
         <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C80" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D80" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E80" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="F80" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G80" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="H80" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I80" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -4680,28 +4650,28 @@
         <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C81" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D81" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E81" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="F81" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G81" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="H81" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I81" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -4709,28 +4679,28 @@
         <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C82" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D82" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E82" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="F82" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G82" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H82" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I82" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -4738,28 +4708,28 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C83" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D83" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E83" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F83" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G83" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="H83" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I83" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -4767,28 +4737,28 @@
         <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C84" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D84" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E84" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="F84" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G84" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="H84" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I84" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -4796,28 +4766,28 @@
         <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C85" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D85" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E85" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="F85" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G85" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="H85" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I85" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -4825,28 +4795,28 @@
         <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C86" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D86" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E86" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="F86" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G86" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="H86" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I86" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -4854,28 +4824,28 @@
         <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C87" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="D87" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E87" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="F87" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G87" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="H87" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I87" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -4883,28 +4853,28 @@
         <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C88" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="D88" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E88" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F88" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G88" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="H88" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I88" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -4912,28 +4882,28 @@
         <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C89" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D89" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E89" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F89" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G89" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H89" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I89" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -4941,28 +4911,28 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C90" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D90" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E90" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="F90" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G90" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="H90" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I90" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -4970,28 +4940,28 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C91" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D91" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E91" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="F91" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G91" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H91" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I91" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -4999,28 +4969,28 @@
         <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C92" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D92" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E92" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="F92" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G92" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H92" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I92" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -5028,28 +4998,28 @@
         <v>100</v>
       </c>
       <c r="B93" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C93" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D93" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E93" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F93" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G93" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H93" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I93" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -5057,28 +5027,28 @@
         <v>101</v>
       </c>
       <c r="B94" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C94" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D94" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E94" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F94" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G94" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="H94" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I94" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -5086,28 +5056,28 @@
         <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C95" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D95" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E95" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="F95" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G95" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="H95" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I95" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -5115,28 +5085,28 @@
         <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C96" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D96" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E96" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="F96" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G96" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="H96" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I96" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -5144,28 +5114,28 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C97" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D97" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E97" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F97" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G97" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="H97" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I97" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -5173,28 +5143,28 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C98" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D98" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E98" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="F98" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G98" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="H98" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I98" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -5202,28 +5172,28 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C99" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D99" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E99" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F99" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G99" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="H99" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I99" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -5231,28 +5201,28 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C100" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D100" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E100" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="F100" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G100" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="H100" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I100" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -5260,28 +5230,28 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C101" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D101" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E101" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="F101" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G101" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="H101" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I101" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -5289,28 +5259,28 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C102" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D102" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E102" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F102" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G102" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="H102" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I102" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -5318,28 +5288,28 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C103" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D103" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E103" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="F103" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G103" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="H103" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I103" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -5347,28 +5317,28 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C104" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D104" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E104" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F104" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G104" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="H104" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I104" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -5376,28 +5346,28 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C105" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D105" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E105" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F105" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G105" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="H105" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I105" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -5405,28 +5375,28 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C106" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D106" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E106" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="F106" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G106" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="H106" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I106" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -5434,28 +5404,28 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C107" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D107" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E107" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F107" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G107" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="H107" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I107" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -5463,28 +5433,28 @@
         <v>115</v>
       </c>
       <c r="B108" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C108" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D108" t="s">
+        <v>448</v>
+      </c>
+      <c r="E108" t="s">
         <v>453</v>
       </c>
-      <c r="E108" t="s">
-        <v>458</v>
-      </c>
       <c r="F108" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G108" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="H108" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I108" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -5492,28 +5462,28 @@
         <v>116</v>
       </c>
       <c r="B109" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C109" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D109" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E109" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="F109" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G109" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="H109" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I109" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -5521,28 +5491,28 @@
         <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C110" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D110" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E110" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="F110" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G110" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="H110" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I110" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -5550,28 +5520,28 @@
         <v>118</v>
       </c>
       <c r="B111" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C111" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D111" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E111" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F111" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G111" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="H111" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I111" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -5579,28 +5549,28 @@
         <v>119</v>
       </c>
       <c r="B112" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C112" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="D112" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E112" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="F112" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G112" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="H112" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I112" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -5608,28 +5578,28 @@
         <v>120</v>
       </c>
       <c r="B113" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C113" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="D113" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E113" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="F113" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G113" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="H113" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I113" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -5637,28 +5607,28 @@
         <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C114" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D114" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E114" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F114" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G114" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="H114" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I114" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -5666,28 +5636,28 @@
         <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C115" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="D115" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E115" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="F115" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G115" t="s">
         <v>98</v>
       </c>
       <c r="H115" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I115" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -5695,28 +5665,28 @@
         <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C116" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="D116" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E116" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F116" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G116" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="H116" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I116" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -5724,28 +5694,28 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C117" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="D117" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E117" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="F117" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G117" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="H117" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I117" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -5753,28 +5723,28 @@
         <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C118" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="D118" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E118" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="F118" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G118" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="H118" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I118" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -5782,28 +5752,28 @@
         <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C119" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="D119" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E119" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F119" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G119" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="H119" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I119" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -5811,28 +5781,28 @@
         <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C120" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="D120" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E120" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="F120" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G120" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="H120" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I120" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -5840,28 +5810,28 @@
         <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C121" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="D121" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E121" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="F121" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G121" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="H121" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I121" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -5869,28 +5839,28 @@
         <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C122" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D122" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E122" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F122" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G122" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="H122" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I122" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -5898,28 +5868,28 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C123" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="D123" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E123" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="F123" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G123" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="H123" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I123" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -5927,28 +5897,28 @@
         <v>131</v>
       </c>
       <c r="B124" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C124" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="D124" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E124" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="F124" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G124" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="H124" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I124" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -5956,28 +5926,28 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C125" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D125" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E125" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F125" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G125" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="H125" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I125" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -5985,28 +5955,28 @@
         <v>133</v>
       </c>
       <c r="B126" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C126" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D126" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E126" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="F126" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G126" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="H126" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I126" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -6014,28 +5984,28 @@
         <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C127" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D127" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E127" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="F127" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G127" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="H127" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I127" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -6043,28 +6013,28 @@
         <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C128" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D128" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E128" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="F128" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G128" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="H128" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I128" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -6072,28 +6042,28 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C129" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D129" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E129" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="F129" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G129" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="H129" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I129" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -6101,28 +6071,28 @@
         <v>137</v>
       </c>
       <c r="B130" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C130" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D130" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E130" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="F130" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G130" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="H130" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I130" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -6130,28 +6100,28 @@
         <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C131" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D131" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E131" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="F131" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G131" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="H131" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I131" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -6159,28 +6129,28 @@
         <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C132" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D132" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E132" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="F132" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G132" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="H132" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I132" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -6188,28 +6158,28 @@
         <v>140</v>
       </c>
       <c r="B133" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C133" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D133" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E133" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="F133" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G133" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="H133" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I133" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -6217,28 +6187,28 @@
         <v>141</v>
       </c>
       <c r="B134" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C134" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D134" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E134" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F134" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G134" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="H134" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I134" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -6246,28 +6216,28 @@
         <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C135" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="D135" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E135" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="F135" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G135" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="H135" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I135" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -6275,28 +6245,28 @@
         <v>143</v>
       </c>
       <c r="B136" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C136" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D136" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E136" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="F136" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G136" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="H136" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I136" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -6304,28 +6274,28 @@
         <v>144</v>
       </c>
       <c r="B137" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C137" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D137" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E137" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="F137" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G137" t="s">
-        <v>530</v>
+        <v>586</v>
       </c>
       <c r="H137" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I137" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -6333,28 +6303,28 @@
         <v>145</v>
       </c>
       <c r="B138" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C138" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D138" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E138" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F138" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G138" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H138" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I138" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -6362,28 +6332,28 @@
         <v>146</v>
       </c>
       <c r="B139" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C139" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D139" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E139" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F139" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G139" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="H139" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I139" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -6391,28 +6361,28 @@
         <v>147</v>
       </c>
       <c r="B140" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C140" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D140" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E140" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="F140" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G140" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H140" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I140" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -6420,28 +6390,28 @@
         <v>148</v>
       </c>
       <c r="B141" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C141" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D141" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E141" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F141" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G141" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="H141" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I141" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -6449,28 +6419,28 @@
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C142" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D142" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E142" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="F142" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G142" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H142" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I142" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -6478,28 +6448,28 @@
         <v>150</v>
       </c>
       <c r="B143" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C143" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D143" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E143" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F143" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G143" t="s">
         <v>137</v>
       </c>
       <c r="H143" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I143" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -6507,28 +6477,28 @@
         <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C144" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D144" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E144" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="F144" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G144" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="H144" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I144" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -6536,28 +6506,28 @@
         <v>152</v>
       </c>
       <c r="B145" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C145" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D145" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E145" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F145" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G145" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="H145" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I145" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -6565,28 +6535,28 @@
         <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C146" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D146" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E146" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="F146" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G146" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H146" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I146" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -6594,28 +6564,28 @@
         <v>154</v>
       </c>
       <c r="B147" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C147" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D147" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E147" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="F147" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G147" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="H147" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I147" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -6623,28 +6593,28 @@
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C148" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D148" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E148" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F148" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G148" t="s">
         <v>127</v>
       </c>
       <c r="H148" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I148" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -6652,28 +6622,28 @@
         <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C149" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D149" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E149" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F149" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G149" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="H149" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I149" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -6681,28 +6651,28 @@
         <v>157</v>
       </c>
       <c r="B150" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C150" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D150" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E150" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F150" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G150" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="H150" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I150" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -6710,28 +6680,28 @@
         <v>158</v>
       </c>
       <c r="B151" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C151" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D151" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E151" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="F151" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G151" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="H151" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I151" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -6739,28 +6709,28 @@
         <v>159</v>
       </c>
       <c r="B152" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C152" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D152" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E152" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="F152" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G152" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="H152" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I152" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -6768,28 +6738,28 @@
         <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C153" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D153" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E153" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F153" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G153" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="H153" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I153" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -6797,28 +6767,28 @@
         <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C154" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D154" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E154" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F154" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G154" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="H154" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I154" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -6826,28 +6796,28 @@
         <v>162</v>
       </c>
       <c r="B155" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C155" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D155" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E155" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="F155" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G155" t="s">
-        <v>653</v>
+        <v>586</v>
       </c>
       <c r="H155" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I155" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -6855,28 +6825,28 @@
         <v>163</v>
       </c>
       <c r="B156" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C156" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="D156" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E156" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="F156" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G156" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="H156" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I156" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -6884,28 +6854,28 @@
         <v>164</v>
       </c>
       <c r="B157" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C157" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D157" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E157" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F157" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G157" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="H157" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I157" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -6913,28 +6883,28 @@
         <v>165</v>
       </c>
       <c r="B158" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C158" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D158" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E158" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="F158" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G158" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="H158" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I158" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -6942,28 +6912,28 @@
         <v>166</v>
       </c>
       <c r="B159" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C159" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D159" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E159" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F159" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G159" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H159" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I159" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -6971,28 +6941,28 @@
         <v>167</v>
       </c>
       <c r="B160" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C160" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="D160" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E160" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F160" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G160" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H160" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I160" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -7000,28 +6970,28 @@
         <v>168</v>
       </c>
       <c r="B161" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C161" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="D161" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E161" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="F161" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G161" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="H161" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I161" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -7029,28 +6999,28 @@
         <v>169</v>
       </c>
       <c r="B162" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C162" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D162" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E162" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="F162" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G162" t="s">
         <v>121</v>
       </c>
       <c r="H162" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I162" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -7058,28 +7028,28 @@
         <v>170</v>
       </c>
       <c r="B163" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C163" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="D163" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E163" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="F163" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G163" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="H163" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I163" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -7087,28 +7057,28 @@
         <v>171</v>
       </c>
       <c r="B164" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C164" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D164" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E164" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="F164" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G164" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="H164" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I164" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -7116,28 +7086,28 @@
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C165" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D165" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E165" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="F165" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G165" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H165" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I165" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -7145,28 +7115,28 @@
         <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C166" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D166" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E166" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F166" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G166" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H166" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I166" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -7174,28 +7144,28 @@
         <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C167" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="D167" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E167" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F167" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G167" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="H167" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I167" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -7203,28 +7173,28 @@
         <v>175</v>
       </c>
       <c r="B168" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C168" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="D168" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E168" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F168" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G168" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H168" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I168" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -7232,28 +7202,28 @@
         <v>176</v>
       </c>
       <c r="B169" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C169" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="D169" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E169" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="F169" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G169" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H169" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I169" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -7261,28 +7231,28 @@
         <v>177</v>
       </c>
       <c r="B170" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C170" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="D170" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E170" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="F170" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G170" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="H170" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I170" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -7290,28 +7260,28 @@
         <v>178</v>
       </c>
       <c r="B171" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C171" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D171" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E171" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F171" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G171" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H171" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I171" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -7319,28 +7289,28 @@
         <v>179</v>
       </c>
       <c r="B172" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C172" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="D172" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E172" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="F172" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G172" t="s">
-        <v>662</v>
+        <v>586</v>
       </c>
       <c r="H172" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I172" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -7348,28 +7318,28 @@
         <v>180</v>
       </c>
       <c r="B173" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C173" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D173" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E173" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F173" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G173" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="H173" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I173" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -7377,28 +7347,28 @@
         <v>181</v>
       </c>
       <c r="B174" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C174" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D174" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E174" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="F174" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G174" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H174" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I174" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -7406,28 +7376,28 @@
         <v>182</v>
       </c>
       <c r="B175" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C175" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D175" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E175" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="F175" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G175" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="H175" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I175" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -7435,86 +7405,28 @@
         <v>183</v>
       </c>
       <c r="B176" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C176" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D176" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E176" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F176" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G176" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="H176" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="I176" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9">
-      <c r="A177" t="s">
-        <v>184</v>
-      </c>
-      <c r="B177" t="s">
-        <v>361</v>
-      </c>
-      <c r="C177" t="s">
-        <v>451</v>
-      </c>
-      <c r="D177" t="s">
-        <v>453</v>
-      </c>
-      <c r="E177" t="s">
-        <v>459</v>
-      </c>
-      <c r="F177" t="s">
-        <v>521</v>
-      </c>
-      <c r="G177" t="s">
-        <v>665</v>
-      </c>
-      <c r="H177" t="s">
-        <v>667</v>
-      </c>
-      <c r="I177" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9">
-      <c r="A178" t="s">
-        <v>185</v>
-      </c>
-      <c r="B178" t="s">
-        <v>362</v>
-      </c>
-      <c r="C178" t="s">
-        <v>451</v>
-      </c>
-      <c r="D178" t="s">
-        <v>453</v>
-      </c>
-      <c r="E178" t="s">
-        <v>471</v>
-      </c>
-      <c r="F178" t="s">
-        <v>521</v>
-      </c>
-      <c r="G178" t="s">
-        <v>666</v>
-      </c>
-      <c r="H178" t="s">
-        <v>667</v>
-      </c>
-      <c r="I178" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>

--- a/data/BioTecnos.xlsx
+++ b/data/BioTecnos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="644">
   <si>
     <t>ID</t>
   </si>
@@ -553,21 +553,6 @@
     <t>729</t>
   </si>
   <si>
-    <t>728</t>
-  </si>
-  <si>
-    <t>727</t>
-  </si>
-  <si>
-    <t>726</t>
-  </si>
-  <si>
-    <t>725</t>
-  </si>
-  <si>
-    <t>723</t>
-  </si>
-  <si>
     <t>M04D002LI2603</t>
   </si>
   <si>
@@ -1078,21 +1063,6 @@
     <t>M02Q047L24503</t>
   </si>
   <si>
-    <t>M0247514</t>
-  </si>
-  <si>
-    <t>M02Q048L33505</t>
-  </si>
-  <si>
-    <t>M02Q047L14503</t>
-  </si>
-  <si>
-    <t>M02Q068L01505</t>
-  </si>
-  <si>
-    <t>M02Q050L01519</t>
-  </si>
-  <si>
     <t>20-04-2026</t>
   </si>
   <si>
@@ -1348,15 +1318,6 @@
     <t>04-09-2025</t>
   </si>
   <si>
-    <t>03-09-2025</t>
-  </si>
-  <si>
-    <t>02-09-2025</t>
-  </si>
-  <si>
-    <t>01-09-2025</t>
-  </si>
-  <si>
     <t>Avellano</t>
   </si>
   <si>
@@ -1979,12 +1940,6 @@
   </si>
   <si>
     <t>60</t>
-  </si>
-  <si>
-    <t>3.168</t>
-  </si>
-  <si>
-    <t>713</t>
   </si>
   <si>
     <t>NO</t>
@@ -2322,7 +2277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I176"/>
+  <dimension ref="A1:I171"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2359,28 +2314,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D2" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E2" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="F2" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G2" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="H2" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I2" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2388,28 +2343,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D3" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E3" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="F3" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G3" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="H3" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I3" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2417,28 +2372,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C4" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D4" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E4" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="F4" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G4" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="H4" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I4" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2446,28 +2401,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C5" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D5" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E5" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="F5" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G5" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="H5" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I5" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2475,28 +2430,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D6" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E6" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F6" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G6" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="H6" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I6" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2504,28 +2459,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C7" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="D7" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E7" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="F7" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G7" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="H7" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I7" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2533,28 +2488,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C8" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="D8" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E8" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="F8" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G8" t="s">
         <v>68</v>
       </c>
       <c r="H8" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I8" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2562,28 +2517,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C9" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="D9" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E9" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="F9" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G9" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="H9" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I9" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2591,28 +2546,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C10" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="D10" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E10" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="F10" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G10" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="H10" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I10" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2620,28 +2575,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C11" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="D11" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E11" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="F11" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G11" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="H11" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I11" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2649,28 +2604,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C12" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="D12" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E12" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="F12" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G12" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="H12" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I12" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2678,28 +2633,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C13" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="D13" t="s">
+        <v>435</v>
+      </c>
+      <c r="E13" t="s">
         <v>448</v>
       </c>
-      <c r="E13" t="s">
-        <v>461</v>
-      </c>
       <c r="F13" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G13" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="H13" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I13" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2707,28 +2662,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C14" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="D14" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E14" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="F14" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G14" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="H14" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I14" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2736,28 +2691,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="D15" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E15" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="F15" t="s">
+        <v>503</v>
+      </c>
+      <c r="G15" t="s">
         <v>516</v>
       </c>
-      <c r="G15" t="s">
-        <v>529</v>
-      </c>
       <c r="H15" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I15" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2765,28 +2720,28 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C16" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="D16" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E16" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F16" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G16" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="H16" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I16" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -2794,28 +2749,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C17" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="D17" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E17" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="F17" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G17" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="H17" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I17" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2823,28 +2778,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C18" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="D18" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E18" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F18" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G18" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="H18" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I18" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -2852,28 +2807,28 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C19" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D19" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E19" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F19" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G19" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="H19" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I19" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2881,28 +2836,28 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C20" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D20" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E20" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="F20" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G20" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="H20" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I20" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -2910,28 +2865,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C21" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D21" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E21" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="F21" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G21" t="s">
         <v>157</v>
       </c>
       <c r="H21" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I21" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -2939,28 +2894,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C22" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D22" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E22" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="F22" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G22" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="H22" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I22" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -2968,28 +2923,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C23" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D23" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E23" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="F23" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G23" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="H23" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I23" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -2997,28 +2952,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C24" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D24" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E24" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="F24" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G24" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="H24" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I24" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -3026,28 +2981,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C25" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D25" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E25" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="F25" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G25" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="H25" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I25" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -3055,28 +3010,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C26" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D26" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E26" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="F26" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G26" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="H26" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I26" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -3084,28 +3039,28 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C27" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D27" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E27" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="F27" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G27" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="H27" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I27" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -3113,28 +3068,28 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C28" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D28" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E28" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="F28" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G28" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="H28" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I28" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -3142,28 +3097,28 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C29" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="D29" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="E29" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="F29" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G29" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="H29" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I29" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -3171,28 +3126,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C30" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="D30" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E30" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="F30" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G30" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="H30" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I30" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -3200,28 +3155,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C31" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="D31" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E31" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="F31" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G31" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="H31" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I31" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -3229,28 +3184,28 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C32" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="D32" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E32" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="F32" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G32" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="H32" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I32" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -3258,28 +3213,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C33" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="D33" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E33" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="F33" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G33" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="H33" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I33" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -3287,28 +3242,28 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C34" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="D34" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E34" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="F34" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G34" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="H34" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I34" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -3316,28 +3271,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C35" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="D35" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E35" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="F35" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G35" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="H35" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I35" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -3345,28 +3300,28 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C36" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D36" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E36" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="F36" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G36" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="H36" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I36" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -3374,28 +3329,28 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C37" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D37" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E37" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="F37" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G37" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="H37" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I37" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -3403,28 +3358,28 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C38" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D38" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E38" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="F38" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G38" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="H38" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I38" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -3432,28 +3387,28 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C39" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D39" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E39" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="F39" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G39" t="s">
         <v>121</v>
       </c>
       <c r="H39" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I39" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -3461,28 +3416,28 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C40" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D40" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E40" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="F40" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G40" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="H40" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I40" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -3490,28 +3445,28 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C41" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D41" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E41" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="F41" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G41" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="H41" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I41" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -3519,28 +3474,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C42" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="D42" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E42" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="F42" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G42" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="H42" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I42" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -3548,28 +3503,28 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C43" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D43" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E43" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F43" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G43" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="H43" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I43" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -3577,28 +3532,28 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C44" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="D44" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E44" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F44" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G44" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="H44" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I44" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -3606,28 +3561,28 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C45" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="D45" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E45" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="F45" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G45" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="H45" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I45" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -3635,28 +3590,28 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C46" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D46" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E46" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="F46" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G46" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="H46" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I46" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -3664,28 +3619,28 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C47" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D47" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E47" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="F47" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G47" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="H47" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I47" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -3693,28 +3648,28 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C48" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D48" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E48" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="F48" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G48" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="H48" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I48" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -3722,28 +3677,28 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C49" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="D49" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E49" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="F49" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G49" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="H49" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I49" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -3751,28 +3706,28 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C50" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="D50" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E50" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="F50" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G50" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="H50" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I50" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -3780,28 +3735,28 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C51" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D51" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E51" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="F51" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G51" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="H51" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I51" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -3809,28 +3764,28 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C52" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D52" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E52" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="F52" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G52" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="H52" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I52" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -3838,28 +3793,28 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C53" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D53" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E53" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="F53" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G53" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="H53" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I53" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -3867,28 +3822,28 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C54" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D54" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E54" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="F54" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G54" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="H54" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I54" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -3896,28 +3851,28 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C55" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D55" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E55" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="F55" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G55" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="H55" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I55" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -3925,28 +3880,28 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C56" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="D56" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E56" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="F56" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G56" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="H56" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I56" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -3954,28 +3909,28 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C57" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="D57" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E57" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="F57" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G57" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="H57" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I57" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -3983,28 +3938,28 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C58" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="D58" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E58" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="F58" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G58" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="H58" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I58" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -4012,28 +3967,28 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C59" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="D59" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E59" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F59" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G59" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="H59" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I59" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -4041,28 +3996,28 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C60" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="D60" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E60" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="F60" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G60" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="H60" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I60" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -4070,28 +4025,28 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C61" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D61" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E61" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="F61" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G61" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="H61" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I61" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -4099,28 +4054,28 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C62" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="D62" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E62" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="F62" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G62" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="H62" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I62" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -4128,28 +4083,28 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C63" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="D63" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E63" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="F63" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G63" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="H63" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I63" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -4157,28 +4112,28 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C64" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="D64" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E64" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="F64" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G64" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="H64" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I64" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -4186,28 +4141,28 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C65" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="D65" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E65" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="F65" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G65" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="H65" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I65" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -4215,28 +4170,28 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C66" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="D66" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E66" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="F66" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G66" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="H66" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I66" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -4244,28 +4199,28 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C67" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="D67" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E67" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="F67" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G67" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="H67" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I67" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -4273,28 +4228,28 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C68" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="D68" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E68" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F68" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G68" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="H68" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I68" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -4302,28 +4257,28 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C69" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="D69" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E69" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="F69" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G69" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="H69" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I69" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -4331,28 +4286,28 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C70" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="D70" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E70" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="F70" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G70" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="H70" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I70" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -4360,28 +4315,28 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C71" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="D71" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E71" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="F71" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G71" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="H71" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I71" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -4389,28 +4344,28 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C72" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="D72" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E72" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="F72" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G72" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="H72" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I72" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -4418,28 +4373,28 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C73" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="D73" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E73" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="F73" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G73" t="s">
         <v>29</v>
       </c>
       <c r="H73" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I73" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -4447,28 +4402,28 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C74" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D74" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="E74" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="F74" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G74" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="H74" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I74" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -4476,28 +4431,28 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C75" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D75" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E75" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="F75" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G75" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="H75" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I75" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -4505,28 +4460,28 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C76" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D76" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E76" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="F76" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G76" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H76" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I76" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -4534,28 +4489,28 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C77" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D77" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E77" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="F77" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G77" t="s">
         <v>38</v>
       </c>
       <c r="H77" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I77" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -4563,28 +4518,28 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C78" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D78" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E78" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F78" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G78" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="H78" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I78" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -4592,28 +4547,28 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C79" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D79" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E79" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="F79" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G79" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="H79" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I79" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -4621,28 +4576,28 @@
         <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C80" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D80" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E80" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="F80" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G80" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="H80" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I80" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -4650,28 +4605,28 @@
         <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C81" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D81" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E81" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="F81" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G81" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="H81" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I81" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -4679,28 +4634,28 @@
         <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C82" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D82" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E82" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="F82" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G82" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H82" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I82" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -4708,28 +4663,28 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C83" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="D83" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E83" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="F83" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G83" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="H83" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I83" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -4737,28 +4692,28 @@
         <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D84" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E84" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="F84" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G84" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="H84" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I84" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -4766,28 +4721,28 @@
         <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C85" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D85" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="E85" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="F85" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G85" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="H85" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I85" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -4795,28 +4750,28 @@
         <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D86" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E86" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="F86" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G86" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="H86" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I86" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -4824,28 +4779,28 @@
         <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C87" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D87" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E87" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="F87" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G87" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="H87" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I87" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -4853,28 +4808,28 @@
         <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C88" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="D88" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E88" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="F88" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G88" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="H88" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I88" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -4882,28 +4837,28 @@
         <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C89" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="D89" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E89" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="F89" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G89" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H89" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I89" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -4911,28 +4866,28 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C90" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D90" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="E90" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="F90" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G90" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="H90" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I90" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -4940,28 +4895,28 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C91" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="D91" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E91" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="F91" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G91" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H91" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I91" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -4969,28 +4924,28 @@
         <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C92" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="D92" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E92" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="F92" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G92" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H92" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I92" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -4998,28 +4953,28 @@
         <v>100</v>
       </c>
       <c r="B93" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C93" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="D93" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E93" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F93" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G93" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H93" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I93" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -5027,28 +4982,28 @@
         <v>101</v>
       </c>
       <c r="B94" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C94" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="D94" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E94" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="F94" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G94" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="H94" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I94" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -5056,28 +5011,28 @@
         <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C95" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="D95" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E95" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="F95" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G95" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="H95" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I95" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -5085,28 +5040,28 @@
         <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C96" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="D96" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E96" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="F96" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G96" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="H96" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I96" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -5114,28 +5069,28 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C97" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="D97" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E97" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="F97" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G97" t="s">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="H97" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I97" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -5143,28 +5098,28 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C98" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="D98" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E98" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="F98" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G98" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="H98" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I98" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -5172,28 +5127,28 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C99" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="D99" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E99" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F99" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G99" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="H99" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I99" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -5201,28 +5156,28 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C100" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="D100" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E100" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="F100" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G100" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="H100" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I100" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -5230,28 +5185,28 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C101" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D101" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E101" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="F101" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G101" t="s">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="H101" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I101" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -5259,28 +5214,28 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C102" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="D102" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E102" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="F102" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G102" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="H102" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I102" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -5288,28 +5243,28 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C103" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="D103" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E103" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="F103" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G103" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="H103" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I103" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -5317,28 +5272,28 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C104" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="D104" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E104" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="F104" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G104" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="H104" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I104" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -5346,28 +5301,28 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C105" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="D105" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E105" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="F105" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G105" t="s">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="H105" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I105" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -5375,28 +5330,28 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C106" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="D106" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E106" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="F106" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G106" t="s">
-        <v>609</v>
+        <v>596</v>
       </c>
       <c r="H106" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I106" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -5404,28 +5359,28 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C107" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="D107" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E107" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="F107" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G107" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="H107" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I107" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -5433,28 +5388,28 @@
         <v>115</v>
       </c>
       <c r="B108" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C108" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="D108" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E108" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="F108" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G108" t="s">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="H108" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I108" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -5462,28 +5417,28 @@
         <v>116</v>
       </c>
       <c r="B109" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C109" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D109" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E109" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="F109" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G109" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="H109" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I109" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -5491,28 +5446,28 @@
         <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C110" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D110" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E110" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="F110" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G110" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="H110" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I110" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -5520,28 +5475,28 @@
         <v>118</v>
       </c>
       <c r="B111" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C111" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="D111" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E111" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="F111" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G111" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="H111" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I111" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -5549,28 +5504,28 @@
         <v>119</v>
       </c>
       <c r="B112" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C112" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="D112" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E112" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="F112" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G112" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="H112" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I112" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -5578,28 +5533,28 @@
         <v>120</v>
       </c>
       <c r="B113" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C113" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="D113" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E113" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="F113" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G113" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="H113" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I113" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -5607,28 +5562,28 @@
         <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C114" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="D114" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E114" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="F114" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G114" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="H114" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I114" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -5636,28 +5591,28 @@
         <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C115" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="D115" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E115" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="F115" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G115" t="s">
         <v>98</v>
       </c>
       <c r="H115" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I115" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -5665,28 +5620,28 @@
         <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C116" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="D116" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E116" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="F116" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G116" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="H116" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I116" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -5694,28 +5649,28 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C117" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D117" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E117" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="F117" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G117" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="H117" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I117" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -5723,28 +5678,28 @@
         <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C118" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D118" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E118" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="F118" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G118" t="s">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="H118" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I118" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -5752,28 +5707,28 @@
         <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C119" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="D119" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E119" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="F119" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G119" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="H119" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I119" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -5781,28 +5736,28 @@
         <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C120" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D120" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E120" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="F120" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G120" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="H120" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I120" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -5810,28 +5765,28 @@
         <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C121" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D121" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E121" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="F121" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G121" t="s">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="H121" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I121" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -5839,28 +5794,28 @@
         <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C122" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="D122" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E122" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F122" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G122" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="H122" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I122" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -5868,28 +5823,28 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C123" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="D123" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E123" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="F123" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G123" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="H123" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I123" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -5897,28 +5852,28 @@
         <v>131</v>
       </c>
       <c r="B124" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C124" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="D124" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E124" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="F124" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G124" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="H124" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I124" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -5926,28 +5881,28 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C125" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D125" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E125" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F125" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G125" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="H125" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I125" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -5955,28 +5910,28 @@
         <v>133</v>
       </c>
       <c r="B126" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C126" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="D126" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E126" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="F126" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G126" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="H126" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I126" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -5984,28 +5939,28 @@
         <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C127" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="D127" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E127" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="F127" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G127" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="H127" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I127" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -6013,28 +5968,28 @@
         <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C128" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="D128" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E128" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="F128" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G128" t="s">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="H128" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I128" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -6042,28 +5997,28 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C129" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="D129" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E129" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="F129" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G129" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="H129" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I129" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -6071,28 +6026,28 @@
         <v>137</v>
       </c>
       <c r="B130" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C130" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="D130" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E130" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="F130" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G130" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="H130" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I130" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -6100,28 +6055,28 @@
         <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C131" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="D131" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E131" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="F131" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G131" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="H131" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I131" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -6129,28 +6084,28 @@
         <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C132" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="D132" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E132" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="F132" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G132" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="H132" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I132" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -6158,28 +6113,28 @@
         <v>140</v>
       </c>
       <c r="B133" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C133" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="D133" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E133" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="F133" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G133" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="H133" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I133" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -6187,28 +6142,28 @@
         <v>141</v>
       </c>
       <c r="B134" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C134" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="D134" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E134" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="F134" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G134" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="H134" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I134" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -6216,28 +6171,28 @@
         <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C135" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="D135" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E135" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="F135" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G135" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="H135" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I135" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -6245,28 +6200,28 @@
         <v>143</v>
       </c>
       <c r="B136" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C136" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="D136" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E136" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="F136" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G136" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="H136" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I136" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -6274,28 +6229,28 @@
         <v>144</v>
       </c>
       <c r="B137" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C137" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="D137" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E137" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="F137" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G137" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H137" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I137" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -6303,28 +6258,28 @@
         <v>145</v>
       </c>
       <c r="B138" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C138" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="D138" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E138" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F138" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G138" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H138" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I138" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -6332,28 +6287,28 @@
         <v>146</v>
       </c>
       <c r="B139" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C139" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="D139" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E139" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F139" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G139" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="H139" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I139" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -6361,28 +6316,28 @@
         <v>147</v>
       </c>
       <c r="B140" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C140" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="D140" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E140" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="F140" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G140" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H140" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I140" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -6390,28 +6345,28 @@
         <v>148</v>
       </c>
       <c r="B141" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C141" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="D141" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E141" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="F141" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G141" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="H141" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I141" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -6419,28 +6374,28 @@
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C142" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D142" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E142" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="F142" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G142" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H142" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I142" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -6448,28 +6403,28 @@
         <v>150</v>
       </c>
       <c r="B143" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C143" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="D143" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E143" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F143" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G143" t="s">
         <v>137</v>
       </c>
       <c r="H143" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I143" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -6477,28 +6432,28 @@
         <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C144" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="D144" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E144" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="F144" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G144" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="H144" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I144" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -6506,28 +6461,28 @@
         <v>152</v>
       </c>
       <c r="B145" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C145" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D145" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E145" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="F145" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G145" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="H145" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I145" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -6535,28 +6490,28 @@
         <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C146" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D146" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E146" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="F146" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G146" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H146" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I146" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -6564,28 +6519,28 @@
         <v>154</v>
       </c>
       <c r="B147" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C147" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="D147" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E147" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="F147" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G147" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="H147" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I147" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -6593,28 +6548,28 @@
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C148" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="D148" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E148" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F148" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G148" t="s">
         <v>127</v>
       </c>
       <c r="H148" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I148" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -6622,28 +6577,28 @@
         <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C149" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="D149" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E149" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F149" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G149" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="H149" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I149" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -6651,28 +6606,28 @@
         <v>157</v>
       </c>
       <c r="B150" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C150" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="D150" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E150" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F150" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G150" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="H150" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I150" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -6680,28 +6635,28 @@
         <v>158</v>
       </c>
       <c r="B151" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C151" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D151" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E151" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="F151" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G151" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="H151" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I151" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -6709,28 +6664,28 @@
         <v>159</v>
       </c>
       <c r="B152" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C152" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D152" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E152" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="F152" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G152" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="H152" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I152" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -6738,28 +6693,28 @@
         <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C153" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D153" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E153" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="F153" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G153" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="H153" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I153" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -6767,28 +6722,28 @@
         <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C154" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D154" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E154" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F154" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G154" t="s">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="H154" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I154" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -6796,28 +6751,28 @@
         <v>162</v>
       </c>
       <c r="B155" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C155" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D155" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E155" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="F155" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G155" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H155" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I155" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -6825,28 +6780,28 @@
         <v>163</v>
       </c>
       <c r="B156" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C156" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="D156" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E156" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="F156" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G156" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="H156" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I156" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -6854,28 +6809,28 @@
         <v>164</v>
       </c>
       <c r="B157" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C157" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D157" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E157" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F157" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G157" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="H157" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I157" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -6883,28 +6838,28 @@
         <v>165</v>
       </c>
       <c r="B158" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C158" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="D158" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E158" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="F158" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G158" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="H158" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I158" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -6912,28 +6867,28 @@
         <v>166</v>
       </c>
       <c r="B159" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C159" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D159" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E159" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="F159" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G159" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H159" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I159" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -6941,28 +6896,28 @@
         <v>167</v>
       </c>
       <c r="B160" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C160" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="D160" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E160" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="F160" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G160" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H160" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I160" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -6970,28 +6925,28 @@
         <v>168</v>
       </c>
       <c r="B161" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C161" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="D161" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E161" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="F161" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G161" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="H161" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I161" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -6999,28 +6954,28 @@
         <v>169</v>
       </c>
       <c r="B162" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C162" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="D162" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E162" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="F162" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G162" t="s">
         <v>121</v>
       </c>
       <c r="H162" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I162" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -7028,28 +6983,28 @@
         <v>170</v>
       </c>
       <c r="B163" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C163" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D163" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E163" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="F163" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G163" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="H163" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I163" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -7057,28 +7012,28 @@
         <v>171</v>
       </c>
       <c r="B164" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C164" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D164" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E164" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="F164" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G164" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="H164" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I164" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -7086,28 +7041,28 @@
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C165" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D165" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E165" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="F165" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G165" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H165" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I165" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -7115,28 +7070,28 @@
         <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C166" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="D166" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E166" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="F166" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G166" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H166" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I166" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -7144,28 +7099,28 @@
         <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C167" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="D167" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E167" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="F167" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G167" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="H167" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I167" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -7173,28 +7128,28 @@
         <v>175</v>
       </c>
       <c r="B168" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C168" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="D168" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E168" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="F168" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G168" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H168" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I168" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -7202,28 +7157,28 @@
         <v>176</v>
       </c>
       <c r="B169" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C169" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="D169" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E169" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="F169" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G169" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H169" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I169" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -7231,28 +7186,28 @@
         <v>177</v>
       </c>
       <c r="B170" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C170" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="D170" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E170" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="F170" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G170" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="H170" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I170" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -7260,173 +7215,28 @@
         <v>178</v>
       </c>
       <c r="B171" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C171" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="D171" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E171" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="F171" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="G171" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H171" t="s">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="I171" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9">
-      <c r="A172" t="s">
-        <v>179</v>
-      </c>
-      <c r="B172" t="s">
-        <v>354</v>
-      </c>
-      <c r="C172" t="s">
-        <v>444</v>
-      </c>
-      <c r="D172" t="s">
-        <v>448</v>
-      </c>
-      <c r="E172" t="s">
-        <v>505</v>
-      </c>
-      <c r="F172" t="s">
-        <v>516</v>
-      </c>
-      <c r="G172" t="s">
-        <v>586</v>
-      </c>
-      <c r="H172" t="s">
-        <v>657</v>
-      </c>
-      <c r="I172" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9">
-      <c r="A173" t="s">
-        <v>180</v>
-      </c>
-      <c r="B173" t="s">
-        <v>355</v>
-      </c>
-      <c r="C173" t="s">
-        <v>445</v>
-      </c>
-      <c r="D173" t="s">
-        <v>448</v>
-      </c>
-      <c r="E173" t="s">
-        <v>463</v>
-      </c>
-      <c r="F173" t="s">
-        <v>516</v>
-      </c>
-      <c r="G173" t="s">
-        <v>655</v>
-      </c>
-      <c r="H173" t="s">
-        <v>657</v>
-      </c>
-      <c r="I173" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9">
-      <c r="A174" t="s">
-        <v>181</v>
-      </c>
-      <c r="B174" t="s">
-        <v>356</v>
-      </c>
-      <c r="C174" t="s">
-        <v>445</v>
-      </c>
-      <c r="D174" t="s">
-        <v>448</v>
-      </c>
-      <c r="E174" t="s">
-        <v>481</v>
-      </c>
-      <c r="F174" t="s">
-        <v>516</v>
-      </c>
-      <c r="G174" t="s">
-        <v>586</v>
-      </c>
-      <c r="H174" t="s">
-        <v>657</v>
-      </c>
-      <c r="I174" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9">
-      <c r="A175" t="s">
-        <v>182</v>
-      </c>
-      <c r="B175" t="s">
-        <v>357</v>
-      </c>
-      <c r="C175" t="s">
-        <v>446</v>
-      </c>
-      <c r="D175" t="s">
-        <v>448</v>
-      </c>
-      <c r="E175" t="s">
-        <v>492</v>
-      </c>
-      <c r="F175" t="s">
-        <v>516</v>
-      </c>
-      <c r="G175" t="s">
-        <v>656</v>
-      </c>
-      <c r="H175" t="s">
-        <v>657</v>
-      </c>
-      <c r="I175" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9">
-      <c r="A176" t="s">
-        <v>183</v>
-      </c>
-      <c r="B176" t="s">
-        <v>358</v>
-      </c>
-      <c r="C176" t="s">
-        <v>446</v>
-      </c>
-      <c r="D176" t="s">
-        <v>448</v>
-      </c>
-      <c r="E176" t="s">
-        <v>488</v>
-      </c>
-      <c r="F176" t="s">
-        <v>516</v>
-      </c>
-      <c r="G176" t="s">
-        <v>586</v>
-      </c>
-      <c r="H176" t="s">
-        <v>657</v>
-      </c>
-      <c r="I176" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>

--- a/data/BioTecnos.xlsx
+++ b/data/BioTecnos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="640">
   <si>
     <t>ID</t>
   </si>
@@ -550,9 +550,6 @@
     <t>730</t>
   </si>
   <si>
-    <t>729</t>
-  </si>
-  <si>
     <t>M04D002LI2603</t>
   </si>
   <si>
@@ -1060,9 +1057,6 @@
     <t>M02Q048L23502</t>
   </si>
   <si>
-    <t>M02Q047L24503</t>
-  </si>
-  <si>
     <t>20-04-2026</t>
   </si>
   <si>
@@ -1315,9 +1309,6 @@
     <t>05-09-2025</t>
   </si>
   <si>
-    <t>04-09-2025</t>
-  </si>
-  <si>
     <t>Avellano</t>
   </si>
   <si>
@@ -1765,7 +1756,7 @@
     <t>15.591</t>
   </si>
   <si>
-    <t>10.238</t>
+    <t>8.839</t>
   </si>
   <si>
     <t>3.635</t>
@@ -1825,16 +1816,13 @@
     <t>12.264</t>
   </si>
   <si>
-    <t>528</t>
-  </si>
-  <si>
     <t>3.887</t>
   </si>
   <si>
     <t>408</t>
   </si>
   <si>
-    <t>1.741</t>
+    <t>355</t>
   </si>
   <si>
     <t>1.392</t>
@@ -2277,7 +2265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I171"/>
+  <dimension ref="A1:I170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2314,28 +2302,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E2" t="s">
         <v>434</v>
       </c>
-      <c r="E2" t="s">
-        <v>437</v>
-      </c>
       <c r="F2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H2" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2343,28 +2331,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D3" t="s">
+        <v>432</v>
+      </c>
+      <c r="E3" t="s">
         <v>435</v>
       </c>
-      <c r="E3" t="s">
-        <v>438</v>
-      </c>
       <c r="F3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H3" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I3" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2372,28 +2360,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D4" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E4" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F4" t="s">
+        <v>500</v>
+      </c>
+      <c r="G4" t="s">
         <v>503</v>
       </c>
-      <c r="G4" t="s">
-        <v>506</v>
-      </c>
       <c r="H4" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I4" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2401,28 +2389,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D5" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E5" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F5" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G5" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H5" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I5" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2430,28 +2418,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D6" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E6" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F6" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G6" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H6" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I6" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2459,28 +2447,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C7" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D7" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E7" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F7" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G7" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="H7" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I7" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2488,28 +2476,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C8" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D8" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E8" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F8" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G8" t="s">
         <v>68</v>
       </c>
       <c r="H8" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I8" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2517,28 +2505,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C9" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D9" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E9" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F9" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G9" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H9" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I9" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2546,28 +2534,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D10" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E10" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F10" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G10" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="H10" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I10" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2575,28 +2563,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D11" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E11" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F11" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G11" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H11" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I11" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2604,28 +2592,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D12" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E12" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F12" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G12" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="H12" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I12" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2633,28 +2621,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C13" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D13" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E13" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F13" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G13" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H13" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I13" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2662,28 +2650,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C14" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D14" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E14" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F14" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G14" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="H14" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I14" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2691,28 +2679,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C15" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D15" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E15" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F15" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G15" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="H15" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I15" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2720,28 +2708,28 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D16" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E16" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F16" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G16" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="H16" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I16" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -2749,28 +2737,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C17" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D17" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E17" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F17" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G17" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="H17" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I17" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2778,28 +2766,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C18" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D18" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E18" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F18" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G18" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="H18" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I18" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -2807,28 +2795,28 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C19" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D19" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E19" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F19" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G19" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="H19" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I19" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2836,28 +2824,28 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C20" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D20" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E20" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F20" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G20" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="H20" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I20" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -2865,28 +2853,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C21" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D21" t="s">
+        <v>432</v>
+      </c>
+      <c r="E21" t="s">
         <v>435</v>
       </c>
-      <c r="E21" t="s">
-        <v>438</v>
-      </c>
       <c r="F21" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G21" t="s">
         <v>157</v>
       </c>
       <c r="H21" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I21" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -2894,28 +2882,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C22" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D22" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E22" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F22" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G22" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="H22" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I22" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -2923,28 +2911,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C23" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D23" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E23" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F23" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G23" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="H23" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I23" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -2952,28 +2940,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C24" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D24" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E24" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F24" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G24" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="H24" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I24" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -2981,28 +2969,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C25" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D25" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E25" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F25" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G25" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="H25" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I25" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -3010,28 +2998,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C26" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D26" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E26" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F26" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G26" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="H26" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I26" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -3039,28 +3027,28 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C27" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D27" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E27" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F27" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G27" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H27" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I27" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -3068,28 +3056,28 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C28" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D28" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E28" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F28" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G28" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H28" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I28" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -3097,28 +3085,28 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C29" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D29" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E29" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F29" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G29" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="H29" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I29" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -3126,28 +3114,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C30" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D30" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E30" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F30" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G30" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="H30" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I30" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -3155,28 +3143,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C31" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D31" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E31" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F31" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G31" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H31" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I31" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -3184,28 +3172,28 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C32" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D32" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E32" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F32" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G32" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="H32" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I32" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -3213,28 +3201,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C33" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D33" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E33" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F33" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G33" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="H33" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I33" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -3242,28 +3230,28 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C34" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D34" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E34" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F34" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G34" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="H34" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I34" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -3271,28 +3259,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C35" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D35" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E35" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F35" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G35" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="H35" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I35" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -3300,28 +3288,28 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C36" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D36" t="s">
+        <v>431</v>
+      </c>
+      <c r="E36" t="s">
         <v>434</v>
       </c>
-      <c r="E36" t="s">
-        <v>437</v>
-      </c>
       <c r="F36" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G36" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="H36" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I36" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -3329,28 +3317,28 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C37" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D37" t="s">
+        <v>431</v>
+      </c>
+      <c r="E37" t="s">
         <v>434</v>
       </c>
-      <c r="E37" t="s">
-        <v>437</v>
-      </c>
       <c r="F37" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G37" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="H37" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I37" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -3358,28 +3346,28 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C38" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D38" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E38" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F38" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G38" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="H38" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I38" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -3387,28 +3375,28 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C39" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D39" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E39" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F39" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G39" t="s">
         <v>121</v>
       </c>
       <c r="H39" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I39" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -3416,28 +3404,28 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C40" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D40" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E40" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F40" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G40" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="H40" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I40" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -3445,28 +3433,28 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C41" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D41" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E41" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F41" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G41" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="H41" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I41" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -3474,28 +3462,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C42" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D42" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E42" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F42" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G42" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H42" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I42" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -3503,28 +3491,28 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C43" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D43" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E43" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F43" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G43" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="H43" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I43" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -3532,28 +3520,28 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C44" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D44" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E44" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F44" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G44" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="H44" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I44" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -3561,28 +3549,28 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C45" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D45" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E45" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F45" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G45" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H45" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I45" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -3590,28 +3578,28 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C46" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D46" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E46" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F46" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G46" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="H46" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I46" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -3619,28 +3607,28 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C47" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D47" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E47" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="F47" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G47" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H47" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I47" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -3648,28 +3636,28 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C48" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D48" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E48" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F48" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G48" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H48" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I48" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -3677,28 +3665,28 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C49" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D49" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E49" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F49" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G49" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="H49" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I49" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -3706,28 +3694,28 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C50" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D50" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E50" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F50" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G50" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="H50" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I50" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -3735,28 +3723,28 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C51" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D51" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E51" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F51" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G51" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H51" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I51" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -3764,28 +3752,28 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C52" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D52" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E52" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F52" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G52" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="H52" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I52" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -3793,28 +3781,28 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C53" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D53" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E53" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F53" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G53" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H53" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I53" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -3822,28 +3810,28 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C54" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D54" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E54" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="F54" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G54" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H54" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I54" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -3851,28 +3839,28 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C55" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D55" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E55" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F55" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G55" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H55" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I55" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -3880,28 +3868,28 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C56" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D56" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E56" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F56" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G56" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="H56" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I56" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -3909,28 +3897,28 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C57" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D57" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E57" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F57" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G57" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H57" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I57" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -3938,28 +3926,28 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C58" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D58" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E58" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F58" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G58" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H58" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I58" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -3967,28 +3955,28 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C59" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D59" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E59" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F59" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G59" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H59" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I59" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -3996,28 +3984,28 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C60" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D60" t="s">
+        <v>432</v>
+      </c>
+      <c r="E60" t="s">
         <v>435</v>
       </c>
-      <c r="E60" t="s">
-        <v>438</v>
-      </c>
       <c r="F60" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G60" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H60" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I60" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -4025,28 +4013,28 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C61" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D61" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E61" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F61" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G61" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="H61" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I61" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -4054,28 +4042,28 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C62" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D62" t="s">
+        <v>432</v>
+      </c>
+      <c r="E62" t="s">
         <v>435</v>
       </c>
-      <c r="E62" t="s">
-        <v>438</v>
-      </c>
       <c r="F62" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G62" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="H62" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I62" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -4083,28 +4071,28 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C63" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D63" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E63" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F63" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G63" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="H63" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I63" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -4112,28 +4100,28 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C64" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E64" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F64" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G64" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H64" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I64" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -4141,28 +4129,28 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C65" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D65" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E65" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F65" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G65" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="H65" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I65" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -4170,28 +4158,28 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C66" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D66" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E66" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F66" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G66" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="H66" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I66" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -4199,28 +4187,28 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C67" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D67" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E67" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F67" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G67" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="H67" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I67" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -4228,28 +4216,28 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C68" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D68" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E68" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F68" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G68" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="H68" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I68" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -4257,28 +4245,28 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C69" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D69" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E69" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F69" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G69" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="H69" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I69" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -4286,28 +4274,28 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C70" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D70" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E70" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F70" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G70" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="H70" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I70" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -4315,28 +4303,28 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C71" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D71" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E71" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F71" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G71" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="H71" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I71" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -4344,28 +4332,28 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C72" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D72" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E72" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F72" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G72" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="H72" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I72" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -4373,28 +4361,28 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C73" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D73" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E73" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F73" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G73" t="s">
         <v>29</v>
       </c>
       <c r="H73" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I73" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -4402,28 +4390,28 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C74" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D74" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E74" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F74" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G74" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="H74" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I74" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -4431,28 +4419,28 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C75" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D75" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E75" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F75" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G75" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="H75" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I75" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -4460,28 +4448,28 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C76" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D76" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E76" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F76" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G76" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H76" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I76" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -4489,28 +4477,28 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C77" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D77" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E77" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F77" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G77" t="s">
         <v>38</v>
       </c>
       <c r="H77" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I77" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -4518,28 +4506,28 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C78" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D78" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E78" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F78" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G78" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="H78" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I78" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -4547,28 +4535,28 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C79" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D79" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E79" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F79" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G79" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="H79" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I79" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -4576,28 +4564,28 @@
         <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C80" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D80" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E80" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F80" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G80" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="H80" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I80" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -4605,28 +4593,28 @@
         <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C81" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D81" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E81" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F81" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G81" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="H81" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I81" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -4634,28 +4622,28 @@
         <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C82" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D82" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E82" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F82" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G82" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H82" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I82" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -4663,28 +4651,28 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C83" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D83" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E83" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F83" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G83" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="H83" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I83" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -4692,28 +4680,28 @@
         <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C84" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D84" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E84" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F84" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G84" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="H84" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I84" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -4721,28 +4709,28 @@
         <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C85" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D85" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E85" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F85" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G85" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H85" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I85" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -4750,28 +4738,28 @@
         <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C86" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D86" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E86" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F86" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G86" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="H86" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I86" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -4779,28 +4767,28 @@
         <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D87" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E87" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F87" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G87" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="H87" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I87" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -4808,28 +4796,28 @@
         <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C88" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D88" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E88" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F88" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G88" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="H88" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I88" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -4837,28 +4825,28 @@
         <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C89" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D89" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E89" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F89" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G89" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H89" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I89" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -4866,28 +4854,28 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C90" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D90" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E90" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F90" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G90" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="H90" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I90" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -4895,28 +4883,28 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C91" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D91" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E91" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F91" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G91" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H91" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I91" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -4924,28 +4912,28 @@
         <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C92" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D92" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E92" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F92" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G92" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H92" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I92" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -4953,28 +4941,28 @@
         <v>100</v>
       </c>
       <c r="B93" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C93" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D93" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E93" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F93" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G93" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H93" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I93" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -4982,28 +4970,28 @@
         <v>101</v>
       </c>
       <c r="B94" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C94" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D94" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E94" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F94" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G94" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="H94" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I94" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -5011,28 +4999,28 @@
         <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C95" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D95" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E95" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F95" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G95" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="H95" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I95" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -5040,28 +5028,28 @@
         <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C96" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D96" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E96" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F96" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G96" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="H96" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I96" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -5069,28 +5057,28 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C97" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D97" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E97" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F97" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G97" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="H97" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I97" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -5098,28 +5086,28 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C98" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D98" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E98" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F98" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G98" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="H98" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I98" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -5127,28 +5115,28 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C99" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D99" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E99" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F99" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G99" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="H99" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I99" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -5156,28 +5144,28 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C100" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D100" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E100" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F100" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G100" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="H100" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I100" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -5185,28 +5173,28 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C101" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D101" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E101" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F101" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G101" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="H101" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I101" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -5214,28 +5202,28 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C102" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D102" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E102" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F102" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G102" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="H102" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I102" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -5243,28 +5231,28 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C103" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D103" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E103" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F103" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G103" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="H103" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I103" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -5272,28 +5260,28 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C104" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D104" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E104" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F104" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G104" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="H104" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I104" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -5301,28 +5289,28 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C105" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D105" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E105" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F105" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G105" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="H105" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I105" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -5330,28 +5318,28 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C106" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D106" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E106" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F106" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G106" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="H106" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I106" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -5359,28 +5347,28 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C107" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D107" t="s">
+        <v>432</v>
+      </c>
+      <c r="E107" t="s">
         <v>435</v>
       </c>
-      <c r="E107" t="s">
-        <v>438</v>
-      </c>
       <c r="F107" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G107" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H107" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I107" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -5388,28 +5376,28 @@
         <v>115</v>
       </c>
       <c r="B108" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C108" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D108" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E108" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F108" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G108" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="H108" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I108" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -5417,28 +5405,28 @@
         <v>116</v>
       </c>
       <c r="B109" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C109" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D109" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E109" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F109" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G109" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="H109" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I109" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -5446,28 +5434,28 @@
         <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C110" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D110" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E110" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F110" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G110" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="H110" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I110" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -5475,28 +5463,28 @@
         <v>118</v>
       </c>
       <c r="B111" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C111" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D111" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E111" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F111" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G111" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H111" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I111" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -5504,28 +5492,28 @@
         <v>119</v>
       </c>
       <c r="B112" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C112" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D112" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E112" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F112" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G112" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="H112" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I112" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -5533,28 +5521,28 @@
         <v>120</v>
       </c>
       <c r="B113" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C113" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D113" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E113" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F113" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G113" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="H113" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I113" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -5562,28 +5550,28 @@
         <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C114" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D114" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E114" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F114" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G114" t="s">
-        <v>603</v>
+        <v>570</v>
       </c>
       <c r="H114" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I114" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -5591,28 +5579,28 @@
         <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C115" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D115" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E115" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F115" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G115" t="s">
-        <v>98</v>
+        <v>570</v>
       </c>
       <c r="H115" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I115" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -5620,28 +5608,28 @@
         <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C116" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D116" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E116" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F116" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G116" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="H116" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I116" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -5649,28 +5637,28 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C117" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D117" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E117" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F117" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G117" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="H117" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I117" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -5678,28 +5666,28 @@
         <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C118" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D118" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E118" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="F118" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G118" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="H118" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I118" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -5707,28 +5695,28 @@
         <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C119" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D119" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E119" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F119" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G119" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="H119" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I119" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -5736,28 +5724,28 @@
         <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C120" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D120" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E120" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F120" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G120" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="H120" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I120" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -5765,28 +5753,28 @@
         <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C121" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D121" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E121" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F121" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G121" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="H121" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I121" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -5794,28 +5782,28 @@
         <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C122" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D122" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E122" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F122" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G122" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="H122" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I122" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -5823,28 +5811,28 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C123" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D123" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E123" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F123" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G123" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="H123" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I123" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -5852,28 +5840,28 @@
         <v>131</v>
       </c>
       <c r="B124" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C124" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D124" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E124" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F124" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G124" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="H124" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I124" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -5881,28 +5869,28 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C125" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D125" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E125" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F125" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G125" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="H125" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I125" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -5910,28 +5898,28 @@
         <v>133</v>
       </c>
       <c r="B126" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C126" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D126" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E126" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F126" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G126" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="H126" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I126" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -5939,28 +5927,28 @@
         <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C127" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D127" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E127" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F127" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G127" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="H127" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I127" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -5968,28 +5956,28 @@
         <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C128" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D128" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E128" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F128" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G128" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="H128" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I128" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -5997,28 +5985,28 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C129" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D129" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E129" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F129" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G129" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="H129" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I129" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -6026,28 +6014,28 @@
         <v>137</v>
       </c>
       <c r="B130" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C130" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D130" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E130" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F130" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G130" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="H130" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I130" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -6055,28 +6043,28 @@
         <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C131" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D131" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E131" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F131" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G131" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="H131" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I131" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -6084,28 +6072,28 @@
         <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C132" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D132" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E132" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F132" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G132" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="H132" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I132" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -6113,28 +6101,28 @@
         <v>140</v>
       </c>
       <c r="B133" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C133" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D133" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E133" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="F133" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G133" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="H133" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I133" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -6142,28 +6130,28 @@
         <v>141</v>
       </c>
       <c r="B134" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C134" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D134" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E134" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F134" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G134" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="H134" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I134" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -6171,28 +6159,28 @@
         <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C135" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D135" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E135" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F135" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G135" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="H135" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I135" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -6200,28 +6188,28 @@
         <v>143</v>
       </c>
       <c r="B136" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C136" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D136" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E136" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F136" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G136" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="H136" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I136" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -6229,28 +6217,28 @@
         <v>144</v>
       </c>
       <c r="B137" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C137" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D137" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E137" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F137" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G137" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H137" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I137" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -6258,28 +6246,28 @@
         <v>145</v>
       </c>
       <c r="B138" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C138" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D138" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E138" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F138" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G138" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H138" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I138" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -6287,28 +6275,28 @@
         <v>146</v>
       </c>
       <c r="B139" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C139" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D139" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E139" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F139" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G139" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="H139" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I139" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -6316,28 +6304,28 @@
         <v>147</v>
       </c>
       <c r="B140" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C140" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D140" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E140" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F140" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G140" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H140" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I140" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -6345,28 +6333,28 @@
         <v>148</v>
       </c>
       <c r="B141" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C141" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D141" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E141" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F141" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G141" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="H141" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I141" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -6374,28 +6362,28 @@
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C142" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D142" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E142" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F142" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G142" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H142" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I142" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -6403,28 +6391,28 @@
         <v>150</v>
       </c>
       <c r="B143" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C143" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D143" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E143" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F143" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G143" t="s">
         <v>137</v>
       </c>
       <c r="H143" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I143" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -6432,28 +6420,28 @@
         <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C144" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D144" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E144" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F144" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G144" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H144" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I144" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -6461,28 +6449,28 @@
         <v>152</v>
       </c>
       <c r="B145" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C145" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D145" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E145" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F145" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G145" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="H145" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I145" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -6490,28 +6478,28 @@
         <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C146" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D146" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E146" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F146" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G146" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H146" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I146" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -6519,28 +6507,28 @@
         <v>154</v>
       </c>
       <c r="B147" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C147" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D147" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E147" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F147" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G147" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="H147" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I147" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -6548,28 +6536,28 @@
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C148" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D148" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E148" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F148" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G148" t="s">
         <v>127</v>
       </c>
       <c r="H148" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I148" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -6577,28 +6565,28 @@
         <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C149" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D149" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E149" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F149" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G149" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="H149" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I149" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -6606,28 +6594,28 @@
         <v>157</v>
       </c>
       <c r="B150" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C150" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D150" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E150" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F150" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G150" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="H150" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I150" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -6635,28 +6623,28 @@
         <v>158</v>
       </c>
       <c r="B151" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C151" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D151" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E151" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F151" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G151" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="H151" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I151" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -6664,28 +6652,28 @@
         <v>159</v>
       </c>
       <c r="B152" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C152" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D152" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E152" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F152" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G152" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="H152" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I152" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -6693,28 +6681,28 @@
         <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C153" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D153" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E153" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F153" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G153" t="s">
-        <v>532</v>
+        <v>570</v>
       </c>
       <c r="H153" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I153" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -6722,28 +6710,28 @@
         <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C154" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D154" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E154" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F154" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G154" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="H154" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I154" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -6751,28 +6739,28 @@
         <v>162</v>
       </c>
       <c r="B155" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C155" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D155" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E155" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F155" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G155" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H155" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I155" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -6780,28 +6768,28 @@
         <v>163</v>
       </c>
       <c r="B156" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C156" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D156" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E156" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F156" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G156" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="H156" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I156" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -6809,28 +6797,28 @@
         <v>164</v>
       </c>
       <c r="B157" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C157" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D157" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E157" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F157" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G157" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="H157" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I157" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -6838,28 +6826,28 @@
         <v>165</v>
       </c>
       <c r="B158" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C158" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D158" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E158" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F158" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G158" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="H158" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I158" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -6867,28 +6855,28 @@
         <v>166</v>
       </c>
       <c r="B159" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C159" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D159" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E159" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F159" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G159" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H159" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I159" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -6896,28 +6884,28 @@
         <v>167</v>
       </c>
       <c r="B160" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C160" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D160" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E160" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F160" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G160" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H160" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I160" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -6925,28 +6913,28 @@
         <v>168</v>
       </c>
       <c r="B161" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C161" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D161" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E161" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F161" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G161" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="H161" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I161" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -6954,28 +6942,28 @@
         <v>169</v>
       </c>
       <c r="B162" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C162" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D162" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E162" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F162" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G162" t="s">
         <v>121</v>
       </c>
       <c r="H162" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I162" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -6983,28 +6971,28 @@
         <v>170</v>
       </c>
       <c r="B163" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C163" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D163" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E163" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F163" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G163" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="H163" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I163" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -7012,28 +7000,28 @@
         <v>171</v>
       </c>
       <c r="B164" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C164" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D164" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E164" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F164" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G164" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="H164" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I164" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -7041,28 +7029,28 @@
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C165" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D165" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E165" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F165" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G165" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H165" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I165" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -7070,28 +7058,28 @@
         <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C166" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D166" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E166" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F166" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G166" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H166" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I166" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -7099,28 +7087,28 @@
         <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C167" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D167" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E167" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F167" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G167" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="H167" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I167" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -7128,28 +7116,28 @@
         <v>175</v>
       </c>
       <c r="B168" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C168" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E168" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F168" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G168" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H168" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I168" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -7157,28 +7145,28 @@
         <v>176</v>
       </c>
       <c r="B169" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C169" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D169" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E169" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F169" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G169" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H169" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I169" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -7186,57 +7174,28 @@
         <v>177</v>
       </c>
       <c r="B170" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C170" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D170" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E170" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="F170" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G170" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="H170" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I170" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9">
-      <c r="A171" t="s">
-        <v>178</v>
-      </c>
-      <c r="B171" t="s">
-        <v>348</v>
-      </c>
-      <c r="C171" t="s">
-        <v>433</v>
-      </c>
-      <c r="D171" t="s">
-        <v>435</v>
-      </c>
-      <c r="E171" t="s">
-        <v>451</v>
-      </c>
-      <c r="F171" t="s">
-        <v>503</v>
-      </c>
-      <c r="G171" t="s">
-        <v>573</v>
-      </c>
-      <c r="H171" t="s">
-        <v>642</v>
-      </c>
-      <c r="I171" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
